--- a/database/event/2636/event_2636_evp_summary.xlsx
+++ b/database/event/2636/event_2636_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.552899999999999</v>
+        <v>10.5319</v>
       </c>
       <c r="C2" t="n">
-        <v>3.0203</v>
+        <v>3.3299</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4378</v>
+        <v>3.752</v>
       </c>
       <c r="E2" t="n">
-        <v>9.552899999999999</v>
+        <v>10.5319</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9325</v>
+        <v>3.9115</v>
       </c>
       <c r="G2" t="n">
         <v>6.6204</v>
       </c>
       <c r="H2" t="n">
-        <v>2.9325</v>
+        <v>3.9115</v>
       </c>
       <c r="I2" t="n">
-        <v>2.3769</v>
+        <v>3.1704</v>
       </c>
       <c r="J2" t="n">
         <v>7.0274</v>
@@ -529,7 +529,7 @@
         <v>108</v>
       </c>
       <c r="M2" t="n">
-        <v>9.404299999999999</v>
+        <v>10.1978</v>
       </c>
       <c r="N2" t="n">
         <v>151</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.4627</v>
+        <v>9.436999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>2.6757</v>
+        <v>2.9837</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9974</v>
+        <v>3.3158</v>
       </c>
       <c r="E3" t="n">
-        <v>8.4627</v>
+        <v>9.436999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2148</v>
+        <v>4.1892</v>
       </c>
       <c r="G3" t="n">
         <v>5.2478</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2148</v>
+        <v>4.2936</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6057</v>
+        <v>3.48</v>
       </c>
       <c r="J3" t="n">
         <v>5.2478</v>
@@ -575,7 +575,7 @@
         <v>108</v>
       </c>
       <c r="M3" t="n">
-        <v>7.8535</v>
+        <v>8.7278</v>
       </c>
       <c r="N3" t="n">
         <v>151</v>
@@ -584,231 +584,231 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.7703</v>
+        <v>5.2057</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5082</v>
+        <v>1.6459</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5057</v>
+        <v>1.63</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7703</v>
+        <v>5.2057</v>
       </c>
       <c r="F4" t="n">
-        <v>4.6052</v>
+        <v>3.5644</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1651</v>
+        <v>1.6413</v>
       </c>
       <c r="H4" t="n">
-        <v>5.9675</v>
+        <v>3.5644</v>
       </c>
       <c r="I4" t="n">
-        <v>4.8368</v>
+        <v>2.8891</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1651</v>
+        <v>1.6413</v>
       </c>
       <c r="K4" t="n">
-        <v>192</v>
+        <v>49</v>
       </c>
       <c r="L4" t="n">
-        <v>160</v>
+        <v>91</v>
       </c>
       <c r="M4" t="n">
-        <v>5.0019</v>
+        <v>4.5304</v>
       </c>
       <c r="N4" t="n">
-        <v>352</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.6944</v>
+        <v>4.7703</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4842</v>
+        <v>1.5082</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4751</v>
+        <v>1.4566</v>
       </c>
       <c r="E5" t="n">
-        <v>4.6944</v>
+        <v>4.7703</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5658</v>
+        <v>4.6052</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1286</v>
+        <v>0.1651</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5658</v>
+        <v>5.9675</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4586</v>
+        <v>4.8368</v>
       </c>
       <c r="J5" t="n">
-        <v>4.1286</v>
+        <v>0.1651</v>
       </c>
       <c r="K5" t="n">
-        <v>43</v>
+        <v>192</v>
       </c>
       <c r="L5" t="n">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="M5" t="n">
-        <v>4.587199999999999</v>
+        <v>5.0019</v>
       </c>
       <c r="N5" t="n">
-        <v>151</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.3437</v>
+        <v>4.6944</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3734</v>
+        <v>1.4842</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3334</v>
+        <v>1.4263</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3437</v>
+        <v>4.6944</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7024</v>
+        <v>0.5658</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6413</v>
+        <v>4.1286</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7024</v>
+        <v>0.5658</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1904</v>
+        <v>0.4586</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6413</v>
+        <v>4.1286</v>
       </c>
       <c r="K6" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="L6" t="n">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="M6" t="n">
-        <v>3.8317</v>
+        <v>4.587199999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1946</v>
+        <v>4.3871</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3262</v>
+        <v>1.3871</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2732</v>
+        <v>1.3039</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1946</v>
+        <v>4.3871</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0758</v>
+        <v>3.1414</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1188</v>
+        <v>1.2457</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0758</v>
+        <v>3.1414</v>
       </c>
       <c r="I7" t="n">
-        <v>0.872</v>
+        <v>2.5462</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1188</v>
+        <v>1.2457</v>
       </c>
       <c r="K7" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L7" t="n">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9908</v>
+        <v>3.7919</v>
       </c>
       <c r="N7" t="n">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7248</v>
+        <v>4.3517</v>
       </c>
       <c r="C8" t="n">
-        <v>1.1777</v>
+        <v>1.3759</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0834</v>
+        <v>1.2898</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7248</v>
+        <v>4.3517</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4791</v>
+        <v>1.2329</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2457</v>
+        <v>3.1188</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4791</v>
+        <v>1.2329</v>
       </c>
       <c r="I8" t="n">
-        <v>2.0094</v>
+        <v>0.9993</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2457</v>
+        <v>3.1188</v>
       </c>
       <c r="K8" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="L8" t="n">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2551</v>
+        <v>4.1181</v>
       </c>
       <c r="N8" t="n">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9">
@@ -824,7 +824,7 @@
         <v>1.0867</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9255</v>
       </c>
       <c r="E9" t="n">
         <v>3.4372</v>
@@ -860,93 +860,93 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9802</v>
+        <v>3.0396</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9423</v>
+        <v>0.961</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7826</v>
+        <v>0.7671</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9802</v>
+        <v>3.0396</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3858</v>
+        <v>1.6329</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5944</v>
+        <v>1.4067</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3858</v>
+        <v>1.6329</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3127</v>
+        <v>1.3235</v>
       </c>
       <c r="J10" t="n">
-        <v>2.5944</v>
+        <v>1.4067</v>
       </c>
       <c r="K10" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L10" t="n">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9071</v>
+        <v>2.7302</v>
       </c>
       <c r="N10" t="n">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9453</v>
+        <v>2.9802</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9312</v>
+        <v>0.9423</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7685</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9453</v>
+        <v>2.9802</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5386</v>
+        <v>0.3858</v>
       </c>
       <c r="G11" t="n">
-        <v>1.4067</v>
+        <v>2.5944</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5386</v>
+        <v>0.3858</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2471</v>
+        <v>0.3127</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4067</v>
+        <v>2.5944</v>
       </c>
       <c r="K11" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="L11" t="n">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="M11" t="n">
-        <v>2.6538</v>
+        <v>2.9071</v>
       </c>
       <c r="N11" t="n">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12">
@@ -962,7 +962,7 @@
         <v>0.914</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7465000000000001</v>
+        <v>0.7078</v>
       </c>
       <c r="E12" t="n">
         <v>2.8908</v>
@@ -1008,7 +1008,7 @@
         <v>0.6913</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4619</v>
+        <v>0.4272</v>
       </c>
       <c r="E13" t="n">
         <v>2.1864</v>
@@ -1044,127 +1044,127 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.535</v>
+        <v>1.63</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4853</v>
+        <v>0.5154</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1987</v>
+        <v>0.2055</v>
       </c>
       <c r="E14" t="n">
-        <v>1.535</v>
+        <v>1.63</v>
       </c>
       <c r="F14" t="n">
-        <v>1.535</v>
+        <v>2.63</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H14" t="n">
-        <v>1.535</v>
+        <v>2.63</v>
       </c>
       <c r="I14" t="n">
-        <v>1.535</v>
+        <v>2.1317</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K14" t="n">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M14" t="n">
-        <v>1.535</v>
+        <v>1.1317</v>
       </c>
       <c r="N14" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.1966</v>
+        <v>1.5422</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3783</v>
+        <v>0.4876</v>
       </c>
       <c r="D15" t="n">
-        <v>0.062</v>
+        <v>0.1705</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1966</v>
+        <v>1.5422</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6864</v>
+        <v>1.5422</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4898</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6864</v>
+        <v>1.5422</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3669</v>
+        <v>1.5422</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4898</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="L15" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8771</v>
+        <v>1.5422</v>
       </c>
       <c r="N15" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.1884</v>
+        <v>1.1966</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3757</v>
+        <v>0.3783</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0587</v>
+        <v>0.0328</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1884</v>
+        <v>1.1966</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1884</v>
+        <v>1.6864</v>
       </c>
       <c r="G16" t="n">
-        <v>-1</v>
+        <v>-0.4898</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1884</v>
+        <v>1.6864</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7738</v>
+        <v>1.3669</v>
       </c>
       <c r="J16" t="n">
-        <v>-1</v>
+        <v>-0.4898</v>
       </c>
       <c r="K16" t="n">
         <v>103</v>
@@ -1173,7 +1173,7 @@
         <v>39</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7738</v>
+        <v>0.8771</v>
       </c>
       <c r="N16" t="n">
         <v>142</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.024</v>
+        <v>1.0253</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3238</v>
+        <v>0.3242</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0077</v>
+        <v>-0.0354</v>
       </c>
       <c r="E17" t="n">
-        <v>1.024</v>
+        <v>1.0253</v>
       </c>
       <c r="F17" t="n">
-        <v>1.024</v>
+        <v>1.0253</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.024</v>
+        <v>1.0253</v>
       </c>
       <c r="I17" t="n">
-        <v>1.024</v>
+        <v>1.0253</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.024</v>
+        <v>1.0253</v>
       </c>
       <c r="N17" t="n">
         <v>145</v>
@@ -1238,7 +1238,7 @@
         <v>0.3137</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0205</v>
+        <v>-0.0486</v>
       </c>
       <c r="E18" t="n">
         <v>0.9923</v>
@@ -1284,7 +1284,7 @@
         <v>0.2723</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0735</v>
+        <v>-0.1008</v>
       </c>
       <c r="E19" t="n">
         <v>0.8612</v>
@@ -1330,7 +1330,7 @@
         <v>0.1853</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1846</v>
+        <v>-0.2104</v>
       </c>
       <c r="E20" t="n">
         <v>0.5861</v>
@@ -1376,7 +1376,7 @@
         <v>0.1696</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2047</v>
+        <v>-0.2302</v>
       </c>
       <c r="E21" t="n">
         <v>0.5364</v>
@@ -1422,7 +1422,7 @@
         <v>0.1653</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2102</v>
+        <v>-0.2356</v>
       </c>
       <c r="E22" t="n">
         <v>0.5228</v>
@@ -1468,7 +1468,7 @@
         <v>-0.0022</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4242</v>
+        <v>-0.4467</v>
       </c>
       <c r="E23" t="n">
         <v>-0.007</v>
@@ -1514,7 +1514,7 @@
         <v>-0.0026</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4247</v>
+        <v>-0.4472</v>
       </c>
       <c r="E24" t="n">
         <v>-0.008200000000000001</v>
@@ -1560,7 +1560,7 @@
         <v>-0.057</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4942</v>
+        <v>-0.5157</v>
       </c>
       <c r="E25" t="n">
         <v>-0.1802</v>
@@ -1606,7 +1606,7 @@
         <v>-0.07770000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5206</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="E26" t="n">
         <v>-0.2456</v>
@@ -1652,7 +1652,7 @@
         <v>-0.1385</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="E27" t="n">
         <v>-0.4381</v>
@@ -1688,231 +1688,231 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>xms</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.6718</v>
+        <v>-0.5065</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.2124</v>
+        <v>-0.1601</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6928</v>
+        <v>-0.6457000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.6718</v>
+        <v>-0.5065</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.6718</v>
+        <v>0.4935</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.6718</v>
+        <v>0.4935</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.6718</v>
+        <v>0.4</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K28" t="n">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.6718</v>
+        <v>-0.6</v>
       </c>
       <c r="N28" t="n">
-        <v>79</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>xms</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.6772</v>
+        <v>-0.6718</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2141</v>
+        <v>-0.2124</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6949</v>
+        <v>-0.7116</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.6772</v>
+        <v>-0.6718</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.6772</v>
+        <v>-0.6718</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.6772</v>
+        <v>-0.6718</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.6772</v>
+        <v>-0.6718</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.6772</v>
+        <v>-0.6718</v>
       </c>
       <c r="N29" t="n">
-        <v>145</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.7267</v>
+        <v>-0.6772</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2298</v>
+        <v>-0.2141</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7149</v>
+        <v>-0.7137</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.7267</v>
+        <v>-0.6772</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2733</v>
+        <v>-0.6772</v>
       </c>
       <c r="G30" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.2733</v>
+        <v>-0.6772</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2215</v>
+        <v>-0.6772</v>
       </c>
       <c r="J30" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="L30" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.7785</v>
+        <v>-0.6772</v>
       </c>
       <c r="N30" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.9046999999999999</v>
+        <v>-0.8986</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.286</v>
+        <v>-0.2841</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.8018999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.9046999999999999</v>
+        <v>-0.8986</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.9046999999999999</v>
+        <v>-0.8986</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.9046999999999999</v>
+        <v>-0.8986</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.9046999999999999</v>
+        <v>-0.8986</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>90</v>
+        <v>145</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.9046999999999999</v>
+        <v>-0.8986</v>
       </c>
       <c r="N31" t="n">
-        <v>90</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.9328</v>
+        <v>-0.9046999999999999</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2949</v>
+        <v>-0.286</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7982</v>
+        <v>-0.8043</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.9328</v>
+        <v>-0.9046999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.9328</v>
+        <v>-0.9046999999999999</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.9328</v>
+        <v>-0.9046999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.9328</v>
+        <v>-0.9046999999999999</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>145</v>
+        <v>90</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.9328</v>
+        <v>-0.9046999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>145</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33">
@@ -1928,7 +1928,7 @@
         <v>-0.3183</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.828</v>
+        <v>-0.845</v>
       </c>
       <c r="E33" t="n">
         <v>-1.0067</v>
@@ -1974,7 +1974,7 @@
         <v>-0.3302</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8433</v>
+        <v>-0.86</v>
       </c>
       <c r="E34" t="n">
         <v>-1.0445</v>
@@ -2020,7 +2020,7 @@
         <v>-0.3608</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8824</v>
+        <v>-0.8986</v>
       </c>
       <c r="E35" t="n">
         <v>-1.1413</v>
@@ -2066,7 +2066,7 @@
         <v>-0.417</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9542</v>
+        <v>-0.9694</v>
       </c>
       <c r="E36" t="n">
         <v>-1.319</v>
@@ -2112,7 +2112,7 @@
         <v>-0.4337</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9755</v>
+        <v>-0.9903999999999999</v>
       </c>
       <c r="E37" t="n">
         <v>-1.3716</v>
@@ -2158,7 +2158,7 @@
         <v>-0.4937</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0521</v>
+        <v>-1.066</v>
       </c>
       <c r="E38" t="n">
         <v>-1.5614</v>
@@ -2204,7 +2204,7 @@
         <v>-0.527</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0948</v>
+        <v>-1.108</v>
       </c>
       <c r="E39" t="n">
         <v>-1.6669</v>
@@ -2250,7 +2250,7 @@
         <v>-0.8463000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.5027</v>
+        <v>-1.5103</v>
       </c>
       <c r="E40" t="n">
         <v>-2.6767</v>
@@ -2296,7 +2296,7 @@
         <v>-1.1379</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.8753</v>
+        <v>-1.8778</v>
       </c>
       <c r="E41" t="n">
         <v>-3.599</v>

--- a/database/event/2636/event_2636_evp_summary.xlsx
+++ b/database/event/2636/event_2636_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.5319</v>
+        <v>9.223699999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>3.3299</v>
+        <v>2.9163</v>
       </c>
       <c r="D2" t="n">
-        <v>3.752</v>
+        <v>3.526</v>
       </c>
       <c r="E2" t="n">
-        <v>10.5319</v>
+        <v>9.223699999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9115</v>
+        <v>3.0916</v>
       </c>
       <c r="G2" t="n">
-        <v>6.6204</v>
+        <v>6.1321</v>
       </c>
       <c r="H2" t="n">
-        <v>3.9115</v>
+        <v>5.4066</v>
       </c>
       <c r="I2" t="n">
-        <v>3.1704</v>
+        <v>2.8112</v>
       </c>
       <c r="J2" t="n">
-        <v>7.0274</v>
+        <v>6.1321</v>
       </c>
       <c r="K2" t="n">
         <v>43</v>
@@ -529,7 +529,7 @@
         <v>108</v>
       </c>
       <c r="M2" t="n">
-        <v>10.1978</v>
+        <v>8.943300000000001</v>
       </c>
       <c r="N2" t="n">
         <v>151</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.436999999999999</v>
+        <v>7.9339</v>
       </c>
       <c r="C3" t="n">
-        <v>2.9837</v>
+        <v>2.5085</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3158</v>
+        <v>2.9437</v>
       </c>
       <c r="E3" t="n">
-        <v>9.436999999999999</v>
+        <v>7.9339</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1892</v>
+        <v>3.2485</v>
       </c>
       <c r="G3" t="n">
-        <v>5.2478</v>
+        <v>4.6854</v>
       </c>
       <c r="H3" t="n">
-        <v>4.2936</v>
+        <v>5.9595</v>
       </c>
       <c r="I3" t="n">
-        <v>3.48</v>
+        <v>3.0987</v>
       </c>
       <c r="J3" t="n">
-        <v>5.2478</v>
+        <v>4.6854</v>
       </c>
       <c r="K3" t="n">
         <v>43</v>
@@ -575,7 +575,7 @@
         <v>108</v>
       </c>
       <c r="M3" t="n">
-        <v>8.7278</v>
+        <v>7.7841</v>
       </c>
       <c r="N3" t="n">
         <v>151</v>
@@ -584,173 +584,173 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.2057</v>
+        <v>5.2087</v>
       </c>
       <c r="C4" t="n">
-        <v>1.6459</v>
+        <v>1.6468</v>
       </c>
       <c r="D4" t="n">
-        <v>1.63</v>
+        <v>1.7135</v>
       </c>
       <c r="E4" t="n">
-        <v>5.2057</v>
+        <v>5.2087</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5644</v>
+        <v>1.2636</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6413</v>
+        <v>3.9451</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5644</v>
+        <v>1.2636</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8891</v>
+        <v>0.657</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6413</v>
+        <v>3.9451</v>
       </c>
       <c r="K4" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="L4" t="n">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="M4" t="n">
-        <v>4.5304</v>
+        <v>4.6021</v>
       </c>
       <c r="N4" t="n">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.7703</v>
+        <v>5.1805</v>
       </c>
       <c r="C5" t="n">
-        <v>1.5082</v>
+        <v>1.6379</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4566</v>
+        <v>1.7007</v>
       </c>
       <c r="E5" t="n">
-        <v>4.7703</v>
+        <v>5.1805</v>
       </c>
       <c r="F5" t="n">
-        <v>4.6052</v>
+        <v>2.1961</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1651</v>
+        <v>2.9844</v>
       </c>
       <c r="H5" t="n">
-        <v>5.9675</v>
+        <v>2.2514</v>
       </c>
       <c r="I5" t="n">
-        <v>4.8368</v>
+        <v>1.1706</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1651</v>
+        <v>2.9844</v>
       </c>
       <c r="K5" t="n">
-        <v>192</v>
+        <v>43</v>
       </c>
       <c r="L5" t="n">
-        <v>160</v>
+        <v>108</v>
       </c>
       <c r="M5" t="n">
-        <v>5.0019</v>
+        <v>4.155</v>
       </c>
       <c r="N5" t="n">
-        <v>352</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.6944</v>
+        <v>4.593</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4842</v>
+        <v>1.4522</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4263</v>
+        <v>1.4355</v>
       </c>
       <c r="E6" t="n">
-        <v>4.6944</v>
+        <v>4.593</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5658</v>
+        <v>4.4518</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1286</v>
+        <v>0.1412</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5658</v>
+        <v>10.3811</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4586</v>
+        <v>5.3977</v>
       </c>
       <c r="J6" t="n">
-        <v>4.1286</v>
+        <v>0.1412</v>
       </c>
       <c r="K6" t="n">
-        <v>43</v>
+        <v>192</v>
       </c>
       <c r="L6" t="n">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="M6" t="n">
-        <v>4.587199999999999</v>
+        <v>5.5389</v>
       </c>
       <c r="N6" t="n">
-        <v>151</v>
+        <v>352</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.3871</v>
+        <v>4.2393</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3871</v>
+        <v>1.3403</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3039</v>
+        <v>1.2758</v>
       </c>
       <c r="E7" t="n">
-        <v>4.3871</v>
+        <v>4.2393</v>
       </c>
       <c r="F7" t="n">
-        <v>3.1414</v>
+        <v>2.9715</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2457</v>
+        <v>1.2678</v>
       </c>
       <c r="H7" t="n">
-        <v>3.1414</v>
+        <v>4.9833</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5462</v>
+        <v>2.5911</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2457</v>
+        <v>1.2678</v>
       </c>
       <c r="K7" t="n">
         <v>49</v>
@@ -759,7 +759,7 @@
         <v>91</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7919</v>
+        <v>3.8589</v>
       </c>
       <c r="N7" t="n">
         <v>140</v>
@@ -768,185 +768,185 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.3517</v>
+        <v>3.8815</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3759</v>
+        <v>1.2272</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2898</v>
+        <v>1.1143</v>
       </c>
       <c r="E8" t="n">
-        <v>4.3517</v>
+        <v>3.8815</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2329</v>
+        <v>2.8357</v>
       </c>
       <c r="G8" t="n">
-        <v>3.1188</v>
+        <v>1.0458</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2329</v>
+        <v>4.505</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9993</v>
+        <v>2.3424</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1188</v>
+        <v>1.0458</v>
       </c>
       <c r="K8" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L8" t="n">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="M8" t="n">
-        <v>4.1181</v>
+        <v>3.3882</v>
       </c>
       <c r="N8" t="n">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.4372</v>
+        <v>3.5884</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0867</v>
+        <v>1.1345</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9255</v>
+        <v>0.982</v>
       </c>
       <c r="E9" t="n">
-        <v>3.4372</v>
+        <v>3.5884</v>
       </c>
       <c r="F9" t="n">
-        <v>3.4372</v>
+        <v>2.3453</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1.2431</v>
       </c>
       <c r="H9" t="n">
-        <v>3.4372</v>
+        <v>2.777</v>
       </c>
       <c r="I9" t="n">
-        <v>3.4372</v>
+        <v>1.4439</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1.2431</v>
       </c>
       <c r="K9" t="n">
-        <v>133</v>
+        <v>49</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4372</v>
+        <v>2.687</v>
       </c>
       <c r="N9" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.0396</v>
+        <v>3.43</v>
       </c>
       <c r="C10" t="n">
-        <v>0.961</v>
+        <v>1.0845</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7671</v>
+        <v>0.9105</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0396</v>
+        <v>3.43</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6329</v>
+        <v>0.9735</v>
       </c>
       <c r="G10" t="n">
-        <v>1.4067</v>
+        <v>2.4565</v>
       </c>
       <c r="H10" t="n">
-        <v>1.6329</v>
+        <v>0.9735</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3235</v>
+        <v>0.5062</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4067</v>
+        <v>2.4565</v>
       </c>
       <c r="K10" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="L10" t="n">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="M10" t="n">
-        <v>2.7302</v>
+        <v>2.9627</v>
       </c>
       <c r="N10" t="n">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9802</v>
+        <v>3.344</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9423</v>
+        <v>1.0573</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.8716</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9802</v>
+        <v>3.344</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3858</v>
+        <v>3.344</v>
       </c>
       <c r="G11" t="n">
-        <v>2.5944</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3858</v>
+        <v>3.983</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3127</v>
+        <v>3.983</v>
       </c>
       <c r="J11" t="n">
-        <v>2.5944</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="L11" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9071</v>
+        <v>3.983</v>
       </c>
       <c r="N11" t="n">
-        <v>151</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8908</v>
+        <v>3.0518</v>
       </c>
       <c r="C12" t="n">
-        <v>0.914</v>
+        <v>0.9649</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7078</v>
+        <v>0.7397</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8908</v>
+        <v>3.0518</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8143</v>
+        <v>2.8797</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0765</v>
+        <v>0.1721</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8143</v>
+        <v>4.6598</v>
       </c>
       <c r="I12" t="n">
-        <v>2.2811</v>
+        <v>2.4229</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0765</v>
+        <v>0.1721</v>
       </c>
       <c r="K12" t="n">
         <v>192</v>
@@ -989,7 +989,7 @@
         <v>160</v>
       </c>
       <c r="M12" t="n">
-        <v>2.3576</v>
+        <v>2.595</v>
       </c>
       <c r="N12" t="n">
         <v>352</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.1864</v>
+        <v>2.681</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6913</v>
+        <v>0.8477</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4272</v>
+        <v>0.5723</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1864</v>
+        <v>2.681</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3219</v>
+        <v>2.6833</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1355</v>
+        <v>-0.0023</v>
       </c>
       <c r="H13" t="n">
-        <v>2.3219</v>
+        <v>3.9679</v>
       </c>
       <c r="I13" t="n">
-        <v>1.882</v>
+        <v>2.0631</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1355</v>
+        <v>-0.0023</v>
       </c>
       <c r="K13" t="n">
         <v>103</v>
@@ -1035,7 +1035,7 @@
         <v>39</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7465</v>
+        <v>2.0608</v>
       </c>
       <c r="N13" t="n">
         <v>142</v>
@@ -1044,35 +1044,35 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.63</v>
+        <v>1.9724</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5154</v>
+        <v>0.6236</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2055</v>
+        <v>0.2524</v>
       </c>
       <c r="E14" t="n">
-        <v>1.63</v>
+        <v>1.9724</v>
       </c>
       <c r="F14" t="n">
-        <v>2.63</v>
+        <v>2.3792</v>
       </c>
       <c r="G14" t="n">
-        <v>-1</v>
+        <v>-0.4068</v>
       </c>
       <c r="H14" t="n">
-        <v>2.63</v>
+        <v>2.8966</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1317</v>
+        <v>1.5061</v>
       </c>
       <c r="J14" t="n">
-        <v>-1</v>
+        <v>-0.4068</v>
       </c>
       <c r="K14" t="n">
         <v>103</v>
@@ -1081,7 +1081,7 @@
         <v>39</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1317</v>
+        <v>1.0993</v>
       </c>
       <c r="N14" t="n">
         <v>142</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.5422</v>
+        <v>1.7866</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4876</v>
+        <v>0.5649</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1705</v>
+        <v>0.1685</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5422</v>
+        <v>1.7866</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5422</v>
+        <v>1.7866</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5422</v>
+        <v>1.7866</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5422</v>
+        <v>1.7866</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.5422</v>
+        <v>1.7866</v>
       </c>
       <c r="N15" t="n">
         <v>145</v>
@@ -1136,35 +1136,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.1966</v>
+        <v>1.7617</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3783</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0328</v>
+        <v>0.1573</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1966</v>
+        <v>1.7617</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6864</v>
+        <v>2.7617</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4898</v>
+        <v>-1</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6864</v>
+        <v>4.2442</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3669</v>
+        <v>2.2068</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4898</v>
+        <v>-1</v>
       </c>
       <c r="K16" t="n">
         <v>103</v>
@@ -1173,7 +1173,7 @@
         <v>39</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8771</v>
+        <v>1.2068</v>
       </c>
       <c r="N16" t="n">
         <v>142</v>
@@ -1182,645 +1182,645 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.0253</v>
+        <v>1.7246</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3242</v>
+        <v>0.5453</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0354</v>
+        <v>0.1406</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0253</v>
+        <v>1.7246</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0253</v>
+        <v>2.2525</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.5279</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0253</v>
+        <v>2.45</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0253</v>
+        <v>1.2739</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.5279</v>
       </c>
       <c r="K17" t="n">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0253</v>
+        <v>0.746</v>
       </c>
       <c r="N17" t="n">
-        <v>145</v>
+        <v>352</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9923</v>
+        <v>1.3356</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3137</v>
+        <v>0.4223</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0486</v>
+        <v>-0.0351</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9923</v>
+        <v>1.3356</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9923</v>
+        <v>1.3356</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9923</v>
+        <v>1.3356</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9923</v>
+        <v>1.3356</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9923</v>
+        <v>1.3356</v>
       </c>
       <c r="N18" t="n">
-        <v>133</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8612</v>
+        <v>1.3068</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2723</v>
+        <v>0.4132</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1008</v>
+        <v>-0.0481</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8612</v>
+        <v>1.3068</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3048</v>
+        <v>1.3068</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4436</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3048</v>
+        <v>1.3068</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0576</v>
+        <v>1.3068</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4436</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>192</v>
+        <v>133</v>
       </c>
       <c r="L19" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6140000000000001</v>
+        <v>1.3068</v>
       </c>
       <c r="N19" t="n">
-        <v>352</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5861</v>
+        <v>1.2632</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1853</v>
+        <v>0.3994</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2104</v>
+        <v>-0.0677</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5861</v>
+        <v>1.2632</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5861</v>
+        <v>1.2632</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5861</v>
+        <v>1.2632</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5861</v>
+        <v>1.2632</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5861</v>
+        <v>1.2632</v>
       </c>
       <c r="N20" t="n">
-        <v>79</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5364</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1696</v>
+        <v>0.2813</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2302</v>
+        <v>-0.2364</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5364</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5364</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5364</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5364</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5364</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5228</v>
+        <v>0.7832</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1653</v>
+        <v>0.2476</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2356</v>
+        <v>-0.2844</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5228</v>
+        <v>0.7832</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5228</v>
+        <v>1.1941</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.4109</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5228</v>
+        <v>1.1941</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5228</v>
+        <v>0.6209</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.4109</v>
       </c>
       <c r="K22" t="n">
-        <v>133</v>
+        <v>49</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5228</v>
+        <v>0.21</v>
       </c>
       <c r="N22" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.007</v>
+        <v>0.7269</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0022</v>
+        <v>0.2298</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4467</v>
+        <v>-0.3099</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.007</v>
+        <v>0.7269</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.007</v>
+        <v>0.7269</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.007</v>
+        <v>0.7269</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.007</v>
+        <v>0.7269</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.007</v>
+        <v>0.7269</v>
       </c>
       <c r="N23" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.5018</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0026</v>
+        <v>0.1587</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4472</v>
+        <v>-0.4115</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.5018</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.008200000000000001</v>
+        <v>1.3799</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.8781</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.008200000000000001</v>
+        <v>1.3799</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.7175</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.8781</v>
       </c>
       <c r="K24" t="n">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.008200000000000001</v>
+        <v>-0.1606</v>
       </c>
       <c r="N24" t="n">
-        <v>79</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1802</v>
+        <v>0.1935</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.057</v>
+        <v>0.0612</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5157</v>
+        <v>-0.5507</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1802</v>
+        <v>0.1935</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1802</v>
+        <v>0.1935</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1802</v>
+        <v>0.1935</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1802</v>
+        <v>0.1935</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1802</v>
+        <v>0.1935</v>
       </c>
       <c r="N25" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.2456</v>
+        <v>0.1394</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.07770000000000001</v>
+        <v>0.0441</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5417999999999999</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.2456</v>
+        <v>0.1394</v>
       </c>
       <c r="F26" t="n">
-        <v>0.55</v>
+        <v>0.1394</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.7956</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.55</v>
+        <v>0.1394</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4458</v>
+        <v>0.1394</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.7956</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="L26" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.3498</v>
+        <v>0.1394</v>
       </c>
       <c r="N26" t="n">
-        <v>140</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.4381</v>
+        <v>0.0745</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1385</v>
+        <v>0.0236</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.6044</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.4381</v>
+        <v>0.0745</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.4381</v>
+        <v>0.0745</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.4381</v>
+        <v>0.0745</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.4381</v>
+        <v>0.0745</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.4381</v>
+        <v>0.0745</v>
       </c>
       <c r="N27" t="n">
-        <v>145</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.5065</v>
+        <v>-0.2769</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1601</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6457000000000001</v>
+        <v>-0.763</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.5065</v>
+        <v>-0.2769</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4935</v>
+        <v>-0.2769</v>
       </c>
       <c r="G28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4935</v>
+        <v>-0.2769</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4</v>
+        <v>-0.2769</v>
       </c>
       <c r="J28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="L28" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.6</v>
+        <v>-0.2769</v>
       </c>
       <c r="N28" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>xms</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.6718</v>
+        <v>-0.309</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2124</v>
+        <v>-0.0977</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7116</v>
+        <v>-0.7775</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.6718</v>
+        <v>-0.309</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.6718</v>
+        <v>-0.309</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.6718</v>
+        <v>-0.309</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.6718</v>
+        <v>-0.309</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.6718</v>
+        <v>-0.309</v>
       </c>
       <c r="N29" t="n">
-        <v>79</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>xms</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.6772</v>
+        <v>-0.3854</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2141</v>
+        <v>-0.1219</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7137</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.6772</v>
+        <v>-0.3854</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.6772</v>
+        <v>-0.3854</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.6772</v>
+        <v>-0.3854</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6772</v>
+        <v>-0.3854</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.6772</v>
+        <v>-0.3854</v>
       </c>
       <c r="N30" t="n">
-        <v>145</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.8986</v>
+        <v>-0.44</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2841</v>
+        <v>-0.1391</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8018999999999999</v>
+        <v>-0.8367</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.8986</v>
+        <v>-0.44</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.8986</v>
+        <v>-0.44</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.8986</v>
+        <v>-0.44</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8986</v>
+        <v>-0.44</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.8986</v>
+        <v>-0.44</v>
       </c>
       <c r="N31" t="n">
         <v>145</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.9046999999999999</v>
+        <v>-0.5225</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.286</v>
+        <v>-0.1652</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8043</v>
+        <v>-0.8739</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.9046999999999999</v>
+        <v>-0.5225</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.9046999999999999</v>
+        <v>-0.5225</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.9046999999999999</v>
+        <v>-0.5225</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.9046999999999999</v>
+        <v>-0.5225</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.9046999999999999</v>
+        <v>-0.5225</v>
       </c>
       <c r="N32" t="n">
         <v>90</v>
@@ -1918,93 +1918,93 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SIXER</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.0067</v>
+        <v>-0.5877</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3183</v>
+        <v>-0.1858</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.845</v>
+        <v>-0.9033</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.0067</v>
+        <v>-0.5877</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.0067</v>
+        <v>-0.5877</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.0067</v>
+        <v>-0.5877</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.0067</v>
+        <v>-0.5877</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.0067</v>
+        <v>-0.5877</v>
       </c>
       <c r="N33" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>SIXER</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.0445</v>
+        <v>-0.6203</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3302</v>
+        <v>-0.1961</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.86</v>
+        <v>-0.918</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.0445</v>
+        <v>-0.6203</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.0445</v>
+        <v>-0.6203</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.0445</v>
+        <v>-0.6203</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.0445</v>
+        <v>-0.6203</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.0445</v>
+        <v>-0.6203</v>
       </c>
       <c r="N34" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1413</v>
+        <v>-0.6611</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3608</v>
+        <v>-0.209</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8986</v>
+        <v>-0.9365</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1413</v>
+        <v>-0.6611</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.1413</v>
+        <v>-0.6611</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.1413</v>
+        <v>-0.6611</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.1413</v>
+        <v>-0.6611</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.1413</v>
+        <v>-0.6611</v>
       </c>
       <c r="N35" t="n">
         <v>133</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.319</v>
+        <v>-0.8168</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.417</v>
+        <v>-0.2582</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9694</v>
+        <v>-1.0068</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.319</v>
+        <v>-0.8168</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.319</v>
+        <v>-0.8168</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.319</v>
+        <v>-0.8168</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.319</v>
+        <v>-0.8168</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.319</v>
+        <v>-0.8168</v>
       </c>
       <c r="N36" t="n">
         <v>133</v>
@@ -2102,139 +2102,139 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.3716</v>
+        <v>-1.1233</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4337</v>
+        <v>-0.3552</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9903999999999999</v>
+        <v>-1.1451</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.3716</v>
+        <v>-1.1233</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.825</v>
+        <v>-0.1233</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.5466</v>
+        <v>-1</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.825</v>
+        <v>-0.1233</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.6687</v>
+        <v>-0.0641</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.5466</v>
+        <v>-1</v>
       </c>
       <c r="K37" t="n">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="L37" t="n">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.2153</v>
+        <v>-1.0641</v>
       </c>
       <c r="N37" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.5614</v>
+        <v>-1.1681</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4937</v>
+        <v>-0.3693</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.066</v>
+        <v>-1.1654</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.5614</v>
+        <v>-1.1681</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.5614</v>
+        <v>-1.1681</v>
       </c>
       <c r="G38" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.5614</v>
+        <v>-1.1681</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.455</v>
+        <v>-1.1681</v>
       </c>
       <c r="J38" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="L38" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.455</v>
+        <v>-1.1681</v>
       </c>
       <c r="N38" t="n">
-        <v>142</v>
+        <v>90</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.6669</v>
+        <v>-1.2052</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.527</v>
+        <v>-0.381</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.108</v>
+        <v>-1.1821</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.6669</v>
+        <v>-1.2052</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.6669</v>
+        <v>-0.9659</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.2393</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.6669</v>
+        <v>-0.9659</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.6669</v>
+        <v>-0.5022</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.2393</v>
       </c>
       <c r="K39" t="n">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.6669</v>
+        <v>-0.7415</v>
       </c>
       <c r="N39" t="n">
-        <v>90</v>
+        <v>140</v>
       </c>
     </row>
     <row r="40">
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.6767</v>
+        <v>-2.3642</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.8463000000000001</v>
+        <v>-0.7475000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.5103</v>
+        <v>-1.7053</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.6767</v>
+        <v>-2.3642</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.9104</v>
+        <v>-0.7387</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.7663</v>
+        <v>-1.6255</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.9104</v>
+        <v>-0.7387</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.7379</v>
+        <v>-0.3841</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.7663</v>
+        <v>-1.6255</v>
       </c>
       <c r="K40" t="n">
         <v>192</v>
@@ -2277,7 +2277,7 @@
         <v>160</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.5042</v>
+        <v>-2.0096</v>
       </c>
       <c r="N40" t="n">
         <v>352</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.599</v>
+        <v>-3.2384</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.1379</v>
+        <v>-1.0239</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.8778</v>
+        <v>-2.1</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.599</v>
+        <v>-3.2384</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.3743</v>
+        <v>-1.9934</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.2247</v>
+        <v>-1.245</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.3743</v>
+        <v>-1.9934</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.9244</v>
+        <v>-1.0365</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.2247</v>
+        <v>-1.245</v>
       </c>
       <c r="K41" t="n">
         <v>192</v>
@@ -2323,7 +2323,7 @@
         <v>160</v>
       </c>
       <c r="M41" t="n">
-        <v>-3.1491</v>
+        <v>-2.2815</v>
       </c>
       <c r="N41" t="n">
         <v>352</v>
@@ -2429,10 +2429,10 @@
         <v>0.86</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1053</v>
+        <v>-0.1122</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.0007</v>
+        <v>-2.1318</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.8</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2015</v>
+        <v>-0.1809</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.8285</v>
+        <v>-3.4371</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.7</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3579</v>
+        <v>-0.2857</v>
       </c>
       <c r="J4" t="n">
-        <v>-6.8001</v>
+        <v>-5.4283</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.49</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7032</v>
+        <v>-0.4797</v>
       </c>
       <c r="J5" t="n">
-        <v>-13.3608</v>
+        <v>-9.1143</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.29</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9578</v>
+        <v>-0.6697</v>
       </c>
       <c r="J6" t="n">
-        <v>-18.1982</v>
+        <v>-12.7243</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.9</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8206</v>
+        <v>1.5491</v>
       </c>
       <c r="J7" t="n">
-        <v>34.5914</v>
+        <v>29.4329</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.75</v>
       </c>
       <c r="I8" t="n">
-        <v>1.557</v>
+        <v>1.3801</v>
       </c>
       <c r="J8" t="n">
-        <v>29.583</v>
+        <v>26.2219</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.34</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6949</v>
+        <v>0.8235</v>
       </c>
       <c r="J9" t="n">
-        <v>13.2031</v>
+        <v>15.6465</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.33</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6733</v>
+        <v>0.8013</v>
       </c>
       <c r="J10" t="n">
-        <v>12.7927</v>
+        <v>15.2247</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.24</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4749</v>
+        <v>0.594</v>
       </c>
       <c r="J11" t="n">
-        <v>9.023099999999999</v>
+        <v>11.286</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.17</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3589</v>
+        <v>0.4008</v>
       </c>
       <c r="J12" t="n">
-        <v>10.767</v>
+        <v>12.024</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.99</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0028</v>
+        <v>-0.0161</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.483</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.93</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.15</v>
+        <v>-0.0948</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.5</v>
+        <v>-2.844</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.92</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1703</v>
+        <v>-0.1061</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.109</v>
+        <v>-3.183</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.72</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4829</v>
+        <v>-0.3108</v>
       </c>
       <c r="J16" t="n">
-        <v>-14.487</v>
+        <v>-9.324</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.42</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1015</v>
+        <v>1.0582</v>
       </c>
       <c r="J17" t="n">
-        <v>33.045</v>
+        <v>31.746</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.14</v>
       </c>
       <c r="I18" t="n">
-        <v>0.43</v>
+        <v>0.4258</v>
       </c>
       <c r="J18" t="n">
-        <v>12.9</v>
+        <v>12.774</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.04</v>
       </c>
       <c r="I19" t="n">
-        <v>0.09030000000000001</v>
+        <v>0.1401</v>
       </c>
       <c r="J19" t="n">
-        <v>2.709</v>
+        <v>4.203</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.01</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0282</v>
+        <v>0.0277</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.846</v>
+        <v>0.831</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.97</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2282</v>
+        <v>-0.1602</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.846</v>
+        <v>-4.806</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>0.86</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0667</v>
+        <v>-0.0827</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.334</v>
+        <v>-1.654</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.8</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.163</v>
+        <v>-0.1551</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.26</v>
+        <v>-3.102</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.48</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.6894</v>
+        <v>-0.4758</v>
       </c>
       <c r="J24" t="n">
-        <v>-13.788</v>
+        <v>-9.516</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.41</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.7887</v>
+        <v>-0.5426</v>
       </c>
       <c r="J25" t="n">
-        <v>-15.774</v>
+        <v>-10.852</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.25</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.9949</v>
+        <v>-0.6987</v>
       </c>
       <c r="J26" t="n">
-        <v>-19.898</v>
+        <v>-13.974</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>2.13</v>
       </c>
       <c r="I27" t="n">
-        <v>2.0716</v>
+        <v>1.7896</v>
       </c>
       <c r="J27" t="n">
-        <v>41.432</v>
+        <v>35.792</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.83</v>
       </c>
       <c r="I28" t="n">
-        <v>1.6766</v>
+        <v>1.4608</v>
       </c>
       <c r="J28" t="n">
-        <v>33.532</v>
+        <v>29.216</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.42</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8433</v>
+        <v>0.9779</v>
       </c>
       <c r="J29" t="n">
-        <v>16.866</v>
+        <v>19.558</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.29</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5693</v>
+        <v>0.6996</v>
       </c>
       <c r="J30" t="n">
-        <v>11.386</v>
+        <v>13.992</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.18</v>
       </c>
       <c r="I31" t="n">
-        <v>0.322</v>
+        <v>0.4354</v>
       </c>
       <c r="J31" t="n">
-        <v>6.44</v>
+        <v>8.708</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.7</v>
       </c>
       <c r="I32" t="n">
-        <v>1.4924</v>
+        <v>1.0597</v>
       </c>
       <c r="J32" t="n">
-        <v>29.848</v>
+        <v>21.194</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.65</v>
       </c>
       <c r="I33" t="n">
-        <v>1.3989</v>
+        <v>1.0015</v>
       </c>
       <c r="J33" t="n">
-        <v>27.978</v>
+        <v>20.03</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.59</v>
       </c>
       <c r="I34" t="n">
-        <v>1.283</v>
+        <v>0.9311</v>
       </c>
       <c r="J34" t="n">
-        <v>25.66</v>
+        <v>18.622</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.34</v>
       </c>
       <c r="I35" t="n">
-        <v>0.7194</v>
+        <v>0.6296</v>
       </c>
       <c r="J35" t="n">
-        <v>14.388</v>
+        <v>12.592</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.96</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3597</v>
+        <v>-0.2726</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.194</v>
+        <v>-5.452</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.19</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4701</v>
+        <v>0.461</v>
       </c>
       <c r="J37" t="n">
-        <v>9.401999999999999</v>
+        <v>9.220000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.79</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2784</v>
+        <v>-0.2183</v>
       </c>
       <c r="J38" t="n">
-        <v>-5.568</v>
+        <v>-4.366</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.7</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4447</v>
+        <v>-0.3023</v>
       </c>
       <c r="J39" t="n">
-        <v>-8.894</v>
+        <v>-6.046</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.59</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.6047</v>
+        <v>-0.4053</v>
       </c>
       <c r="J40" t="n">
-        <v>-12.094</v>
+        <v>-8.106</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.44</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7969000000000001</v>
+        <v>-0.5449000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>-15.938</v>
+        <v>-10.898</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>2.04</v>
       </c>
       <c r="I42" t="n">
-        <v>1.8698</v>
+        <v>1.3976</v>
       </c>
       <c r="J42" t="n">
-        <v>35.5262</v>
+        <v>26.5544</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.84</v>
       </c>
       <c r="I43" t="n">
-        <v>1.6478</v>
+        <v>1.1823</v>
       </c>
       <c r="J43" t="n">
-        <v>31.3082</v>
+        <v>22.4637</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.6</v>
       </c>
       <c r="I44" t="n">
-        <v>1.1625</v>
+        <v>0.9203</v>
       </c>
       <c r="J44" t="n">
-        <v>22.0875</v>
+        <v>17.4857</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.57</v>
       </c>
       <c r="I45" t="n">
-        <v>1.1033</v>
+        <v>0.8859</v>
       </c>
       <c r="J45" t="n">
-        <v>20.9627</v>
+        <v>16.8321</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1.37</v>
       </c>
       <c r="I46" t="n">
-        <v>0.7072000000000001</v>
+        <v>0.6422</v>
       </c>
       <c r="J46" t="n">
-        <v>13.4368</v>
+        <v>12.2018</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>0.72</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.2114</v>
+        <v>-0.1885</v>
       </c>
       <c r="J47" t="n">
-        <v>-4.0166</v>
+        <v>-3.5815</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.47</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.6056</v>
+        <v>-0.4633</v>
       </c>
       <c r="J48" t="n">
-        <v>-11.5064</v>
+        <v>-8.8027</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.46</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.6251</v>
+        <v>-0.4724</v>
       </c>
       <c r="J49" t="n">
-        <v>-11.8769</v>
+        <v>-8.9756</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.35</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.8278</v>
+        <v>-0.5758</v>
       </c>
       <c r="J50" t="n">
-        <v>-15.7282</v>
+        <v>-10.9402</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.24</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.9833</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="J51" t="n">
-        <v>-18.6827</v>
+        <v>-13.091</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.41</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6454</v>
+        <v>0.6017</v>
       </c>
       <c r="J52" t="n">
-        <v>25.816</v>
+        <v>24.068</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.35</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5716</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="J53" t="n">
-        <v>22.864</v>
+        <v>21.712</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.96</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1291</v>
+        <v>-0.067</v>
       </c>
       <c r="J54" t="n">
-        <v>-5.164</v>
+        <v>-2.68</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.74</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4744</v>
+        <v>-0.3022</v>
       </c>
       <c r="J55" t="n">
-        <v>-18.976</v>
+        <v>-12.088</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.73</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4877</v>
+        <v>-0.3118</v>
       </c>
       <c r="J56" t="n">
-        <v>-19.508</v>
+        <v>-12.472</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.53</v>
       </c>
       <c r="I57" t="n">
-        <v>1.3369</v>
+        <v>0.9379</v>
       </c>
       <c r="J57" t="n">
-        <v>53.476</v>
+        <v>37.516</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.24</v>
       </c>
       <c r="I58" t="n">
-        <v>0.7114</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="J58" t="n">
-        <v>28.456</v>
+        <v>21.632</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.98</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1785</v>
+        <v>-0.1166</v>
       </c>
       <c r="J59" t="n">
-        <v>-7.14</v>
+        <v>-4.664</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.88</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.495</v>
+        <v>-0.4321</v>
       </c>
       <c r="J60" t="n">
-        <v>-19.8</v>
+        <v>-17.284</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.83</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6259</v>
+        <v>-0.5688</v>
       </c>
       <c r="J61" t="n">
-        <v>-25.036</v>
+        <v>-22.752</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.91</v>
       </c>
       <c r="I62" t="n">
-        <v>1.0481</v>
+        <v>0.7119</v>
       </c>
       <c r="J62" t="n">
-        <v>22.0101</v>
+        <v>14.9499</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.69</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8222</v>
+        <v>0.5878</v>
       </c>
       <c r="J63" t="n">
-        <v>17.2662</v>
+        <v>12.3438</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.54</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6383</v>
+        <v>0.5023</v>
       </c>
       <c r="J64" t="n">
-        <v>13.4043</v>
+        <v>10.5483</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.42</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4894</v>
+        <v>0.4304</v>
       </c>
       <c r="J65" t="n">
-        <v>10.2774</v>
+        <v>9.038399999999999</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.18</v>
       </c>
       <c r="I66" t="n">
-        <v>0.188</v>
+        <v>0.2211</v>
       </c>
       <c r="J66" t="n">
-        <v>3.948</v>
+        <v>4.6431</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>0.82</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.1741</v>
+        <v>-0.1612</v>
       </c>
       <c r="J67" t="n">
-        <v>-3.6561</v>
+        <v>-3.3852</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.79</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.2215</v>
+        <v>-0.1943</v>
       </c>
       <c r="J68" t="n">
-        <v>-4.6515</v>
+        <v>-4.0803</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.75</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2841</v>
+        <v>-0.2369</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.9661</v>
+        <v>-4.9749</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.42</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.7984</v>
+        <v>-0.5473</v>
       </c>
       <c r="J70" t="n">
-        <v>-16.7664</v>
+        <v>-11.4933</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.4</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.8239</v>
+        <v>-0.5663</v>
       </c>
       <c r="J71" t="n">
-        <v>-17.3019</v>
+        <v>-11.8923</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.31</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5526</v>
+        <v>0.525</v>
       </c>
       <c r="J72" t="n">
-        <v>16.578</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.07</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1968</v>
+        <v>0.198</v>
       </c>
       <c r="J73" t="n">
-        <v>5.904</v>
+        <v>5.94</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.97</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0522</v>
+        <v>-0.0458</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.566</v>
+        <v>-1.374</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.71</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4959</v>
+        <v>-0.3202</v>
       </c>
       <c r="J75" t="n">
-        <v>-14.877</v>
+        <v>-9.606</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.66</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5616</v>
+        <v>-0.3675</v>
       </c>
       <c r="J76" t="n">
-        <v>-16.848</v>
+        <v>-11.025</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.36</v>
       </c>
       <c r="I77" t="n">
-        <v>0.9627</v>
+        <v>0.6988</v>
       </c>
       <c r="J77" t="n">
-        <v>28.881</v>
+        <v>20.964</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.24</v>
       </c>
       <c r="I78" t="n">
-        <v>0.6853</v>
+        <v>0.5323</v>
       </c>
       <c r="J78" t="n">
-        <v>20.559</v>
+        <v>15.969</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.05</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1138</v>
+        <v>0.1681</v>
       </c>
       <c r="J79" t="n">
-        <v>3.414</v>
+        <v>5.043</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.03</v>
       </c>
       <c r="I80" t="n">
-        <v>0.0434</v>
+        <v>0.1005</v>
       </c>
       <c r="J80" t="n">
-        <v>1.302</v>
+        <v>3.015</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.09719999999999999</v>
+        <v>-0.0322</v>
       </c>
       <c r="J81" t="n">
-        <v>-2.916</v>
+        <v>-0.966</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.42</v>
       </c>
       <c r="I82" t="n">
-        <v>0.641</v>
+        <v>0.7852</v>
       </c>
       <c r="J82" t="n">
-        <v>19.23</v>
+        <v>23.556</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.13</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2421</v>
+        <v>0.2863</v>
       </c>
       <c r="J83" t="n">
-        <v>7.263</v>
+        <v>8.589</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.11</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2067</v>
+        <v>0.2483</v>
       </c>
       <c r="J84" t="n">
-        <v>6.201</v>
+        <v>7.449</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.05</v>
       </c>
       <c r="I85" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.1263</v>
       </c>
       <c r="J85" t="n">
-        <v>2.451</v>
+        <v>3.789</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.74</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4832</v>
+        <v>-0.3077</v>
       </c>
       <c r="J86" t="n">
-        <v>-14.496</v>
+        <v>-9.231</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.59</v>
       </c>
       <c r="I87" t="n">
-        <v>1.5074</v>
+        <v>1.3294</v>
       </c>
       <c r="J87" t="n">
-        <v>45.222</v>
+        <v>39.882</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.09</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3691</v>
+        <v>0.3211</v>
       </c>
       <c r="J88" t="n">
-        <v>11.073</v>
+        <v>9.632999999999999</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.6405999999999999</v>
+        <v>-0.5938</v>
       </c>
       <c r="J89" t="n">
-        <v>-19.218</v>
+        <v>-17.814</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.78</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.7155</v>
+        <v>-0.6716</v>
       </c>
       <c r="J90" t="n">
-        <v>-21.465</v>
+        <v>-20.148</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.71</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.8812</v>
+        <v>-0.8479</v>
       </c>
       <c r="J91" t="n">
-        <v>-26.436</v>
+        <v>-25.437</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.24</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4129</v>
+        <v>0.3467</v>
       </c>
       <c r="J92" t="n">
-        <v>14.8644</v>
+        <v>12.4812</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.14</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2631</v>
+        <v>0.2185</v>
       </c>
       <c r="J93" t="n">
-        <v>9.4716</v>
+        <v>7.866</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.08</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1509</v>
+        <v>0.1361</v>
       </c>
       <c r="J94" t="n">
-        <v>5.4324</v>
+        <v>4.8996</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.03</v>
       </c>
       <c r="I95" t="n">
-        <v>0.0434</v>
+        <v>0.0575</v>
       </c>
       <c r="J95" t="n">
-        <v>1.5624</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.91</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2331</v>
+        <v>-0.1318</v>
       </c>
       <c r="J96" t="n">
-        <v>-8.3916</v>
+        <v>-4.7448</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.23</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4275</v>
+        <v>0.3785</v>
       </c>
       <c r="J97" t="n">
-        <v>15.39</v>
+        <v>13.626</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.22</v>
       </c>
       <c r="I98" t="n">
-        <v>0.4135</v>
+        <v>0.3647</v>
       </c>
       <c r="J98" t="n">
-        <v>14.886</v>
+        <v>13.1292</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.19</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3705</v>
+        <v>0.3225</v>
       </c>
       <c r="J99" t="n">
-        <v>13.338</v>
+        <v>11.61</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.78</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4112</v>
+        <v>-0.2584</v>
       </c>
       <c r="J100" t="n">
-        <v>-14.8032</v>
+        <v>-9.3024</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6933</v>
+        <v>-0.4652</v>
       </c>
       <c r="J101" t="n">
-        <v>-24.9588</v>
+        <v>-16.7472</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.32</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5591</v>
+        <v>0.6677</v>
       </c>
       <c r="J102" t="n">
-        <v>15.6548</v>
+        <v>18.6956</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.93</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.1586</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="J103" t="n">
-        <v>-4.4408</v>
+        <v>-2.6936</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.92</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.178</v>
+        <v>-0.1077</v>
       </c>
       <c r="J104" t="n">
-        <v>-4.984</v>
+        <v>-3.0156</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.89</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2321</v>
+        <v>-0.141</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.4988</v>
+        <v>-3.948</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.75</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4454</v>
+        <v>-0.2838</v>
       </c>
       <c r="J106" t="n">
-        <v>-12.4712</v>
+        <v>-7.9464</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.37</v>
       </c>
       <c r="I107" t="n">
-        <v>1.0125</v>
+        <v>0.989</v>
       </c>
       <c r="J107" t="n">
-        <v>28.35</v>
+        <v>27.692</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.26</v>
       </c>
       <c r="I108" t="n">
-        <v>0.7641</v>
+        <v>0.737</v>
       </c>
       <c r="J108" t="n">
-        <v>21.3948</v>
+        <v>20.636</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.23</v>
       </c>
       <c r="I109" t="n">
-        <v>0.6917</v>
+        <v>0.6632</v>
       </c>
       <c r="J109" t="n">
-        <v>19.3676</v>
+        <v>18.5696</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.79</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.7218</v>
+        <v>-0.6713</v>
       </c>
       <c r="J110" t="n">
-        <v>-20.2104</v>
+        <v>-18.7964</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.77</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.7694</v>
+        <v>-0.7225</v>
       </c>
       <c r="J111" t="n">
-        <v>-21.5432</v>
+        <v>-20.23</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.43</v>
       </c>
       <c r="I112" t="n">
-        <v>1.079</v>
+        <v>1.0505</v>
       </c>
       <c r="J112" t="n">
-        <v>28.054</v>
+        <v>27.313</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.35</v>
       </c>
       <c r="I113" t="n">
-        <v>0.9064</v>
+        <v>0.9073</v>
       </c>
       <c r="J113" t="n">
-        <v>23.5664</v>
+        <v>23.5898</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.15</v>
       </c>
       <c r="I114" t="n">
-        <v>0.3779</v>
+        <v>0.4371</v>
       </c>
       <c r="J114" t="n">
-        <v>9.8254</v>
+        <v>11.3646</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.09</v>
       </c>
       <c r="I115" t="n">
-        <v>0.207</v>
+        <v>0.274</v>
       </c>
       <c r="J115" t="n">
-        <v>5.382</v>
+        <v>7.124</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.98</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2236</v>
+        <v>-0.1447</v>
       </c>
       <c r="J116" t="n">
-        <v>-5.8136</v>
+        <v>-3.7622</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.13</v>
       </c>
       <c r="I117" t="n">
-        <v>0.2982</v>
+        <v>0.3233</v>
       </c>
       <c r="J117" t="n">
-        <v>7.7532</v>
+        <v>8.405799999999999</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.12</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2822</v>
+        <v>0.3032</v>
       </c>
       <c r="J118" t="n">
-        <v>7.3372</v>
+        <v>7.8832</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.87</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2595</v>
+        <v>-0.1604</v>
       </c>
       <c r="J119" t="n">
-        <v>-6.747</v>
+        <v>-4.1704</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.85</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2923</v>
+        <v>-0.1814</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.5998</v>
+        <v>-4.7164</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.75</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4412</v>
+        <v>-0.2816</v>
       </c>
       <c r="J121" t="n">
-        <v>-11.4712</v>
+        <v>-7.3216</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.39</v>
       </c>
       <c r="I122" t="n">
-        <v>1.0035</v>
+        <v>0.993</v>
       </c>
       <c r="J122" t="n">
-        <v>27.0945</v>
+        <v>26.811</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.2</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.5627</v>
       </c>
       <c r="J123" t="n">
-        <v>14.8203</v>
+        <v>15.1929</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.16</v>
       </c>
       <c r="I124" t="n">
-        <v>0.4192</v>
+        <v>0.466</v>
       </c>
       <c r="J124" t="n">
-        <v>11.3184</v>
+        <v>12.582</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.09</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2159</v>
+        <v>0.2782</v>
       </c>
       <c r="J125" t="n">
-        <v>5.8293</v>
+        <v>7.5114</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>1.07</v>
       </c>
       <c r="I126" t="n">
-        <v>0.1551</v>
+        <v>0.2193</v>
       </c>
       <c r="J126" t="n">
-        <v>4.1877</v>
+        <v>5.9211</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.58</v>
       </c>
       <c r="I127" t="n">
-        <v>0.8737</v>
+        <v>1.0683</v>
       </c>
       <c r="J127" t="n">
-        <v>23.5899</v>
+        <v>28.8441</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.1263</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="J128" t="n">
-        <v>-3.4101</v>
+        <v>-2.2437</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.79</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.384</v>
+        <v>-0.2423</v>
       </c>
       <c r="J129" t="n">
-        <v>-10.368</v>
+        <v>-6.5421</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.76</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4271</v>
+        <v>-0.2719</v>
       </c>
       <c r="J130" t="n">
-        <v>-11.5317</v>
+        <v>-7.3413</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.65</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5744</v>
+        <v>-0.3768</v>
       </c>
       <c r="J131" t="n">
-        <v>-15.5088</v>
+        <v>-10.1736</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.39</v>
       </c>
       <c r="I132" t="n">
-        <v>0.6473</v>
+        <v>0.7895</v>
       </c>
       <c r="J132" t="n">
-        <v>16.8298</v>
+        <v>20.527</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.24</v>
       </c>
       <c r="I133" t="n">
-        <v>0.4538</v>
+        <v>0.5261</v>
       </c>
       <c r="J133" t="n">
-        <v>11.7988</v>
+        <v>13.6786</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.88</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2484</v>
+        <v>-0.1516</v>
       </c>
       <c r="J134" t="n">
-        <v>-6.4584</v>
+        <v>-3.9416</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.68</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.5387999999999999</v>
+        <v>-0.3505</v>
       </c>
       <c r="J135" t="n">
-        <v>-14.0088</v>
+        <v>-9.113</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.61</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.6274999999999999</v>
+        <v>-0.4158</v>
       </c>
       <c r="J136" t="n">
-        <v>-16.315</v>
+        <v>-10.8108</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.48</v>
       </c>
       <c r="I137" t="n">
-        <v>1.1919</v>
+        <v>1.1207</v>
       </c>
       <c r="J137" t="n">
-        <v>30.9894</v>
+        <v>29.1382</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.35</v>
       </c>
       <c r="I138" t="n">
-        <v>0.9172</v>
+        <v>0.9136</v>
       </c>
       <c r="J138" t="n">
-        <v>23.8472</v>
+        <v>23.7536</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.16</v>
       </c>
       <c r="I139" t="n">
-        <v>0.4209</v>
+        <v>0.4664</v>
       </c>
       <c r="J139" t="n">
-        <v>10.9434</v>
+        <v>12.1264</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.1</v>
       </c>
       <c r="I140" t="n">
-        <v>0.2465</v>
+        <v>0.3072</v>
       </c>
       <c r="J140" t="n">
-        <v>6.409</v>
+        <v>7.9872</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.701</v>
+        <v>-0.6443</v>
       </c>
       <c r="J141" t="n">
-        <v>-18.226</v>
+        <v>-16.7518</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.44</v>
       </c>
       <c r="I142" t="n">
-        <v>0.606</v>
+        <v>0.5425</v>
       </c>
       <c r="J142" t="n">
-        <v>13.332</v>
+        <v>11.935</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.37</v>
       </c>
       <c r="I143" t="n">
-        <v>0.5181</v>
+        <v>0.4663</v>
       </c>
       <c r="J143" t="n">
-        <v>11.3982</v>
+        <v>10.2586</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.33</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4642</v>
+        <v>0.4223</v>
       </c>
       <c r="J144" t="n">
-        <v>10.2124</v>
+        <v>9.2906</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.21</v>
       </c>
       <c r="I145" t="n">
-        <v>0.2794</v>
+        <v>0.2857</v>
       </c>
       <c r="J145" t="n">
-        <v>6.1468</v>
+        <v>6.2854</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.1</v>
       </c>
       <c r="I146" t="n">
-        <v>0.114</v>
+        <v>0.1415</v>
       </c>
       <c r="J146" t="n">
-        <v>2.508</v>
+        <v>3.113</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.44</v>
       </c>
       <c r="I147" t="n">
-        <v>0.7625</v>
+        <v>0.7391</v>
       </c>
       <c r="J147" t="n">
-        <v>16.775</v>
+        <v>16.2602</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.02</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1467</v>
+        <v>0.0914</v>
       </c>
       <c r="J148" t="n">
-        <v>3.2274</v>
+        <v>2.0108</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.74</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.417</v>
+        <v>-0.2748</v>
       </c>
       <c r="J149" t="n">
-        <v>-9.173999999999999</v>
+        <v>-6.0456</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.46</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.7861</v>
+        <v>-0.5364</v>
       </c>
       <c r="J150" t="n">
-        <v>-17.2942</v>
+        <v>-11.8008</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.43</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.8216</v>
+        <v>-0.5637</v>
       </c>
       <c r="J151" t="n">
-        <v>-18.0752</v>
+        <v>-12.4014</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.72</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.289</v>
+        <v>-0.2465</v>
       </c>
       <c r="J152" t="n">
-        <v>-6.069</v>
+        <v>-5.1765</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.68</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.3504</v>
+        <v>-0.2888</v>
       </c>
       <c r="J153" t="n">
-        <v>-7.3584</v>
+        <v>-6.0648</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.5</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.6613</v>
+        <v>-0.4578</v>
       </c>
       <c r="J154" t="n">
-        <v>-13.8873</v>
+        <v>-9.613799999999999</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.47</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.7059</v>
+        <v>-0.4861</v>
       </c>
       <c r="J155" t="n">
-        <v>-14.8239</v>
+        <v>-10.2081</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.45</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.7346</v>
+        <v>-0.5051</v>
       </c>
       <c r="J156" t="n">
-        <v>-15.4266</v>
+        <v>-10.6071</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.59</v>
       </c>
       <c r="I157" t="n">
-        <v>1.2783</v>
+        <v>1.2035</v>
       </c>
       <c r="J157" t="n">
-        <v>26.8443</v>
+        <v>25.2735</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.57</v>
       </c>
       <c r="I158" t="n">
-        <v>1.2384</v>
+        <v>1.1799</v>
       </c>
       <c r="J158" t="n">
-        <v>26.0064</v>
+        <v>24.7779</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.55</v>
       </c>
       <c r="I159" t="n">
-        <v>1.1978</v>
+        <v>1.1564</v>
       </c>
       <c r="J159" t="n">
-        <v>25.1538</v>
+        <v>24.2844</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.46</v>
       </c>
       <c r="I160" t="n">
-        <v>0.9961</v>
+        <v>1.0499</v>
       </c>
       <c r="J160" t="n">
-        <v>20.9181</v>
+        <v>22.0479</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.12</v>
       </c>
       <c r="I161" t="n">
-        <v>0.201</v>
+        <v>0.3002</v>
       </c>
       <c r="J161" t="n">
-        <v>4.221</v>
+        <v>6.3042</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.41</v>
       </c>
       <c r="I162" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.8404</v>
       </c>
       <c r="J162" t="n">
-        <v>18.441</v>
+        <v>22.6908</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.21</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4234</v>
+        <v>0.4836</v>
       </c>
       <c r="J163" t="n">
-        <v>11.4318</v>
+        <v>13.0572</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.91</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1801</v>
+        <v>-0.1156</v>
       </c>
       <c r="J164" t="n">
-        <v>-4.8627</v>
+        <v>-3.1212</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.61</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.622</v>
+        <v>-0.4121</v>
       </c>
       <c r="J165" t="n">
-        <v>-16.794</v>
+        <v>-11.1267</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.5</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.7549</v>
+        <v>-0.5124</v>
       </c>
       <c r="J166" t="n">
-        <v>-20.3823</v>
+        <v>-13.8348</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.37</v>
       </c>
       <c r="I167" t="n">
-        <v>0.9495</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="J167" t="n">
-        <v>25.6365</v>
+        <v>25.6257</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.3</v>
       </c>
       <c r="I168" t="n">
-        <v>0.7907</v>
+        <v>0.793</v>
       </c>
       <c r="J168" t="n">
-        <v>21.3489</v>
+        <v>21.411</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.19</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4904</v>
+        <v>0.5363</v>
       </c>
       <c r="J169" t="n">
-        <v>13.2408</v>
+        <v>14.4801</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.1</v>
       </c>
       <c r="I170" t="n">
-        <v>0.2352</v>
+        <v>0.302</v>
       </c>
       <c r="J170" t="n">
-        <v>6.3504</v>
+        <v>8.154</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.05</v>
       </c>
       <c r="I171" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.1518</v>
       </c>
       <c r="J171" t="n">
-        <v>2.2302</v>
+        <v>4.0986</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.11</v>
       </c>
       <c r="I172" t="n">
-        <v>0.2448</v>
+        <v>0.2666</v>
       </c>
       <c r="J172" t="n">
-        <v>5.8752</v>
+        <v>6.3984</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.06</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1553</v>
+        <v>0.1618</v>
       </c>
       <c r="J173" t="n">
-        <v>3.7272</v>
+        <v>3.8832</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.05</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1354</v>
+        <v>0.1393</v>
       </c>
       <c r="J174" t="n">
-        <v>3.2496</v>
+        <v>3.3432</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.99</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.0404</v>
+        <v>-0.0205</v>
       </c>
       <c r="J175" t="n">
-        <v>-0.9696</v>
+        <v>-0.492</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.79</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3979</v>
+        <v>-0.249</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.5496</v>
+        <v>-5.976</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.5</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2232</v>
+        <v>1.142</v>
       </c>
       <c r="J177" t="n">
-        <v>29.3568</v>
+        <v>27.408</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.45</v>
       </c>
       <c r="I178" t="n">
-        <v>1.1216</v>
+        <v>1.0775</v>
       </c>
       <c r="J178" t="n">
-        <v>26.9184</v>
+        <v>25.86</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.37</v>
       </c>
       <c r="I179" t="n">
-        <v>0.9517</v>
+        <v>0.9503</v>
       </c>
       <c r="J179" t="n">
-        <v>22.8408</v>
+        <v>22.8072</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.85</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.6073</v>
+        <v>-0.5427</v>
       </c>
       <c r="J180" t="n">
-        <v>-14.5752</v>
+        <v>-13.0248</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.82</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6815</v>
+        <v>-0.6226</v>
       </c>
       <c r="J181" t="n">
-        <v>-16.356</v>
+        <v>-14.9424</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.89</v>
       </c>
       <c r="I182" t="n">
-        <v>1.8192</v>
+        <v>1.5462</v>
       </c>
       <c r="J182" t="n">
-        <v>40.0224</v>
+        <v>34.0164</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.76</v>
       </c>
       <c r="I183" t="n">
-        <v>1.5916</v>
+        <v>1.3984</v>
       </c>
       <c r="J183" t="n">
-        <v>35.0152</v>
+        <v>30.7648</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.45</v>
       </c>
       <c r="I184" t="n">
-        <v>0.954</v>
+        <v>1.0362</v>
       </c>
       <c r="J184" t="n">
-        <v>20.988</v>
+        <v>22.7964</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.16</v>
       </c>
       <c r="I185" t="n">
-        <v>0.2981</v>
+        <v>0.4037</v>
       </c>
       <c r="J185" t="n">
-        <v>6.5582</v>
+        <v>8.881399999999999</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.1</v>
       </c>
       <c r="I186" t="n">
-        <v>0.1447</v>
+        <v>0.2416</v>
       </c>
       <c r="J186" t="n">
-        <v>3.1834</v>
+        <v>5.3152</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.11</v>
       </c>
       <c r="I187" t="n">
-        <v>0.3596</v>
+        <v>0.3973</v>
       </c>
       <c r="J187" t="n">
-        <v>7.9112</v>
+        <v>8.740600000000001</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.83</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.199</v>
+        <v>-0.1718</v>
       </c>
       <c r="J188" t="n">
-        <v>-4.378</v>
+        <v>-3.7796</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.57</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.6237</v>
+        <v>-0.4199</v>
       </c>
       <c r="J189" t="n">
-        <v>-13.7214</v>
+        <v>-9.2378</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.55</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.6506999999999999</v>
+        <v>-0.4386</v>
       </c>
       <c r="J190" t="n">
-        <v>-14.3154</v>
+        <v>-9.6492</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.52</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.6903</v>
+        <v>-0.4666</v>
       </c>
       <c r="J191" t="n">
-        <v>-15.1866</v>
+        <v>-10.2652</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.79</v>
       </c>
       <c r="I192" t="n">
-        <v>1.6946</v>
+        <v>1.4581</v>
       </c>
       <c r="J192" t="n">
-        <v>35.5866</v>
+        <v>30.6201</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.56</v>
       </c>
       <c r="I193" t="n">
-        <v>1.2677</v>
+        <v>1.184</v>
       </c>
       <c r="J193" t="n">
-        <v>26.6217</v>
+        <v>24.864</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.22</v>
       </c>
       <c r="I194" t="n">
-        <v>0.4817</v>
+        <v>0.5788</v>
       </c>
       <c r="J194" t="n">
-        <v>10.1157</v>
+        <v>12.1548</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.21</v>
       </c>
       <c r="I195" t="n">
-        <v>0.4575</v>
+        <v>0.5545</v>
       </c>
       <c r="J195" t="n">
-        <v>9.6075</v>
+        <v>11.6445</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.99</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.228</v>
+        <v>-0.1399</v>
       </c>
       <c r="J196" t="n">
-        <v>-4.788</v>
+        <v>-2.9379</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.15</v>
       </c>
       <c r="I197" t="n">
-        <v>0.4199</v>
+        <v>0.4807</v>
       </c>
       <c r="J197" t="n">
-        <v>8.8179</v>
+        <v>10.0947</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.86</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.1527</v>
+        <v>-0.1402</v>
       </c>
       <c r="J198" t="n">
-        <v>-3.2067</v>
+        <v>-2.9442</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.59</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.4022</v>
       </c>
       <c r="J199" t="n">
-        <v>-12.5643</v>
+        <v>-8.446199999999999</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.57</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.6256</v>
+        <v>-0.4209</v>
       </c>
       <c r="J200" t="n">
-        <v>-13.1376</v>
+        <v>-8.838900000000001</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.44</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.793</v>
+        <v>-0.5421</v>
       </c>
       <c r="J201" t="n">
-        <v>-16.653</v>
+        <v>-11.3841</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.63</v>
       </c>
       <c r="I202" t="n">
-        <v>1.4624</v>
+        <v>1.299</v>
       </c>
       <c r="J202" t="n">
-        <v>42.4096</v>
+        <v>37.671</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.43</v>
       </c>
       <c r="I203" t="n">
-        <v>1.0668</v>
+        <v>1.0451</v>
       </c>
       <c r="J203" t="n">
-        <v>30.9372</v>
+        <v>30.3079</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.13</v>
       </c>
       <c r="I204" t="n">
-        <v>0.3091</v>
+        <v>0.3793</v>
       </c>
       <c r="J204" t="n">
-        <v>8.963900000000001</v>
+        <v>10.9997</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.07</v>
       </c>
       <c r="I205" t="n">
-        <v>0.1365</v>
+        <v>0.2091</v>
       </c>
       <c r="J205" t="n">
-        <v>3.9585</v>
+        <v>6.0639</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.86</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5888</v>
+        <v>-0.5218</v>
       </c>
       <c r="J206" t="n">
-        <v>-17.0752</v>
+        <v>-15.1322</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.31</v>
       </c>
       <c r="I207" t="n">
-        <v>0.5512</v>
+        <v>0.6564</v>
       </c>
       <c r="J207" t="n">
-        <v>15.9848</v>
+        <v>19.0356</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.18</v>
       </c>
       <c r="I208" t="n">
-        <v>0.3729</v>
+        <v>0.4192</v>
       </c>
       <c r="J208" t="n">
-        <v>10.8141</v>
+        <v>12.1568</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.91</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1905</v>
+        <v>-0.1175</v>
       </c>
       <c r="J209" t="n">
-        <v>-5.5245</v>
+        <v>-3.4075</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.5233</v>
+        <v>-0.3397</v>
       </c>
       <c r="J210" t="n">
-        <v>-15.1757</v>
+        <v>-9.8513</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.65</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5752</v>
+        <v>-0.3773</v>
       </c>
       <c r="J211" t="n">
-        <v>-16.6808</v>
+        <v>-10.9417</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.25</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7251</v>
+        <v>0.7032</v>
       </c>
       <c r="J212" t="n">
-        <v>21.0279</v>
+        <v>20.3928</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.23</v>
       </c>
       <c r="I213" t="n">
-        <v>0.6762</v>
+        <v>0.6543</v>
       </c>
       <c r="J213" t="n">
-        <v>19.6098</v>
+        <v>18.9747</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.22</v>
       </c>
       <c r="I214" t="n">
-        <v>0.6513</v>
+        <v>0.6297</v>
       </c>
       <c r="J214" t="n">
-        <v>18.8877</v>
+        <v>18.2613</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.97</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2255</v>
+        <v>-0.1586</v>
       </c>
       <c r="J215" t="n">
-        <v>-6.5395</v>
+        <v>-4.5994</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.88</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5016</v>
+        <v>-0.4371</v>
       </c>
       <c r="J216" t="n">
-        <v>-14.5464</v>
+        <v>-12.6759</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.33</v>
       </c>
       <c r="I217" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.6906</v>
       </c>
       <c r="J217" t="n">
-        <v>16.7069</v>
+        <v>20.0274</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.12</v>
       </c>
       <c r="I218" t="n">
-        <v>0.28</v>
+        <v>0.3012</v>
       </c>
       <c r="J218" t="n">
-        <v>8.119999999999999</v>
+        <v>8.7348</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.01</v>
       </c>
       <c r="I219" t="n">
-        <v>0.0663</v>
+        <v>0.047</v>
       </c>
       <c r="J219" t="n">
-        <v>1.9227</v>
+        <v>1.363</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.86</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2781</v>
+        <v>-0.1717</v>
       </c>
       <c r="J220" t="n">
-        <v>-8.0649</v>
+        <v>-4.9793</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.43</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.8379</v>
+        <v>-0.577</v>
       </c>
       <c r="J221" t="n">
-        <v>-24.2991</v>
+        <v>-16.733</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.73</v>
       </c>
       <c r="I222" t="n">
-        <v>1.6231</v>
+        <v>1.4075</v>
       </c>
       <c r="J222" t="n">
-        <v>45.4468</v>
+        <v>39.41</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.35</v>
       </c>
       <c r="I223" t="n">
-        <v>0.865</v>
+        <v>0.8871</v>
       </c>
       <c r="J223" t="n">
-        <v>24.22</v>
+        <v>24.8388</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.34</v>
       </c>
       <c r="I224" t="n">
-        <v>0.8418</v>
+        <v>0.8651</v>
       </c>
       <c r="J224" t="n">
-        <v>23.5704</v>
+        <v>24.2228</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.03</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.0117</v>
+        <v>0.0664</v>
       </c>
       <c r="J225" t="n">
-        <v>-0.3276</v>
+        <v>1.8592</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.92</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4407</v>
+        <v>-0.3623</v>
       </c>
       <c r="J226" t="n">
-        <v>-12.3396</v>
+        <v>-10.1444</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.07</v>
       </c>
       <c r="I227" t="n">
-        <v>0.2123</v>
+        <v>0.2106</v>
       </c>
       <c r="J227" t="n">
-        <v>5.9444</v>
+        <v>5.8968</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.97</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.0325</v>
+        <v>-0.0411</v>
       </c>
       <c r="J228" t="n">
-        <v>-0.91</v>
+        <v>-1.1508</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.89</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2051</v>
+        <v>-0.1351</v>
       </c>
       <c r="J229" t="n">
-        <v>-5.7428</v>
+        <v>-3.7828</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3417</v>
+        <v>-0.2174</v>
       </c>
       <c r="J230" t="n">
-        <v>-9.567600000000001</v>
+        <v>-6.0872</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.78</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3872</v>
+        <v>-0.2472</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.8416</v>
+        <v>-6.9216</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>2.16</v>
       </c>
       <c r="I232" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J232" t="n">
-        <v>43.2453</v>
+        <v>38.5098</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.65</v>
       </c>
       <c r="I233" t="n">
-        <v>1.4129</v>
+        <v>1.2806</v>
       </c>
       <c r="J233" t="n">
-        <v>29.6709</v>
+        <v>26.8926</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.16</v>
       </c>
       <c r="I234" t="n">
-        <v>0.3139</v>
+        <v>0.4154</v>
       </c>
       <c r="J234" t="n">
-        <v>6.5919</v>
+        <v>8.7234</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.06</v>
       </c>
       <c r="I235" t="n">
-        <v>0.0453</v>
+        <v>0.1344</v>
       </c>
       <c r="J235" t="n">
-        <v>0.9513</v>
+        <v>2.8224</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>1.05</v>
       </c>
       <c r="I236" t="n">
-        <v>0.0146</v>
+        <v>0.1025</v>
       </c>
       <c r="J236" t="n">
-        <v>0.3066</v>
+        <v>2.1525</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>0.82</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.1773</v>
+        <v>-0.1631</v>
       </c>
       <c r="J237" t="n">
-        <v>-3.7233</v>
+        <v>-3.4251</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.79</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.2247</v>
+        <v>-0.1961</v>
       </c>
       <c r="J238" t="n">
-        <v>-4.7187</v>
+        <v>-4.1181</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.55</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.6244</v>
+        <v>-0.4259</v>
       </c>
       <c r="J239" t="n">
-        <v>-13.1124</v>
+        <v>-8.943899999999999</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.53</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.6529</v>
+        <v>-0.4446</v>
       </c>
       <c r="J240" t="n">
-        <v>-13.7109</v>
+        <v>-9.336600000000001</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.52</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.6669</v>
+        <v>-0.454</v>
       </c>
       <c r="J241" t="n">
-        <v>-14.0049</v>
+        <v>-9.534000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2636/event_2636_evp_summary.xlsx
+++ b/database/event/2636/event_2636_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.223699999999999</v>
+        <v>9.618600000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>2.9163</v>
+        <v>3.0411</v>
       </c>
       <c r="D2" t="n">
-        <v>3.526</v>
+        <v>3.7544</v>
       </c>
       <c r="E2" t="n">
-        <v>9.223699999999999</v>
+        <v>9.618600000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0916</v>
+        <v>3.0586</v>
       </c>
       <c r="G2" t="n">
-        <v>6.1321</v>
+        <v>6.56</v>
       </c>
       <c r="H2" t="n">
-        <v>5.4066</v>
+        <v>5.1973</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8112</v>
+        <v>2.8065</v>
       </c>
       <c r="J2" t="n">
-        <v>6.1321</v>
+        <v>6.56</v>
       </c>
       <c r="K2" t="n">
         <v>43</v>
@@ -529,7 +529,7 @@
         <v>108</v>
       </c>
       <c r="M2" t="n">
-        <v>8.943300000000001</v>
+        <v>9.3665</v>
       </c>
       <c r="N2" t="n">
         <v>151</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.9339</v>
+        <v>8.3057</v>
       </c>
       <c r="C3" t="n">
-        <v>2.5085</v>
+        <v>2.626</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9437</v>
+        <v>3.1567</v>
       </c>
       <c r="E3" t="n">
-        <v>7.9339</v>
+        <v>8.3057</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2485</v>
+        <v>3.3139</v>
       </c>
       <c r="G3" t="n">
-        <v>4.6854</v>
+        <v>4.9919</v>
       </c>
       <c r="H3" t="n">
-        <v>5.9595</v>
+        <v>6.0395</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0987</v>
+        <v>3.2613</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6854</v>
+        <v>4.9919</v>
       </c>
       <c r="K3" t="n">
         <v>43</v>
@@ -575,7 +575,7 @@
         <v>108</v>
       </c>
       <c r="M3" t="n">
-        <v>7.7841</v>
+        <v>8.2532</v>
       </c>
       <c r="N3" t="n">
         <v>151</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.2087</v>
+        <v>5.43</v>
       </c>
       <c r="C4" t="n">
-        <v>1.6468</v>
+        <v>1.7168</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7135</v>
+        <v>1.8476</v>
       </c>
       <c r="E4" t="n">
-        <v>5.2087</v>
+        <v>5.43</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2636</v>
+        <v>1.2811</v>
       </c>
       <c r="G4" t="n">
-        <v>3.9451</v>
+        <v>4.1488</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2636</v>
+        <v>1.2811</v>
       </c>
       <c r="I4" t="n">
-        <v>0.657</v>
+        <v>0.6918</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9451</v>
+        <v>4.1488</v>
       </c>
       <c r="K4" t="n">
         <v>43</v>
@@ -621,7 +621,7 @@
         <v>108</v>
       </c>
       <c r="M4" t="n">
-        <v>4.6021</v>
+        <v>4.840599999999999</v>
       </c>
       <c r="N4" t="n">
         <v>151</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.1805</v>
+        <v>5.2674</v>
       </c>
       <c r="C5" t="n">
-        <v>1.6379</v>
+        <v>1.6654</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7007</v>
+        <v>1.7736</v>
       </c>
       <c r="E5" t="n">
-        <v>5.1805</v>
+        <v>5.2674</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1961</v>
+        <v>2.1338</v>
       </c>
       <c r="G5" t="n">
-        <v>2.9844</v>
+        <v>3.1336</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2514</v>
+        <v>2.146</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1706</v>
+        <v>1.1588</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9844</v>
+        <v>3.1336</v>
       </c>
       <c r="K5" t="n">
         <v>43</v>
@@ -667,7 +667,7 @@
         <v>108</v>
       </c>
       <c r="M5" t="n">
-        <v>4.155</v>
+        <v>4.2924</v>
       </c>
       <c r="N5" t="n">
         <v>151</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.593</v>
+        <v>4.5304</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4522</v>
+        <v>1.4324</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4355</v>
+        <v>1.4381</v>
       </c>
       <c r="E6" t="n">
-        <v>4.593</v>
+        <v>4.5304</v>
       </c>
       <c r="F6" t="n">
-        <v>4.4518</v>
+        <v>4.4211</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1412</v>
+        <v>0.1093</v>
       </c>
       <c r="H6" t="n">
-        <v>10.3811</v>
+        <v>9.6927</v>
       </c>
       <c r="I6" t="n">
-        <v>5.3977</v>
+        <v>5.234</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1412</v>
+        <v>0.1093</v>
       </c>
       <c r="K6" t="n">
         <v>192</v>
@@ -713,7 +713,7 @@
         <v>160</v>
       </c>
       <c r="M6" t="n">
-        <v>5.5389</v>
+        <v>5.3433</v>
       </c>
       <c r="N6" t="n">
         <v>352</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.2393</v>
+        <v>4.3536</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3403</v>
+        <v>1.3765</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2758</v>
+        <v>1.3576</v>
       </c>
       <c r="E7" t="n">
-        <v>4.2393</v>
+        <v>4.3536</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9715</v>
+        <v>2.9128</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2678</v>
+        <v>1.4408</v>
       </c>
       <c r="H7" t="n">
-        <v>4.9833</v>
+        <v>4.7162</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5911</v>
+        <v>2.5467</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2678</v>
+        <v>1.4408</v>
       </c>
       <c r="K7" t="n">
         <v>49</v>
@@ -759,7 +759,7 @@
         <v>91</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8589</v>
+        <v>3.9875</v>
       </c>
       <c r="N7" t="n">
         <v>140</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.8815</v>
+        <v>3.9522</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2272</v>
+        <v>1.2496</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1143</v>
+        <v>1.1749</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8815</v>
+        <v>3.9522</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8357</v>
+        <v>2.7666</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0458</v>
+        <v>1.1856</v>
       </c>
       <c r="H8" t="n">
-        <v>4.505</v>
+        <v>4.2338</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3424</v>
+        <v>2.2862</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0458</v>
+        <v>1.1856</v>
       </c>
       <c r="K8" t="n">
         <v>49</v>
@@ -805,7 +805,7 @@
         <v>91</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3882</v>
+        <v>3.4718</v>
       </c>
       <c r="N8" t="n">
         <v>140</v>
@@ -814,93 +814,93 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5884</v>
+        <v>3.7497</v>
       </c>
       <c r="C9" t="n">
-        <v>1.1345</v>
+        <v>1.1855</v>
       </c>
       <c r="D9" t="n">
-        <v>0.982</v>
+        <v>1.0827</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5884</v>
+        <v>3.7497</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3453</v>
+        <v>1.0196</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2431</v>
+        <v>2.7301</v>
       </c>
       <c r="H9" t="n">
-        <v>2.777</v>
+        <v>1.0196</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4439</v>
+        <v>0.5506</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2431</v>
+        <v>2.7301</v>
       </c>
       <c r="K9" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="L9" t="n">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="M9" t="n">
-        <v>2.687</v>
+        <v>3.2807</v>
       </c>
       <c r="N9" t="n">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.43</v>
+        <v>3.6495</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0845</v>
+        <v>1.1539</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9105</v>
+        <v>1.0371</v>
       </c>
       <c r="E10" t="n">
-        <v>3.43</v>
+        <v>3.6495</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9735</v>
+        <v>2.2622</v>
       </c>
       <c r="G10" t="n">
-        <v>2.4565</v>
+        <v>1.3873</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9735</v>
+        <v>2.5695</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5062</v>
+        <v>1.3875</v>
       </c>
       <c r="J10" t="n">
-        <v>2.4565</v>
+        <v>1.3873</v>
       </c>
       <c r="K10" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L10" t="n">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9627</v>
+        <v>2.7748</v>
       </c>
       <c r="N10" t="n">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.344</v>
+        <v>2.997</v>
       </c>
       <c r="C11" t="n">
-        <v>1.0573</v>
+        <v>0.9476</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8716</v>
+        <v>0.7401</v>
       </c>
       <c r="E11" t="n">
-        <v>3.344</v>
+        <v>2.997</v>
       </c>
       <c r="F11" t="n">
-        <v>3.344</v>
+        <v>2.997</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.983</v>
+        <v>3.8345</v>
       </c>
       <c r="I11" t="n">
-        <v>3.983</v>
+        <v>3.8345</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.983</v>
+        <v>3.8345</v>
       </c>
       <c r="N11" t="n">
         <v>133</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0518</v>
+        <v>2.967</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9649</v>
+        <v>0.9381</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7397</v>
+        <v>0.7264</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0518</v>
+        <v>2.967</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8797</v>
+        <v>2.7961</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1721</v>
+        <v>0.1709</v>
       </c>
       <c r="H12" t="n">
-        <v>4.6598</v>
+        <v>4.3312</v>
       </c>
       <c r="I12" t="n">
-        <v>2.4229</v>
+        <v>2.3388</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1721</v>
+        <v>0.1709</v>
       </c>
       <c r="K12" t="n">
         <v>192</v>
@@ -989,7 +989,7 @@
         <v>160</v>
       </c>
       <c r="M12" t="n">
-        <v>2.595</v>
+        <v>2.5097</v>
       </c>
       <c r="N12" t="n">
         <v>352</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.681</v>
+        <v>2.6059</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8477</v>
+        <v>0.8239</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5723</v>
+        <v>0.5621</v>
       </c>
       <c r="E13" t="n">
-        <v>2.681</v>
+        <v>2.6059</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6833</v>
+        <v>2.5963</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0023</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>3.9679</v>
+        <v>3.6721</v>
       </c>
       <c r="I13" t="n">
-        <v>2.0631</v>
+        <v>1.9829</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.0023</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="K13" t="n">
         <v>103</v>
@@ -1035,7 +1035,7 @@
         <v>39</v>
       </c>
       <c r="M13" t="n">
-        <v>2.0608</v>
+        <v>1.9925</v>
       </c>
       <c r="N13" t="n">
         <v>142</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.9724</v>
+        <v>1.8237</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6236</v>
+        <v>0.5766</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2524</v>
+        <v>0.206</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9724</v>
+        <v>1.8237</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3792</v>
+        <v>2.2907</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4068</v>
+        <v>-0.467</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8966</v>
+        <v>2.6636</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5061</v>
+        <v>1.4383</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.4068</v>
+        <v>-0.467</v>
       </c>
       <c r="K14" t="n">
         <v>103</v>
@@ -1081,7 +1081,7 @@
         <v>39</v>
       </c>
       <c r="M14" t="n">
-        <v>1.0993</v>
+        <v>0.9712999999999998</v>
       </c>
       <c r="N14" t="n">
         <v>142</v>
@@ -1090,139 +1090,139 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.7866</v>
+        <v>1.7434</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5649</v>
+        <v>0.5512</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1685</v>
+        <v>0.1694</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7866</v>
+        <v>1.7434</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7866</v>
+        <v>2.1751</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0.4317</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7866</v>
+        <v>2.2823</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7866</v>
+        <v>1.2324</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.4317</v>
       </c>
       <c r="K15" t="n">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="M15" t="n">
-        <v>1.7866</v>
+        <v>0.8007</v>
       </c>
       <c r="N15" t="n">
-        <v>145</v>
+        <v>352</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.7617</v>
+        <v>1.6956</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5361</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1573</v>
+        <v>0.1477</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7617</v>
+        <v>1.6956</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7617</v>
+        <v>1.6956</v>
       </c>
       <c r="G16" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>4.2442</v>
+        <v>1.6956</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2068</v>
+        <v>1.6956</v>
       </c>
       <c r="J16" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="L16" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2068</v>
+        <v>1.6956</v>
       </c>
       <c r="N16" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.7246</v>
+        <v>1.6767</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5453</v>
+        <v>0.5301</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1406</v>
+        <v>0.1391</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7246</v>
+        <v>1.6767</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2525</v>
+        <v>2.6767</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5279</v>
+        <v>-1</v>
       </c>
       <c r="H17" t="n">
-        <v>2.45</v>
+        <v>3.9371</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2739</v>
+        <v>2.126</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5279</v>
+        <v>-1</v>
       </c>
       <c r="K17" t="n">
-        <v>192</v>
+        <v>103</v>
       </c>
       <c r="L17" t="n">
-        <v>160</v>
+        <v>39</v>
       </c>
       <c r="M17" t="n">
-        <v>0.746</v>
+        <v>1.126</v>
       </c>
       <c r="N17" t="n">
-        <v>352</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18">
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.3356</v>
+        <v>1.2939</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4223</v>
+        <v>0.4091</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0351</v>
+        <v>-0.0352</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3356</v>
+        <v>1.2939</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3356</v>
+        <v>1.2939</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3356</v>
+        <v>1.2939</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3356</v>
+        <v>1.2939</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3356</v>
+        <v>1.2939</v>
       </c>
       <c r="N18" t="n">
         <v>145</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3068</v>
+        <v>1.2236</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4132</v>
+        <v>0.3869</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0481</v>
+        <v>-0.0672</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3068</v>
+        <v>1.2236</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3068</v>
+        <v>1.2236</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3068</v>
+        <v>1.2236</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3068</v>
+        <v>1.2236</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3068</v>
+        <v>1.2236</v>
       </c>
       <c r="N19" t="n">
         <v>133</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.2632</v>
+        <v>1.1191</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3994</v>
+        <v>0.3538</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0677</v>
+        <v>-0.1148</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2632</v>
+        <v>1.1191</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2632</v>
+        <v>1.1191</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2632</v>
+        <v>1.1191</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2632</v>
+        <v>1.1191</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2632</v>
+        <v>1.1191</v>
       </c>
       <c r="N20" t="n">
         <v>133</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8895999999999999</v>
+        <v>0.8312</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2813</v>
+        <v>0.2628</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2364</v>
+        <v>-0.2458</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8895999999999999</v>
+        <v>0.8312</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8895999999999999</v>
+        <v>0.8312</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8895999999999999</v>
+        <v>0.8312</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8895999999999999</v>
+        <v>0.8312</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8895999999999999</v>
+        <v>0.8312</v>
       </c>
       <c r="N21" t="n">
         <v>79</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7832</v>
+        <v>0.7729</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2476</v>
+        <v>0.2444</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2844</v>
+        <v>-0.2724</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7832</v>
+        <v>0.7729</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1941</v>
+        <v>1.1817</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4109</v>
+        <v>-0.4088</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1941</v>
+        <v>1.1817</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6209</v>
+        <v>0.6381</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4109</v>
+        <v>-0.4088</v>
       </c>
       <c r="K22" t="n">
         <v>49</v>
@@ -1449,7 +1449,7 @@
         <v>91</v>
       </c>
       <c r="M22" t="n">
-        <v>0.21</v>
+        <v>0.2293</v>
       </c>
       <c r="N22" t="n">
         <v>140</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7269</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2298</v>
+        <v>0.206</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3099</v>
+        <v>-0.3275</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7269</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7269</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7269</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7269</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7269</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="N23" t="n">
         <v>90</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5018</v>
+        <v>0.3417</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1587</v>
+        <v>0.108</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4115</v>
+        <v>-0.4687</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5018</v>
+        <v>0.3417</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3799</v>
+        <v>1.25</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.8781</v>
+        <v>-0.9083</v>
       </c>
       <c r="H24" t="n">
-        <v>1.3799</v>
+        <v>1.25</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7175</v>
+        <v>0.675</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.8781</v>
+        <v>-0.9083</v>
       </c>
       <c r="K24" t="n">
         <v>103</v>
@@ -1541,7 +1541,7 @@
         <v>39</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1606</v>
+        <v>-0.2333</v>
       </c>
       <c r="N24" t="n">
         <v>142</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1935</v>
+        <v>0.1565</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0612</v>
+        <v>0.0495</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5507</v>
+        <v>-0.553</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1935</v>
+        <v>0.1565</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1935</v>
+        <v>0.1565</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1935</v>
+        <v>0.1565</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1935</v>
+        <v>0.1565</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1935</v>
+        <v>0.1565</v>
       </c>
       <c r="N25" t="n">
         <v>79</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1394</v>
+        <v>0.1</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0441</v>
+        <v>0.0316</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5750999999999999</v>
+        <v>-0.5787</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1394</v>
+        <v>0.1</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1394</v>
+        <v>0.1</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1394</v>
+        <v>0.1</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1394</v>
+        <v>0.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1394</v>
+        <v>0.1</v>
       </c>
       <c r="N26" t="n">
         <v>90</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0745</v>
+        <v>0.0563</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0236</v>
+        <v>0.0178</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6044</v>
+        <v>-0.5986</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0745</v>
+        <v>0.0563</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0745</v>
+        <v>0.0563</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0745</v>
+        <v>0.0563</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0745</v>
+        <v>0.0563</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0745</v>
+        <v>0.0563</v>
       </c>
       <c r="N27" t="n">
         <v>79</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.2769</v>
+        <v>-0.2671</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.0844</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.763</v>
+        <v>-0.7458</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2769</v>
+        <v>-0.2671</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.2769</v>
+        <v>-0.2671</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.2769</v>
+        <v>-0.2671</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2769</v>
+        <v>-0.2671</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.2769</v>
+        <v>-0.2671</v>
       </c>
       <c r="N28" t="n">
         <v>145</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.309</v>
+        <v>-0.3067</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0977</v>
+        <v>-0.097</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7775</v>
+        <v>-0.7638</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.309</v>
+        <v>-0.3067</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.309</v>
+        <v>-0.3067</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.309</v>
+        <v>-0.3067</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.309</v>
+        <v>-0.3067</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.309</v>
+        <v>-0.3067</v>
       </c>
       <c r="N29" t="n">
         <v>145</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3854</v>
+        <v>-0.4025</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1219</v>
+        <v>-0.1273</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.8120000000000001</v>
+        <v>-0.8074</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.3854</v>
+        <v>-0.4025</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.3854</v>
+        <v>-0.4025</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.3854</v>
+        <v>-0.4025</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3854</v>
+        <v>-0.4025</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3854</v>
+        <v>-0.4025</v>
       </c>
       <c r="N30" t="n">
         <v>79</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.44</v>
+        <v>-0.5239</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1391</v>
+        <v>-0.1656</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8367</v>
+        <v>-0.8627</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.44</v>
+        <v>-0.5239</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.44</v>
+        <v>-0.5239</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.44</v>
+        <v>-0.5239</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.44</v>
+        <v>-0.5239</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.44</v>
+        <v>-0.5239</v>
       </c>
       <c r="N31" t="n">
         <v>145</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5225</v>
+        <v>-0.5633</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1652</v>
+        <v>-0.1781</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8739</v>
+        <v>-0.8806</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5225</v>
+        <v>-0.5633</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.5225</v>
+        <v>-0.5633</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5225</v>
+        <v>-0.5633</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5225</v>
+        <v>-0.5633</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5225</v>
+        <v>-0.5633</v>
       </c>
       <c r="N32" t="n">
         <v>90</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5877</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1858</v>
+        <v>-0.1962</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9033</v>
+        <v>-0.9067</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5877</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5877</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5877</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5877</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5877</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="N33" t="n">
         <v>90</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6203</v>
+        <v>-0.6324</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1961</v>
+        <v>-0.1999</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.918</v>
+        <v>-0.9121</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6203</v>
+        <v>-0.6324</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6203</v>
+        <v>-0.6324</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6203</v>
+        <v>-0.6324</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6203</v>
+        <v>-0.6324</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6203</v>
+        <v>-0.6324</v>
       </c>
       <c r="N34" t="n">
         <v>79</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6611</v>
+        <v>-0.6776</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.209</v>
+        <v>-0.2142</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9365</v>
+        <v>-0.9327</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6611</v>
+        <v>-0.6776</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6611</v>
+        <v>-0.6776</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6611</v>
+        <v>-0.6776</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6611</v>
+        <v>-0.6776</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6611</v>
+        <v>-0.6776</v>
       </c>
       <c r="N35" t="n">
         <v>133</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8168</v>
+        <v>-0.7811</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2582</v>
+        <v>-0.247</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0068</v>
+        <v>-0.9798</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8168</v>
+        <v>-0.7811</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.8168</v>
+        <v>-0.7811</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8168</v>
+        <v>-0.7811</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8168</v>
+        <v>-0.7811</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8168</v>
+        <v>-0.7811</v>
       </c>
       <c r="N36" t="n">
         <v>133</v>
@@ -2102,139 +2102,139 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.1233</v>
+        <v>-1.0448</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3552</v>
+        <v>-0.3303</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1451</v>
+        <v>-1.0998</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.1233</v>
+        <v>-1.0448</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.1233</v>
+        <v>-0.8463000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>-1</v>
+        <v>-0.1985</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.1233</v>
+        <v>-0.8463000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.0641</v>
+        <v>-0.457</v>
       </c>
       <c r="J37" t="n">
-        <v>-1</v>
+        <v>-0.1985</v>
       </c>
       <c r="K37" t="n">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="L37" t="n">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.0641</v>
+        <v>-0.6555</v>
       </c>
       <c r="N37" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.1681</v>
+        <v>-1.1022</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3693</v>
+        <v>-0.3485</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1654</v>
+        <v>-1.1259</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.1681</v>
+        <v>-1.1022</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.1681</v>
+        <v>-0.1022</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.1681</v>
+        <v>-0.1022</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.1681</v>
+        <v>-0.0552</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K38" t="n">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.1681</v>
+        <v>-1.0552</v>
       </c>
       <c r="N38" t="n">
-        <v>90</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2052</v>
+        <v>-1.1874</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.381</v>
+        <v>-0.3754</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1821</v>
+        <v>-1.1647</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2052</v>
+        <v>-1.1874</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.9659</v>
+        <v>-1.1874</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.2393</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9659</v>
+        <v>-1.1874</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.5022</v>
+        <v>-1.1874</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.2393</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="L39" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.7415</v>
+        <v>-1.1874</v>
       </c>
       <c r="N39" t="n">
-        <v>140</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40">
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.3642</v>
+        <v>-2.181</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.7475000000000001</v>
+        <v>-0.6896</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.7053</v>
+        <v>-1.617</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.3642</v>
+        <v>-2.181</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.7387</v>
+        <v>-0.5587</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.6255</v>
+        <v>-1.6223</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.7387</v>
+        <v>-0.5587</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3841</v>
+        <v>-0.3017</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.6255</v>
+        <v>-1.6223</v>
       </c>
       <c r="K40" t="n">
         <v>192</v>
@@ -2277,7 +2277,7 @@
         <v>160</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.0096</v>
+        <v>-1.924</v>
       </c>
       <c r="N40" t="n">
         <v>352</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.2384</v>
+        <v>-3.1615</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.0239</v>
+        <v>-0.9996</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.1</v>
+        <v>-2.0634</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.2384</v>
+        <v>-3.1615</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.9934</v>
+        <v>-1.9528</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.245</v>
+        <v>-1.2087</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.9934</v>
+        <v>-1.9528</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.0365</v>
+        <v>-1.0545</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.245</v>
+        <v>-1.2087</v>
       </c>
       <c r="K41" t="n">
         <v>192</v>
@@ -2323,7 +2323,7 @@
         <v>160</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.2815</v>
+        <v>-2.2632</v>
       </c>
       <c r="N41" t="n">
         <v>352</v>
@@ -2429,10 +2429,10 @@
         <v>0.86</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1122</v>
+        <v>-0.1402</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.1318</v>
+        <v>-2.6638</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.8</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1809</v>
+        <v>-0.2074</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.4371</v>
+        <v>-3.9406</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.7</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2857</v>
+        <v>-0.3085</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.4283</v>
+        <v>-5.8615</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.49</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4797</v>
+        <v>-0.493</v>
       </c>
       <c r="J5" t="n">
-        <v>-9.1143</v>
+        <v>-9.367000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.29</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6697</v>
+        <v>-0.6685</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.7243</v>
+        <v>-12.7015</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.9</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5491</v>
+        <v>1.6893</v>
       </c>
       <c r="J7" t="n">
-        <v>29.4329</v>
+        <v>32.0967</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.75</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3801</v>
+        <v>1.4946</v>
       </c>
       <c r="J8" t="n">
-        <v>26.2219</v>
+        <v>28.3974</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.34</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8235</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>15.6465</v>
+        <v>15.0252</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.33</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8013</v>
+        <v>0.7713</v>
       </c>
       <c r="J10" t="n">
-        <v>15.2247</v>
+        <v>14.6547</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.24</v>
       </c>
       <c r="I11" t="n">
-        <v>0.594</v>
+        <v>0.5881</v>
       </c>
       <c r="J11" t="n">
-        <v>11.286</v>
+        <v>11.1739</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.17</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4008</v>
+        <v>0.3949</v>
       </c>
       <c r="J12" t="n">
-        <v>12.024</v>
+        <v>11.847</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.99</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0161</v>
+        <v>-0.0219</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.483</v>
+        <v>-0.657</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.93</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0948</v>
+        <v>-0.1075</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.844</v>
+        <v>-3.225</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.92</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1061</v>
+        <v>-0.1194</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.183</v>
+        <v>-3.582</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.72</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3108</v>
+        <v>-0.3242</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.324</v>
+        <v>-9.726000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.42</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0582</v>
+        <v>1.0131</v>
       </c>
       <c r="J17" t="n">
-        <v>31.746</v>
+        <v>30.393</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.14</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4258</v>
+        <v>0.4199</v>
       </c>
       <c r="J18" t="n">
-        <v>12.774</v>
+        <v>12.597</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.04</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1401</v>
+        <v>0.1523</v>
       </c>
       <c r="J19" t="n">
-        <v>4.203</v>
+        <v>4.569</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.01</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0277</v>
+        <v>0.0412</v>
       </c>
       <c r="J20" t="n">
-        <v>0.831</v>
+        <v>1.236</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.97</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1602</v>
+        <v>-0.1563</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.806</v>
+        <v>-4.689</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>0.86</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0827</v>
+        <v>-0.1169</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.654</v>
+        <v>-2.338</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.8</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1551</v>
+        <v>-0.1871</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.102</v>
+        <v>-3.742</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.48</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4758</v>
+        <v>-0.4914</v>
       </c>
       <c r="J24" t="n">
-        <v>-9.516</v>
+        <v>-9.827999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.41</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5426</v>
+        <v>-0.5533</v>
       </c>
       <c r="J25" t="n">
-        <v>-10.852</v>
+        <v>-11.066</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.25</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6987</v>
+        <v>-0.6961000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.974</v>
+        <v>-13.922</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>2.13</v>
       </c>
       <c r="I27" t="n">
-        <v>1.7896</v>
+        <v>1.8453</v>
       </c>
       <c r="J27" t="n">
-        <v>35.792</v>
+        <v>36.906</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.83</v>
       </c>
       <c r="I28" t="n">
-        <v>1.4608</v>
+        <v>1.5953</v>
       </c>
       <c r="J28" t="n">
-        <v>29.216</v>
+        <v>31.906</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.42</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9779</v>
+        <v>0.9342</v>
       </c>
       <c r="J29" t="n">
-        <v>19.558</v>
+        <v>18.684</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.29</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6996</v>
+        <v>0.6838</v>
       </c>
       <c r="J30" t="n">
-        <v>13.992</v>
+        <v>13.676</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.18</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4354</v>
+        <v>0.4484</v>
       </c>
       <c r="J31" t="n">
-        <v>8.708</v>
+        <v>8.968</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.7</v>
       </c>
       <c r="I32" t="n">
-        <v>1.0597</v>
+        <v>1.1718</v>
       </c>
       <c r="J32" t="n">
-        <v>21.194</v>
+        <v>23.436</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.65</v>
       </c>
       <c r="I33" t="n">
-        <v>1.0015</v>
+        <v>1.1097</v>
       </c>
       <c r="J33" t="n">
-        <v>20.03</v>
+        <v>22.194</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.59</v>
       </c>
       <c r="I34" t="n">
-        <v>0.9311</v>
+        <v>1.0343</v>
       </c>
       <c r="J34" t="n">
-        <v>18.622</v>
+        <v>20.686</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.34</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6296</v>
+        <v>0.7054</v>
       </c>
       <c r="J35" t="n">
-        <v>12.592</v>
+        <v>14.108</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.96</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2726</v>
+        <v>-0.2444</v>
       </c>
       <c r="J36" t="n">
-        <v>-5.452</v>
+        <v>-4.888</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.19</v>
       </c>
       <c r="I37" t="n">
-        <v>0.461</v>
+        <v>0.4929</v>
       </c>
       <c r="J37" t="n">
-        <v>9.220000000000001</v>
+        <v>9.858000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.79</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2183</v>
+        <v>-0.2386</v>
       </c>
       <c r="J38" t="n">
-        <v>-4.366</v>
+        <v>-4.772</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.7</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3023</v>
+        <v>-0.3212</v>
       </c>
       <c r="J39" t="n">
-        <v>-6.046</v>
+        <v>-6.424</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.59</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4053</v>
+        <v>-0.42</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.106</v>
+        <v>-8.4</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.44</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5449000000000001</v>
+        <v>-0.5512</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.898</v>
+        <v>-11.024</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>2.04</v>
       </c>
       <c r="I42" t="n">
-        <v>1.3976</v>
+        <v>1.5354</v>
       </c>
       <c r="J42" t="n">
-        <v>26.5544</v>
+        <v>29.1726</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.84</v>
       </c>
       <c r="I43" t="n">
-        <v>1.1823</v>
+        <v>1.3085</v>
       </c>
       <c r="J43" t="n">
-        <v>22.4637</v>
+        <v>24.8615</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.6</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9203</v>
+        <v>1.0275</v>
       </c>
       <c r="J44" t="n">
-        <v>17.4857</v>
+        <v>19.5225</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.57</v>
       </c>
       <c r="I45" t="n">
-        <v>0.8859</v>
+        <v>0.9903</v>
       </c>
       <c r="J45" t="n">
-        <v>16.8321</v>
+        <v>18.8157</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1.37</v>
       </c>
       <c r="I46" t="n">
-        <v>0.6422</v>
+        <v>0.7251</v>
       </c>
       <c r="J46" t="n">
-        <v>12.2018</v>
+        <v>13.7769</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>0.72</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.1885</v>
+        <v>-0.2284</v>
       </c>
       <c r="J47" t="n">
-        <v>-3.5815</v>
+        <v>-4.3396</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.47</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.4633</v>
+        <v>-0.4833</v>
       </c>
       <c r="J48" t="n">
-        <v>-8.8027</v>
+        <v>-9.182700000000001</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.46</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.4724</v>
+        <v>-0.4919</v>
       </c>
       <c r="J49" t="n">
-        <v>-8.9756</v>
+        <v>-9.3461</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.35</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5758</v>
+        <v>-0.5871</v>
       </c>
       <c r="J50" t="n">
-        <v>-10.9402</v>
+        <v>-11.1549</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.24</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-0.6895</v>
       </c>
       <c r="J51" t="n">
-        <v>-13.091</v>
+        <v>-13.1005</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.41</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6017</v>
+        <v>0.672</v>
       </c>
       <c r="J52" t="n">
-        <v>24.068</v>
+        <v>26.88</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.35</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.6055</v>
       </c>
       <c r="J53" t="n">
-        <v>21.712</v>
+        <v>24.22</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.96</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.067</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="J54" t="n">
-        <v>-2.68</v>
+        <v>-3.016</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.74</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3022</v>
+        <v>-0.3138</v>
       </c>
       <c r="J55" t="n">
-        <v>-12.088</v>
+        <v>-12.552</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.73</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3118</v>
+        <v>-0.3232</v>
       </c>
       <c r="J56" t="n">
-        <v>-12.472</v>
+        <v>-12.928</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.53</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9379</v>
+        <v>1.0262</v>
       </c>
       <c r="J57" t="n">
-        <v>37.516</v>
+        <v>41.048</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.24</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.5956</v>
       </c>
       <c r="J58" t="n">
-        <v>21.632</v>
+        <v>23.824</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.98</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1166</v>
+        <v>-0.1153</v>
       </c>
       <c r="J59" t="n">
-        <v>-4.664</v>
+        <v>-4.612</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.88</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4321</v>
+        <v>-0.4124</v>
       </c>
       <c r="J60" t="n">
-        <v>-17.284</v>
+        <v>-16.496</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.83</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5688</v>
+        <v>-0.5357</v>
       </c>
       <c r="J61" t="n">
-        <v>-22.752</v>
+        <v>-21.428</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.91</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7119</v>
+        <v>0.8238</v>
       </c>
       <c r="J62" t="n">
-        <v>14.9499</v>
+        <v>17.2998</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.69</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5878</v>
+        <v>0.6804</v>
       </c>
       <c r="J63" t="n">
-        <v>12.3438</v>
+        <v>14.2884</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.54</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5023</v>
+        <v>0.5798</v>
       </c>
       <c r="J64" t="n">
-        <v>10.5483</v>
+        <v>12.1758</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.42</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4304</v>
+        <v>0.4943</v>
       </c>
       <c r="J65" t="n">
-        <v>9.038399999999999</v>
+        <v>10.3803</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.18</v>
       </c>
       <c r="I66" t="n">
-        <v>0.2211</v>
+        <v>0.2477</v>
       </c>
       <c r="J66" t="n">
-        <v>4.6431</v>
+        <v>5.2017</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>0.82</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.1612</v>
+        <v>-0.1877</v>
       </c>
       <c r="J67" t="n">
-        <v>-3.3852</v>
+        <v>-3.9417</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.79</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1943</v>
+        <v>-0.22</v>
       </c>
       <c r="J68" t="n">
-        <v>-4.0803</v>
+        <v>-4.62</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.75</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2369</v>
+        <v>-0.2612</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.9749</v>
+        <v>-5.4852</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.42</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5473</v>
+        <v>-0.5557</v>
       </c>
       <c r="J70" t="n">
-        <v>-11.4933</v>
+        <v>-11.6697</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.4</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5663</v>
+        <v>-0.5732</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.8923</v>
+        <v>-12.0372</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.31</v>
       </c>
       <c r="I72" t="n">
-        <v>0.525</v>
+        <v>0.5806</v>
       </c>
       <c r="J72" t="n">
-        <v>15.75</v>
+        <v>17.418</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.07</v>
       </c>
       <c r="I73" t="n">
-        <v>0.198</v>
+        <v>0.202</v>
       </c>
       <c r="J73" t="n">
-        <v>5.94</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.97</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0458</v>
+        <v>-0.055</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.374</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.71</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3202</v>
+        <v>-0.3333</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.606</v>
+        <v>-9.999000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.66</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3675</v>
+        <v>-0.379</v>
       </c>
       <c r="J76" t="n">
-        <v>-11.025</v>
+        <v>-11.37</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.36</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6988</v>
+        <v>0.7713</v>
       </c>
       <c r="J77" t="n">
-        <v>20.964</v>
+        <v>23.139</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.24</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5323</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="J78" t="n">
-        <v>15.969</v>
+        <v>17.646</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.05</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1681</v>
+        <v>0.1804</v>
       </c>
       <c r="J79" t="n">
-        <v>5.043</v>
+        <v>5.412</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.03</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1005</v>
+        <v>0.1153</v>
       </c>
       <c r="J80" t="n">
-        <v>3.015</v>
+        <v>3.459</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.0322</v>
+        <v>-0.0222</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.966</v>
+        <v>-0.666</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.42</v>
       </c>
       <c r="I82" t="n">
-        <v>0.7852</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="J82" t="n">
-        <v>23.556</v>
+        <v>22.635</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.13</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2863</v>
+        <v>0.2952</v>
       </c>
       <c r="J83" t="n">
-        <v>8.589</v>
+        <v>8.856</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.11</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2483</v>
+        <v>0.2587</v>
       </c>
       <c r="J84" t="n">
-        <v>7.449</v>
+        <v>7.761</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.05</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1263</v>
+        <v>0.1387</v>
       </c>
       <c r="J85" t="n">
-        <v>3.789</v>
+        <v>4.161</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.74</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3077</v>
+        <v>-0.3181</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.231</v>
+        <v>-9.542999999999999</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.59</v>
       </c>
       <c r="I87" t="n">
-        <v>1.3294</v>
+        <v>1.2918</v>
       </c>
       <c r="J87" t="n">
-        <v>39.882</v>
+        <v>38.754</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.09</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3211</v>
+        <v>0.3161</v>
       </c>
       <c r="J88" t="n">
-        <v>9.632999999999999</v>
+        <v>9.483000000000001</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.5938</v>
+        <v>-0.5634</v>
       </c>
       <c r="J89" t="n">
-        <v>-17.814</v>
+        <v>-16.902</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.78</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.6716</v>
+        <v>-0.6323</v>
       </c>
       <c r="J90" t="n">
-        <v>-20.148</v>
+        <v>-18.969</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.71</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.8479</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="J91" t="n">
-        <v>-25.437</v>
+        <v>-23.604</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.24</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3467</v>
+        <v>0.3588</v>
       </c>
       <c r="J92" t="n">
-        <v>12.4812</v>
+        <v>12.9168</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.14</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2185</v>
+        <v>0.2336</v>
       </c>
       <c r="J93" t="n">
-        <v>7.866</v>
+        <v>8.409599999999999</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.08</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1361</v>
+        <v>0.1505</v>
       </c>
       <c r="J94" t="n">
-        <v>4.8996</v>
+        <v>5.418</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.03</v>
       </c>
       <c r="I95" t="n">
-        <v>0.0575</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="J95" t="n">
-        <v>2.07</v>
+        <v>2.466</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.91</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1318</v>
+        <v>-0.1422</v>
       </c>
       <c r="J96" t="n">
-        <v>-4.7448</v>
+        <v>-5.1192</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.23</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3785</v>
+        <v>0.38</v>
       </c>
       <c r="J97" t="n">
-        <v>13.626</v>
+        <v>13.68</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.22</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3647</v>
+        <v>0.3669</v>
       </c>
       <c r="J98" t="n">
-        <v>13.1292</v>
+        <v>13.2084</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.19</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3225</v>
+        <v>0.327</v>
       </c>
       <c r="J99" t="n">
-        <v>11.61</v>
+        <v>11.772</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.78</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2584</v>
+        <v>-0.2717</v>
       </c>
       <c r="J100" t="n">
-        <v>-9.3024</v>
+        <v>-9.7812</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4652</v>
+        <v>-0.4716</v>
       </c>
       <c r="J101" t="n">
-        <v>-16.7472</v>
+        <v>-16.9776</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.32</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6677</v>
+        <v>0.6405</v>
       </c>
       <c r="J102" t="n">
-        <v>18.6956</v>
+        <v>17.934</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.93</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.1086</v>
       </c>
       <c r="J103" t="n">
-        <v>-2.6936</v>
+        <v>-3.0408</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.92</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1077</v>
+        <v>-0.1206</v>
       </c>
       <c r="J104" t="n">
-        <v>-3.0156</v>
+        <v>-3.3768</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.89</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.141</v>
+        <v>-0.1549</v>
       </c>
       <c r="J105" t="n">
-        <v>-3.948</v>
+        <v>-4.3372</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.75</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2838</v>
+        <v>-0.2974</v>
       </c>
       <c r="J106" t="n">
-        <v>-7.9464</v>
+        <v>-8.327199999999999</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.37</v>
       </c>
       <c r="I107" t="n">
-        <v>0.989</v>
+        <v>0.924</v>
       </c>
       <c r="J107" t="n">
-        <v>27.692</v>
+        <v>25.872</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.26</v>
       </c>
       <c r="I108" t="n">
-        <v>0.737</v>
+        <v>0.6962</v>
       </c>
       <c r="J108" t="n">
-        <v>20.636</v>
+        <v>19.4936</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.23</v>
       </c>
       <c r="I109" t="n">
-        <v>0.6632</v>
+        <v>0.6311</v>
       </c>
       <c r="J109" t="n">
-        <v>18.5696</v>
+        <v>17.6708</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.79</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.6713</v>
+        <v>-0.6274</v>
       </c>
       <c r="J110" t="n">
-        <v>-18.7964</v>
+        <v>-17.5672</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.77</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.7225</v>
+        <v>-0.6726</v>
       </c>
       <c r="J111" t="n">
-        <v>-20.23</v>
+        <v>-18.8328</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.43</v>
       </c>
       <c r="I112" t="n">
-        <v>1.0505</v>
+        <v>1.001</v>
       </c>
       <c r="J112" t="n">
-        <v>27.313</v>
+        <v>26.026</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.35</v>
       </c>
       <c r="I113" t="n">
-        <v>0.9073</v>
+        <v>0.8528</v>
       </c>
       <c r="J113" t="n">
-        <v>23.5898</v>
+        <v>22.1728</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.15</v>
       </c>
       <c r="I114" t="n">
-        <v>0.4371</v>
+        <v>0.4336</v>
       </c>
       <c r="J114" t="n">
-        <v>11.3646</v>
+        <v>11.2736</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.09</v>
       </c>
       <c r="I115" t="n">
-        <v>0.274</v>
+        <v>0.2838</v>
       </c>
       <c r="J115" t="n">
-        <v>7.124</v>
+        <v>7.3788</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.98</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.1447</v>
+        <v>-0.1349</v>
       </c>
       <c r="J116" t="n">
-        <v>-3.7622</v>
+        <v>-3.5074</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.13</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3233</v>
+        <v>0.322</v>
       </c>
       <c r="J117" t="n">
-        <v>8.405799999999999</v>
+        <v>8.372</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.12</v>
       </c>
       <c r="I118" t="n">
-        <v>0.3032</v>
+        <v>0.303</v>
       </c>
       <c r="J118" t="n">
-        <v>7.8832</v>
+        <v>7.878</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.87</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1604</v>
+        <v>-0.1752</v>
       </c>
       <c r="J119" t="n">
-        <v>-4.1704</v>
+        <v>-4.5552</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.85</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1814</v>
+        <v>-0.1964</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.7164</v>
+        <v>-5.1064</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.75</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2816</v>
+        <v>-0.2957</v>
       </c>
       <c r="J121" t="n">
-        <v>-7.3216</v>
+        <v>-7.6882</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.39</v>
       </c>
       <c r="I122" t="n">
-        <v>0.993</v>
+        <v>0.9346</v>
       </c>
       <c r="J122" t="n">
-        <v>26.811</v>
+        <v>25.2342</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.2</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5627</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="J123" t="n">
-        <v>15.1929</v>
+        <v>14.7663</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.16</v>
       </c>
       <c r="I124" t="n">
-        <v>0.466</v>
+        <v>0.4591</v>
       </c>
       <c r="J124" t="n">
-        <v>12.582</v>
+        <v>12.3957</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.09</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2782</v>
+        <v>0.2868</v>
       </c>
       <c r="J125" t="n">
-        <v>7.5114</v>
+        <v>7.7436</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>1.07</v>
       </c>
       <c r="I126" t="n">
-        <v>0.2193</v>
+        <v>0.2317</v>
       </c>
       <c r="J126" t="n">
-        <v>5.9211</v>
+        <v>6.2559</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.58</v>
       </c>
       <c r="I127" t="n">
-        <v>1.0683</v>
+        <v>1.0259</v>
       </c>
       <c r="J127" t="n">
-        <v>28.8441</v>
+        <v>27.6993</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="J128" t="n">
-        <v>-2.2437</v>
+        <v>-2.5704</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.79</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2423</v>
+        <v>-0.2571</v>
       </c>
       <c r="J129" t="n">
-        <v>-6.5421</v>
+        <v>-6.9417</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.76</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2719</v>
+        <v>-0.2862</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.3413</v>
+        <v>-7.7274</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.65</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3768</v>
+        <v>-0.388</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.1736</v>
+        <v>-10.476</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.39</v>
       </c>
       <c r="I132" t="n">
-        <v>0.7895</v>
+        <v>0.7499</v>
       </c>
       <c r="J132" t="n">
-        <v>20.527</v>
+        <v>19.4974</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.24</v>
       </c>
       <c r="I133" t="n">
-        <v>0.5261</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="J133" t="n">
-        <v>13.6786</v>
+        <v>13.3016</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.88</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1516</v>
+        <v>-0.1658</v>
       </c>
       <c r="J134" t="n">
-        <v>-3.9416</v>
+        <v>-4.3108</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.68</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3505</v>
+        <v>-0.3624</v>
       </c>
       <c r="J135" t="n">
-        <v>-9.113</v>
+        <v>-9.4224</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.61</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4158</v>
+        <v>-0.4251</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.8108</v>
+        <v>-11.0526</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.48</v>
       </c>
       <c r="I137" t="n">
-        <v>1.1207</v>
+        <v>1.0809</v>
       </c>
       <c r="J137" t="n">
-        <v>29.1382</v>
+        <v>28.1034</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.35</v>
       </c>
       <c r="I138" t="n">
-        <v>0.9136</v>
+        <v>0.8574000000000001</v>
       </c>
       <c r="J138" t="n">
-        <v>23.7536</v>
+        <v>22.2924</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.16</v>
       </c>
       <c r="I139" t="n">
-        <v>0.4664</v>
+        <v>0.4594</v>
       </c>
       <c r="J139" t="n">
-        <v>12.1264</v>
+        <v>11.9444</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.1</v>
       </c>
       <c r="I140" t="n">
-        <v>0.3072</v>
+        <v>0.3134</v>
       </c>
       <c r="J140" t="n">
-        <v>7.9872</v>
+        <v>8.148400000000001</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6443</v>
+        <v>-0.5989</v>
       </c>
       <c r="J141" t="n">
-        <v>-16.7518</v>
+        <v>-15.5714</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.44</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5425</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="J142" t="n">
-        <v>11.935</v>
+        <v>12.1418</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.37</v>
       </c>
       <c r="I143" t="n">
-        <v>0.4663</v>
+        <v>0.4797</v>
       </c>
       <c r="J143" t="n">
-        <v>10.2586</v>
+        <v>10.5534</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.33</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4223</v>
+        <v>0.4376</v>
       </c>
       <c r="J144" t="n">
-        <v>9.2906</v>
+        <v>9.6272</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.21</v>
       </c>
       <c r="I145" t="n">
-        <v>0.2857</v>
+        <v>0.3049</v>
       </c>
       <c r="J145" t="n">
-        <v>6.2854</v>
+        <v>6.7078</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.1</v>
       </c>
       <c r="I146" t="n">
-        <v>0.1415</v>
+        <v>0.1621</v>
       </c>
       <c r="J146" t="n">
-        <v>3.113</v>
+        <v>3.5662</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.44</v>
       </c>
       <c r="I147" t="n">
-        <v>0.7391</v>
+        <v>0.6999</v>
       </c>
       <c r="J147" t="n">
-        <v>16.2602</v>
+        <v>15.3978</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.02</v>
       </c>
       <c r="I148" t="n">
-        <v>0.0914</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="J148" t="n">
-        <v>2.0108</v>
+        <v>1.9338</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.74</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2748</v>
+        <v>-0.2924</v>
       </c>
       <c r="J149" t="n">
-        <v>-6.0456</v>
+        <v>-6.4328</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.46</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.5364</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="J150" t="n">
-        <v>-11.8008</v>
+        <v>-11.9196</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.43</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5637</v>
+        <v>-0.5673</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.4014</v>
+        <v>-12.4806</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.72</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.2465</v>
+        <v>-0.2743</v>
       </c>
       <c r="J152" t="n">
-        <v>-5.1765</v>
+        <v>-5.7603</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.68</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.2888</v>
+        <v>-0.3145</v>
       </c>
       <c r="J153" t="n">
-        <v>-6.0648</v>
+        <v>-6.6045</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.5</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.4578</v>
+        <v>-0.4746</v>
       </c>
       <c r="J154" t="n">
-        <v>-9.613799999999999</v>
+        <v>-9.9666</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.47</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4861</v>
+        <v>-0.5009</v>
       </c>
       <c r="J155" t="n">
-        <v>-10.2081</v>
+        <v>-10.5189</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.45</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5051</v>
+        <v>-0.5185</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.6071</v>
+        <v>-10.8885</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.59</v>
       </c>
       <c r="I157" t="n">
-        <v>1.2035</v>
+        <v>1.1803</v>
       </c>
       <c r="J157" t="n">
-        <v>25.2735</v>
+        <v>24.7863</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.57</v>
       </c>
       <c r="I158" t="n">
-        <v>1.1799</v>
+        <v>1.155</v>
       </c>
       <c r="J158" t="n">
-        <v>24.7779</v>
+        <v>24.255</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.55</v>
       </c>
       <c r="I159" t="n">
-        <v>1.1564</v>
+        <v>1.1296</v>
       </c>
       <c r="J159" t="n">
-        <v>24.2844</v>
+        <v>23.7216</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.46</v>
       </c>
       <c r="I160" t="n">
-        <v>1.0499</v>
+        <v>1.0098</v>
       </c>
       <c r="J160" t="n">
-        <v>22.0479</v>
+        <v>21.2058</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.12</v>
       </c>
       <c r="I161" t="n">
-        <v>0.3002</v>
+        <v>0.321</v>
       </c>
       <c r="J161" t="n">
-        <v>6.3042</v>
+        <v>6.741</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.41</v>
       </c>
       <c r="I162" t="n">
-        <v>0.8404</v>
+        <v>0.7927</v>
       </c>
       <c r="J162" t="n">
-        <v>22.6908</v>
+        <v>21.4029</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.21</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4836</v>
+        <v>0.4702</v>
       </c>
       <c r="J163" t="n">
-        <v>13.0572</v>
+        <v>12.6954</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.91</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1156</v>
+        <v>-0.1297</v>
       </c>
       <c r="J164" t="n">
-        <v>-3.1212</v>
+        <v>-3.5019</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.61</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.4121</v>
+        <v>-0.4222</v>
       </c>
       <c r="J165" t="n">
-        <v>-11.1267</v>
+        <v>-11.3994</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.5</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5124</v>
+        <v>-0.5174</v>
       </c>
       <c r="J166" t="n">
-        <v>-13.8348</v>
+        <v>-13.9698</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.37</v>
       </c>
       <c r="I167" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="J167" t="n">
-        <v>25.6257</v>
+        <v>24.0732</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.3</v>
       </c>
       <c r="I168" t="n">
-        <v>0.793</v>
+        <v>0.7526</v>
       </c>
       <c r="J168" t="n">
-        <v>21.411</v>
+        <v>20.3202</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.19</v>
       </c>
       <c r="I169" t="n">
-        <v>0.5363</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="J169" t="n">
-        <v>14.4801</v>
+        <v>14.1399</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.1</v>
       </c>
       <c r="I170" t="n">
-        <v>0.302</v>
+        <v>0.3099</v>
       </c>
       <c r="J170" t="n">
-        <v>8.154</v>
+        <v>8.3673</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.05</v>
       </c>
       <c r="I171" t="n">
-        <v>0.1518</v>
+        <v>0.1691</v>
       </c>
       <c r="J171" t="n">
-        <v>4.0986</v>
+        <v>4.5657</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.11</v>
       </c>
       <c r="I172" t="n">
-        <v>0.2666</v>
+        <v>0.2719</v>
       </c>
       <c r="J172" t="n">
-        <v>6.3984</v>
+        <v>6.5256</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.06</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1618</v>
+        <v>0.1701</v>
       </c>
       <c r="J173" t="n">
-        <v>3.8832</v>
+        <v>4.0824</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.05</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1393</v>
+        <v>0.1479</v>
       </c>
       <c r="J174" t="n">
-        <v>3.3432</v>
+        <v>3.5496</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.99</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.0205</v>
+        <v>-0.0252</v>
       </c>
       <c r="J175" t="n">
-        <v>-0.492</v>
+        <v>-0.6048</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.79</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.249</v>
+        <v>-0.2623</v>
       </c>
       <c r="J176" t="n">
-        <v>-5.976</v>
+        <v>-6.2952</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.5</v>
       </c>
       <c r="I177" t="n">
-        <v>1.142</v>
+        <v>1.1047</v>
       </c>
       <c r="J177" t="n">
-        <v>27.408</v>
+        <v>26.5128</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.45</v>
       </c>
       <c r="I178" t="n">
-        <v>1.0775</v>
+        <v>1.0331</v>
       </c>
       <c r="J178" t="n">
-        <v>25.86</v>
+        <v>24.7944</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.37</v>
       </c>
       <c r="I179" t="n">
-        <v>0.9503</v>
+        <v>0.8925</v>
       </c>
       <c r="J179" t="n">
-        <v>22.8072</v>
+        <v>21.42</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.85</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.5427</v>
+        <v>-0.5069</v>
       </c>
       <c r="J180" t="n">
-        <v>-13.0248</v>
+        <v>-12.1656</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.82</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6226</v>
+        <v>-0.5786</v>
       </c>
       <c r="J181" t="n">
-        <v>-14.9424</v>
+        <v>-13.8864</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.89</v>
       </c>
       <c r="I182" t="n">
-        <v>1.5462</v>
+        <v>1.5448</v>
       </c>
       <c r="J182" t="n">
-        <v>34.0164</v>
+        <v>33.9856</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.76</v>
       </c>
       <c r="I183" t="n">
-        <v>1.3984</v>
+        <v>1.3888</v>
       </c>
       <c r="J183" t="n">
-        <v>30.7648</v>
+        <v>30.5536</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.45</v>
       </c>
       <c r="I184" t="n">
-        <v>1.0362</v>
+        <v>0.9939</v>
       </c>
       <c r="J184" t="n">
-        <v>22.7964</v>
+        <v>21.8658</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.16</v>
       </c>
       <c r="I185" t="n">
-        <v>0.4037</v>
+        <v>0.4159</v>
       </c>
       <c r="J185" t="n">
-        <v>8.881399999999999</v>
+        <v>9.149800000000001</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.1</v>
       </c>
       <c r="I186" t="n">
-        <v>0.2416</v>
+        <v>0.2677</v>
       </c>
       <c r="J186" t="n">
-        <v>5.3152</v>
+        <v>5.8894</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.11</v>
       </c>
       <c r="I187" t="n">
-        <v>0.3973</v>
+        <v>0.3682</v>
       </c>
       <c r="J187" t="n">
-        <v>8.740600000000001</v>
+        <v>8.1004</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.83</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1718</v>
+        <v>-0.1938</v>
       </c>
       <c r="J188" t="n">
-        <v>-3.7796</v>
+        <v>-4.2636</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.57</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.4199</v>
+        <v>-0.4344</v>
       </c>
       <c r="J189" t="n">
-        <v>-9.2378</v>
+        <v>-9.556800000000001</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.55</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.4386</v>
+        <v>-0.4521</v>
       </c>
       <c r="J190" t="n">
-        <v>-9.6492</v>
+        <v>-9.946199999999999</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.52</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4666</v>
+        <v>-0.4785</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.2652</v>
+        <v>-10.527</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.79</v>
       </c>
       <c r="I192" t="n">
-        <v>1.4581</v>
+        <v>1.4475</v>
       </c>
       <c r="J192" t="n">
-        <v>30.6201</v>
+        <v>30.3975</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.56</v>
       </c>
       <c r="I193" t="n">
-        <v>1.184</v>
+        <v>1.1561</v>
       </c>
       <c r="J193" t="n">
-        <v>24.864</v>
+        <v>24.2781</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.22</v>
       </c>
       <c r="I194" t="n">
-        <v>0.5788</v>
+        <v>0.5682</v>
       </c>
       <c r="J194" t="n">
-        <v>12.1548</v>
+        <v>11.9322</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.21</v>
       </c>
       <c r="I195" t="n">
-        <v>0.5545</v>
+        <v>0.5465</v>
       </c>
       <c r="J195" t="n">
-        <v>11.6445</v>
+        <v>11.4765</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.99</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.1399</v>
+        <v>-0.1189</v>
       </c>
       <c r="J196" t="n">
-        <v>-2.9379</v>
+        <v>-2.4969</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.15</v>
       </c>
       <c r="I197" t="n">
-        <v>0.4807</v>
+        <v>0.4464</v>
       </c>
       <c r="J197" t="n">
-        <v>10.0947</v>
+        <v>9.3744</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.86</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.1402</v>
+        <v>-0.1622</v>
       </c>
       <c r="J198" t="n">
-        <v>-2.9442</v>
+        <v>-3.4062</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.59</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.4022</v>
+        <v>-0.4175</v>
       </c>
       <c r="J199" t="n">
-        <v>-8.446199999999999</v>
+        <v>-8.7675</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.57</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4209</v>
+        <v>-0.4352</v>
       </c>
       <c r="J200" t="n">
-        <v>-8.838900000000001</v>
+        <v>-9.139200000000001</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.44</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5421</v>
+        <v>-0.5489000000000001</v>
       </c>
       <c r="J201" t="n">
-        <v>-11.3841</v>
+        <v>-11.5269</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.63</v>
       </c>
       <c r="I202" t="n">
-        <v>1.299</v>
+        <v>1.2734</v>
       </c>
       <c r="J202" t="n">
-        <v>37.671</v>
+        <v>36.9286</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.43</v>
       </c>
       <c r="I203" t="n">
-        <v>1.0451</v>
+        <v>0.9957</v>
       </c>
       <c r="J203" t="n">
-        <v>30.3079</v>
+        <v>28.8753</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.13</v>
       </c>
       <c r="I204" t="n">
-        <v>0.3793</v>
+        <v>0.3821</v>
       </c>
       <c r="J204" t="n">
-        <v>10.9997</v>
+        <v>11.0809</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.07</v>
       </c>
       <c r="I205" t="n">
-        <v>0.2091</v>
+        <v>0.2246</v>
       </c>
       <c r="J205" t="n">
-        <v>6.0639</v>
+        <v>6.5134</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.86</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5218</v>
+        <v>-0.4868</v>
       </c>
       <c r="J206" t="n">
-        <v>-15.1322</v>
+        <v>-14.1172</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.31</v>
       </c>
       <c r="I207" t="n">
-        <v>0.6564</v>
+        <v>0.6293</v>
       </c>
       <c r="J207" t="n">
-        <v>19.0356</v>
+        <v>18.2497</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.18</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4192</v>
+        <v>0.4121</v>
       </c>
       <c r="J208" t="n">
-        <v>12.1568</v>
+        <v>11.9509</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.91</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1175</v>
+        <v>-0.1312</v>
       </c>
       <c r="J209" t="n">
-        <v>-3.4075</v>
+        <v>-3.8048</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3397</v>
+        <v>-0.3521</v>
       </c>
       <c r="J210" t="n">
-        <v>-9.8513</v>
+        <v>-10.2109</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.65</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3773</v>
+        <v>-0.3884</v>
       </c>
       <c r="J211" t="n">
-        <v>-10.9417</v>
+        <v>-11.2636</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.25</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7032</v>
+        <v>0.6682</v>
       </c>
       <c r="J212" t="n">
-        <v>20.3928</v>
+        <v>19.3778</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.23</v>
       </c>
       <c r="I213" t="n">
-        <v>0.6543</v>
+        <v>0.625</v>
       </c>
       <c r="J213" t="n">
-        <v>18.9747</v>
+        <v>18.125</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.22</v>
       </c>
       <c r="I214" t="n">
-        <v>0.6297</v>
+        <v>0.6031</v>
       </c>
       <c r="J214" t="n">
-        <v>18.2613</v>
+        <v>17.4899</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.97</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1586</v>
+        <v>-0.1552</v>
       </c>
       <c r="J215" t="n">
-        <v>-4.5994</v>
+        <v>-4.5008</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.88</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4371</v>
+        <v>-0.4159</v>
       </c>
       <c r="J216" t="n">
-        <v>-12.6759</v>
+        <v>-12.0611</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.33</v>
       </c>
       <c r="I217" t="n">
-        <v>0.6906</v>
+        <v>0.6603</v>
       </c>
       <c r="J217" t="n">
-        <v>20.0274</v>
+        <v>19.1487</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.12</v>
       </c>
       <c r="I218" t="n">
-        <v>0.3012</v>
+        <v>0.3016</v>
       </c>
       <c r="J218" t="n">
-        <v>8.7348</v>
+        <v>8.7464</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.01</v>
       </c>
       <c r="I219" t="n">
-        <v>0.047</v>
+        <v>0.0499</v>
       </c>
       <c r="J219" t="n">
-        <v>1.363</v>
+        <v>1.4471</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.86</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1717</v>
+        <v>-0.1864</v>
       </c>
       <c r="J220" t="n">
-        <v>-4.9793</v>
+        <v>-5.4056</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.43</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.577</v>
+        <v>-0.5779</v>
       </c>
       <c r="J221" t="n">
-        <v>-16.733</v>
+        <v>-16.7591</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.73</v>
       </c>
       <c r="I222" t="n">
-        <v>1.4075</v>
+        <v>1.3906</v>
       </c>
       <c r="J222" t="n">
-        <v>39.41</v>
+        <v>38.9368</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.35</v>
       </c>
       <c r="I223" t="n">
-        <v>0.8871</v>
+        <v>0.8387</v>
       </c>
       <c r="J223" t="n">
-        <v>24.8388</v>
+        <v>23.4836</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.34</v>
       </c>
       <c r="I224" t="n">
-        <v>0.8651</v>
+        <v>0.8193</v>
       </c>
       <c r="J224" t="n">
-        <v>24.2228</v>
+        <v>22.9404</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.03</v>
       </c>
       <c r="I225" t="n">
-        <v>0.0664</v>
+        <v>0.0916</v>
       </c>
       <c r="J225" t="n">
-        <v>1.8592</v>
+        <v>2.5648</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.92</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3623</v>
+        <v>-0.3381</v>
       </c>
       <c r="J226" t="n">
-        <v>-10.1444</v>
+        <v>-9.466799999999999</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.07</v>
       </c>
       <c r="I227" t="n">
-        <v>0.2106</v>
+        <v>0.2112</v>
       </c>
       <c r="J227" t="n">
-        <v>5.8968</v>
+        <v>5.9136</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.97</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.0411</v>
+        <v>-0.0514</v>
       </c>
       <c r="J228" t="n">
-        <v>-1.1508</v>
+        <v>-1.4392</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.89</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1351</v>
+        <v>-0.1504</v>
       </c>
       <c r="J229" t="n">
-        <v>-3.7828</v>
+        <v>-4.2112</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2174</v>
+        <v>-0.2334</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.0872</v>
+        <v>-6.5352</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.78</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2472</v>
+        <v>-0.2629</v>
       </c>
       <c r="J231" t="n">
-        <v>-6.9216</v>
+        <v>-7.3612</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>2.16</v>
       </c>
       <c r="I232" t="n">
-        <v>1.8338</v>
+        <v>1.8725</v>
       </c>
       <c r="J232" t="n">
-        <v>38.5098</v>
+        <v>39.3225</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.65</v>
       </c>
       <c r="I233" t="n">
-        <v>1.2806</v>
+        <v>1.2617</v>
       </c>
       <c r="J233" t="n">
-        <v>26.8926</v>
+        <v>26.4957</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.16</v>
       </c>
       <c r="I234" t="n">
-        <v>0.4154</v>
+        <v>0.4241</v>
       </c>
       <c r="J234" t="n">
-        <v>8.7234</v>
+        <v>8.9061</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.06</v>
       </c>
       <c r="I235" t="n">
-        <v>0.1344</v>
+        <v>0.1649</v>
       </c>
       <c r="J235" t="n">
-        <v>2.8224</v>
+        <v>3.4629</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>1.05</v>
       </c>
       <c r="I236" t="n">
-        <v>0.1025</v>
+        <v>0.1347</v>
       </c>
       <c r="J236" t="n">
-        <v>2.1525</v>
+        <v>2.8287</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>0.82</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.1631</v>
+        <v>-0.1892</v>
       </c>
       <c r="J237" t="n">
-        <v>-3.4251</v>
+        <v>-3.9732</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.79</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.1961</v>
+        <v>-0.2213</v>
       </c>
       <c r="J238" t="n">
-        <v>-4.1181</v>
+        <v>-4.6473</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.55</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.4259</v>
+        <v>-0.4422</v>
       </c>
       <c r="J239" t="n">
-        <v>-8.943899999999999</v>
+        <v>-9.286199999999999</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.53</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.4446</v>
+        <v>-0.4598</v>
       </c>
       <c r="J240" t="n">
-        <v>-9.336600000000001</v>
+        <v>-9.655799999999999</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.52</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.454</v>
+        <v>-0.4686</v>
       </c>
       <c r="J241" t="n">
-        <v>-9.534000000000001</v>
+        <v>-9.8406</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2636/event_2636_evp_summary.xlsx
+++ b/database/event/2636/event_2636_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.618600000000001</v>
+        <v>8.849</v>
       </c>
       <c r="C2" t="n">
-        <v>3.0411</v>
+        <v>2.7978</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7544</v>
+        <v>3.4254</v>
       </c>
       <c r="E2" t="n">
-        <v>9.618600000000001</v>
+        <v>8.849</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0586</v>
+        <v>3.0726</v>
       </c>
       <c r="G2" t="n">
-        <v>6.56</v>
+        <v>5.7764</v>
       </c>
       <c r="H2" t="n">
-        <v>5.1973</v>
+        <v>5.0932</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8065</v>
+        <v>2.8597</v>
       </c>
       <c r="J2" t="n">
-        <v>6.56</v>
+        <v>6.7209</v>
       </c>
       <c r="K2" t="n">
         <v>43</v>
@@ -529,7 +529,7 @@
         <v>108</v>
       </c>
       <c r="M2" t="n">
-        <v>9.3665</v>
+        <v>9.5806</v>
       </c>
       <c r="N2" t="n">
         <v>151</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.3057</v>
+        <v>8.2799</v>
       </c>
       <c r="C3" t="n">
-        <v>2.626</v>
+        <v>2.6179</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1567</v>
+        <v>3.1661</v>
       </c>
       <c r="E3" t="n">
-        <v>8.3057</v>
+        <v>8.2799</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3139</v>
+        <v>3.3073</v>
       </c>
       <c r="G3" t="n">
-        <v>4.9919</v>
+        <v>4.9726</v>
       </c>
       <c r="H3" t="n">
-        <v>6.0395</v>
+        <v>5.9743</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2613</v>
+        <v>3.3544</v>
       </c>
       <c r="J3" t="n">
-        <v>4.9919</v>
+        <v>4.9726</v>
       </c>
       <c r="K3" t="n">
         <v>43</v>
@@ -575,7 +575,7 @@
         <v>108</v>
       </c>
       <c r="M3" t="n">
-        <v>8.2532</v>
+        <v>8.327</v>
       </c>
       <c r="N3" t="n">
         <v>151</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.43</v>
+        <v>5.2348</v>
       </c>
       <c r="C4" t="n">
-        <v>1.7168</v>
+        <v>1.6551</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8476</v>
+        <v>1.7789</v>
       </c>
       <c r="E4" t="n">
-        <v>5.43</v>
+        <v>5.2348</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2811</v>
+        <v>1.1172</v>
       </c>
       <c r="G4" t="n">
-        <v>4.1488</v>
+        <v>4.1175</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2811</v>
+        <v>1.1172</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6918</v>
+        <v>0.6273</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1488</v>
+        <v>4.1175</v>
       </c>
       <c r="K4" t="n">
         <v>43</v>
@@ -621,7 +621,7 @@
         <v>108</v>
       </c>
       <c r="M4" t="n">
-        <v>4.840599999999999</v>
+        <v>4.7448</v>
       </c>
       <c r="N4" t="n">
         <v>151</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.2674</v>
+        <v>5.1449</v>
       </c>
       <c r="C5" t="n">
-        <v>1.6654</v>
+        <v>1.6267</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7736</v>
+        <v>1.738</v>
       </c>
       <c r="E5" t="n">
-        <v>5.2674</v>
+        <v>5.1449</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1338</v>
+        <v>2.0222</v>
       </c>
       <c r="G5" t="n">
-        <v>3.1336</v>
+        <v>3.1227</v>
       </c>
       <c r="H5" t="n">
-        <v>2.146</v>
+        <v>2.0222</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1588</v>
+        <v>1.1354</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1336</v>
+        <v>3.1227</v>
       </c>
       <c r="K5" t="n">
         <v>43</v>
@@ -667,7 +667,7 @@
         <v>108</v>
       </c>
       <c r="M5" t="n">
-        <v>4.2924</v>
+        <v>4.2581</v>
       </c>
       <c r="N5" t="n">
         <v>151</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.5304</v>
+        <v>4.3131</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4324</v>
+        <v>1.3637</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4381</v>
+        <v>1.359</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5304</v>
+        <v>4.3131</v>
       </c>
       <c r="F6" t="n">
-        <v>4.4211</v>
+        <v>4.1719</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1093</v>
+        <v>0.1412</v>
       </c>
       <c r="H6" t="n">
-        <v>9.6927</v>
+        <v>9.220499999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>5.234</v>
+        <v>5.177</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1093</v>
+        <v>0.1412</v>
       </c>
       <c r="K6" t="n">
         <v>192</v>
@@ -713,7 +713,7 @@
         <v>160</v>
       </c>
       <c r="M6" t="n">
-        <v>5.3433</v>
+        <v>5.318199999999999</v>
       </c>
       <c r="N6" t="n">
         <v>352</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.3536</v>
+        <v>4.3094</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3765</v>
+        <v>1.3625</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3576</v>
+        <v>1.3573</v>
       </c>
       <c r="E7" t="n">
-        <v>4.3536</v>
+        <v>4.3094</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9128</v>
+        <v>2.9429</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4408</v>
+        <v>1.3665</v>
       </c>
       <c r="H7" t="n">
-        <v>4.7162</v>
+        <v>4.6061</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5467</v>
+        <v>2.5862</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4408</v>
+        <v>1.3665</v>
       </c>
       <c r="K7" t="n">
         <v>49</v>
@@ -759,7 +759,7 @@
         <v>91</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9875</v>
+        <v>3.9527</v>
       </c>
       <c r="N7" t="n">
         <v>140</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.9522</v>
+        <v>3.9382</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2496</v>
+        <v>1.2451</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1749</v>
+        <v>1.1882</v>
       </c>
       <c r="E8" t="n">
-        <v>3.9522</v>
+        <v>3.9382</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7666</v>
+        <v>2.8049</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1856</v>
+        <v>1.1333</v>
       </c>
       <c r="H8" t="n">
-        <v>4.2338</v>
+        <v>4.088</v>
       </c>
       <c r="I8" t="n">
-        <v>2.2862</v>
+        <v>2.2953</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1856</v>
+        <v>1.1333</v>
       </c>
       <c r="K8" t="n">
         <v>49</v>
@@ -805,7 +805,7 @@
         <v>91</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4718</v>
+        <v>3.4286</v>
       </c>
       <c r="N8" t="n">
         <v>140</v>
@@ -814,185 +814,185 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7497</v>
+        <v>3.6366</v>
       </c>
       <c r="C9" t="n">
-        <v>1.1855</v>
+        <v>1.1498</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0827</v>
+        <v>1.0509</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7497</v>
+        <v>3.6366</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0196</v>
+        <v>2.3516</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7301</v>
+        <v>1.285</v>
       </c>
       <c r="H9" t="n">
-        <v>1.0196</v>
+        <v>2.3864</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5506</v>
+        <v>1.3399</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7301</v>
+        <v>1.285</v>
       </c>
       <c r="K9" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L9" t="n">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2807</v>
+        <v>2.6249</v>
       </c>
       <c r="N9" t="n">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.6495</v>
+        <v>3.6236</v>
       </c>
       <c r="C10" t="n">
-        <v>1.1539</v>
+        <v>1.1457</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0371</v>
+        <v>1.0449</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6495</v>
+        <v>3.6236</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2622</v>
+        <v>0.8745000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3873</v>
+        <v>2.7491</v>
       </c>
       <c r="H10" t="n">
-        <v>2.5695</v>
+        <v>0.8745000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3875</v>
+        <v>0.491</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3873</v>
+        <v>2.7491</v>
       </c>
       <c r="K10" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="L10" t="n">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="M10" t="n">
-        <v>2.7748</v>
+        <v>3.2401</v>
       </c>
       <c r="N10" t="n">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.997</v>
+        <v>2.9729</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9476</v>
+        <v>0.9399</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7401</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>2.997</v>
+        <v>2.9729</v>
       </c>
       <c r="F11" t="n">
-        <v>2.997</v>
+        <v>2.8102</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.1627</v>
       </c>
       <c r="H11" t="n">
-        <v>3.8345</v>
+        <v>4.1082</v>
       </c>
       <c r="I11" t="n">
-        <v>3.8345</v>
+        <v>2.3066</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>0.1627</v>
       </c>
       <c r="K11" t="n">
-        <v>133</v>
+        <v>192</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8345</v>
+        <v>2.4693</v>
       </c>
       <c r="N11" t="n">
-        <v>133</v>
+        <v>352</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.967</v>
+        <v>2.893</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9381</v>
+        <v>0.9147</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7264</v>
+        <v>0.7121</v>
       </c>
       <c r="E12" t="n">
-        <v>2.967</v>
+        <v>2.893</v>
       </c>
       <c r="F12" t="n">
-        <v>2.7961</v>
+        <v>2.893</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1709</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4.3312</v>
+        <v>3.6798</v>
       </c>
       <c r="I12" t="n">
-        <v>2.3388</v>
+        <v>3.6798</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1709</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>192</v>
+        <v>133</v>
       </c>
       <c r="L12" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.5097</v>
+        <v>3.6798</v>
       </c>
       <c r="N12" t="n">
-        <v>352</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6059</v>
+        <v>2.5847</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8239</v>
+        <v>0.8172</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5621</v>
+        <v>0.5717</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6059</v>
+        <v>2.5847</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5963</v>
+        <v>2.5982</v>
       </c>
       <c r="G13" t="n">
-        <v>0.009599999999999999</v>
+        <v>-0.0135</v>
       </c>
       <c r="H13" t="n">
-        <v>3.6721</v>
+        <v>3.3122</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9829</v>
+        <v>1.8597</v>
       </c>
       <c r="J13" t="n">
-        <v>0.009599999999999999</v>
+        <v>-0.0135</v>
       </c>
       <c r="K13" t="n">
         <v>103</v>
@@ -1035,7 +1035,7 @@
         <v>39</v>
       </c>
       <c r="M13" t="n">
-        <v>1.9925</v>
+        <v>1.8462</v>
       </c>
       <c r="N13" t="n">
         <v>142</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.8237</v>
+        <v>1.9433</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5766</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>0.206</v>
+        <v>0.2795</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8237</v>
+        <v>1.9433</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2907</v>
+        <v>2.3682</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.467</v>
+        <v>-0.4249</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6636</v>
+        <v>2.4488</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4383</v>
+        <v>1.3749</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.467</v>
+        <v>-0.4249</v>
       </c>
       <c r="K14" t="n">
         <v>103</v>
@@ -1081,7 +1081,7 @@
         <v>39</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9712999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="N14" t="n">
         <v>142</v>
@@ -1090,185 +1090,185 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.7434</v>
+        <v>1.7205</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5512</v>
+        <v>0.544</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1694</v>
+        <v>0.178</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7434</v>
+        <v>1.7205</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1751</v>
+        <v>2.7205</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4317</v>
+        <v>-1</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2823</v>
+        <v>3.7714</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2324</v>
+        <v>2.1175</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4317</v>
+        <v>-1</v>
       </c>
       <c r="K15" t="n">
-        <v>192</v>
+        <v>103</v>
       </c>
       <c r="L15" t="n">
-        <v>160</v>
+        <v>39</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8007</v>
+        <v>1.1175</v>
       </c>
       <c r="N15" t="n">
-        <v>352</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.6956</v>
+        <v>1.7021</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5361</v>
+        <v>0.5382</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1477</v>
+        <v>0.1696</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6956</v>
+        <v>1.7021</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6956</v>
+        <v>2.172</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0.4699</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6956</v>
+        <v>2.172</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6956</v>
+        <v>1.2195</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0.4699</v>
       </c>
       <c r="K16" t="n">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="M16" t="n">
-        <v>1.6956</v>
+        <v>0.7496</v>
       </c>
       <c r="N16" t="n">
-        <v>145</v>
+        <v>352</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.6767</v>
+        <v>1.5577</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5301</v>
+        <v>0.4925</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1391</v>
+        <v>0.1038</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6767</v>
+        <v>1.5577</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6767</v>
+        <v>1.5577</v>
       </c>
       <c r="G17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>3.9371</v>
+        <v>1.5577</v>
       </c>
       <c r="I17" t="n">
-        <v>2.126</v>
+        <v>1.5577</v>
       </c>
       <c r="J17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="L17" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.126</v>
+        <v>1.5577</v>
       </c>
       <c r="N17" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2939</v>
+        <v>1.1591</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4091</v>
+        <v>0.3665</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0352</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2939</v>
+        <v>1.1591</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2939</v>
+        <v>1.1591</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2939</v>
+        <v>1.1591</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2939</v>
+        <v>1.1591</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2939</v>
+        <v>1.1591</v>
       </c>
       <c r="N18" t="n">
-        <v>145</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.2236</v>
+        <v>1.1483</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3869</v>
+        <v>0.3631</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0672</v>
+        <v>-0.0827</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2236</v>
+        <v>1.1483</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2236</v>
+        <v>1.1483</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2236</v>
+        <v>1.1483</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2236</v>
+        <v>1.1483</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2236</v>
+        <v>1.1483</v>
       </c>
       <c r="N19" t="n">
         <v>133</v>
@@ -1320,47 +1320,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.1191</v>
+        <v>1.1014</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3538</v>
+        <v>0.3482</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1148</v>
+        <v>-0.104</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1191</v>
+        <v>1.1014</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1191</v>
+        <v>1.1014</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1191</v>
+        <v>1.1014</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1191</v>
+        <v>1.1014</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1191</v>
+        <v>1.1014</v>
       </c>
       <c r="N20" t="n">
-        <v>133</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8312</v>
+        <v>0.749</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2628</v>
+        <v>0.2368</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2458</v>
+        <v>-0.2646</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8312</v>
+        <v>0.749</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8312</v>
+        <v>0.749</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8312</v>
+        <v>0.749</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8312</v>
+        <v>0.749</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8312</v>
+        <v>0.749</v>
       </c>
       <c r="N21" t="n">
         <v>79</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7729</v>
+        <v>0.628</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2444</v>
+        <v>0.1986</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2724</v>
+        <v>-0.3197</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7729</v>
+        <v>0.628</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1817</v>
+        <v>1.0492</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4088</v>
+        <v>-0.4212</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1817</v>
+        <v>1.0492</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6381</v>
+        <v>0.5891</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4088</v>
+        <v>-0.4212</v>
       </c>
       <c r="K22" t="n">
         <v>49</v>
@@ -1449,7 +1449,7 @@
         <v>91</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2293</v>
+        <v>0.1678999999999999</v>
       </c>
       <c r="N22" t="n">
         <v>140</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.5571</v>
       </c>
       <c r="C23" t="n">
-        <v>0.206</v>
+        <v>0.1761</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3275</v>
+        <v>-0.352</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.5571</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.5571</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.5571</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.5571</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.5571</v>
       </c>
       <c r="N23" t="n">
         <v>90</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3417</v>
+        <v>0.3069</v>
       </c>
       <c r="C24" t="n">
-        <v>0.108</v>
+        <v>0.097</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4687</v>
+        <v>-0.466</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3417</v>
+        <v>0.3069</v>
       </c>
       <c r="F24" t="n">
-        <v>1.25</v>
+        <v>1.2088</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.9083</v>
+        <v>-0.9019</v>
       </c>
       <c r="H24" t="n">
-        <v>1.25</v>
+        <v>1.2088</v>
       </c>
       <c r="I24" t="n">
-        <v>0.675</v>
+        <v>0.6787</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9083</v>
+        <v>-0.9019</v>
       </c>
       <c r="K24" t="n">
         <v>103</v>
@@ -1541,7 +1541,7 @@
         <v>39</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2333</v>
+        <v>-0.2232000000000001</v>
       </c>
       <c r="N24" t="n">
         <v>142</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1565</v>
+        <v>0.128</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0495</v>
+        <v>0.0405</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.553</v>
+        <v>-0.5475</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1565</v>
+        <v>0.128</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1565</v>
+        <v>0.128</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1565</v>
+        <v>0.128</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1565</v>
+        <v>0.128</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1565</v>
+        <v>0.128</v>
       </c>
       <c r="N25" t="n">
         <v>79</v>
@@ -1596,93 +1596,93 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1</v>
+        <v>0.0374</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0316</v>
+        <v>0.0118</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5787</v>
+        <v>-0.5888</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1</v>
+        <v>0.0374</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1</v>
+        <v>0.0374</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1</v>
+        <v>0.0374</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1</v>
+        <v>0.0374</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1</v>
+        <v>0.0374</v>
       </c>
       <c r="N26" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0563</v>
+        <v>0.0078</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0178</v>
+        <v>0.0025</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5986</v>
+        <v>-0.6022</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0563</v>
+        <v>0.0078</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0563</v>
+        <v>0.0078</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0563</v>
+        <v>0.0078</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0563</v>
+        <v>0.0078</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0563</v>
+        <v>0.0078</v>
       </c>
       <c r="N27" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.2671</v>
+        <v>-0.2817</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0844</v>
+        <v>-0.0891</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7458</v>
+        <v>-0.7341</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2671</v>
+        <v>-0.2817</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.2671</v>
+        <v>-0.2817</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.2671</v>
+        <v>-0.2817</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2671</v>
+        <v>-0.2817</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.2671</v>
+        <v>-0.2817</v>
       </c>
       <c r="N28" t="n">
         <v>145</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3067</v>
+        <v>-0.3331</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.097</v>
+        <v>-0.1053</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7638</v>
+        <v>-0.7575</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.3067</v>
+        <v>-0.3331</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.3067</v>
+        <v>-0.3331</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.3067</v>
+        <v>-0.3331</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3067</v>
+        <v>-0.3331</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.3067</v>
+        <v>-0.3331</v>
       </c>
       <c r="N29" t="n">
         <v>145</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4025</v>
+        <v>-0.4127</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1273</v>
+        <v>-0.1305</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.8074</v>
+        <v>-0.7938</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4025</v>
+        <v>-0.4127</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.4025</v>
+        <v>-0.4127</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.4025</v>
+        <v>-0.4127</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4025</v>
+        <v>-0.4127</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4025</v>
+        <v>-0.4127</v>
       </c>
       <c r="N30" t="n">
         <v>79</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.5239</v>
+        <v>-0.4961</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1656</v>
+        <v>-0.1569</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8627</v>
+        <v>-0.8318</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5239</v>
+        <v>-0.4961</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.5239</v>
+        <v>-0.4961</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.5239</v>
+        <v>-0.4961</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5239</v>
+        <v>-0.4961</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.5239</v>
+        <v>-0.4961</v>
       </c>
       <c r="N31" t="n">
         <v>145</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5633</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1781</v>
+        <v>-0.1917</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8806</v>
+        <v>-0.882</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5633</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.5633</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5633</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5633</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5633</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="N32" t="n">
         <v>90</v>
@@ -1918,47 +1918,47 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6205000000000001</v>
+        <v>-0.6226</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1962</v>
+        <v>-0.1968</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9067</v>
+        <v>-0.8894</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6205000000000001</v>
+        <v>-0.6226</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6205000000000001</v>
+        <v>-0.6226</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6205000000000001</v>
+        <v>-0.6226</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6205000000000001</v>
+        <v>-0.6226</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>90</v>
+        <v>133</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.6205000000000001</v>
+        <v>-0.6226</v>
       </c>
       <c r="N33" t="n">
-        <v>90</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6324</v>
+        <v>-0.6503</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1999</v>
+        <v>-0.2056</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9121</v>
+        <v>-0.902</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6324</v>
+        <v>-0.6503</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6324</v>
+        <v>-0.6503</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6324</v>
+        <v>-0.6503</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6324</v>
+        <v>-0.6503</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6324</v>
+        <v>-0.6503</v>
       </c>
       <c r="N34" t="n">
         <v>79</v>
@@ -2010,47 +2010,47 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6776</v>
+        <v>-0.6567</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2142</v>
+        <v>-0.2076</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9327</v>
+        <v>-0.9049</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6776</v>
+        <v>-0.6567</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6776</v>
+        <v>-0.6567</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6776</v>
+        <v>-0.6567</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6776</v>
+        <v>-0.6567</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>133</v>
+        <v>90</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6776</v>
+        <v>-0.6567</v>
       </c>
       <c r="N35" t="n">
-        <v>133</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7811</v>
+        <v>-0.791</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.247</v>
+        <v>-0.2501</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9798</v>
+        <v>-0.9661</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7811</v>
+        <v>-0.791</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7811</v>
+        <v>-0.791</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7811</v>
+        <v>-0.791</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7811</v>
+        <v>-0.791</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7811</v>
+        <v>-0.791</v>
       </c>
       <c r="N36" t="n">
         <v>133</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.0448</v>
+        <v>-0.9228</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3303</v>
+        <v>-0.2918</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0998</v>
+        <v>-1.0262</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.0448</v>
+        <v>-0.9228</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8463000000000001</v>
+        <v>-0.7121</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.1985</v>
+        <v>-0.2107</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8463000000000001</v>
+        <v>-0.7121</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.457</v>
+        <v>-0.3998</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.1985</v>
+        <v>-0.2107</v>
       </c>
       <c r="K37" t="n">
         <v>49</v>
@@ -2139,7 +2139,7 @@
         <v>91</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.6555</v>
+        <v>-0.6105</v>
       </c>
       <c r="N37" t="n">
         <v>140</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.1022</v>
+        <v>-1.1615</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3485</v>
+        <v>-0.3672</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1259</v>
+        <v>-1.1349</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.1022</v>
+        <v>-1.1615</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.1022</v>
+        <v>-0.1615</v>
       </c>
       <c r="G38" t="n">
         <v>-1</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.1022</v>
+        <v>-0.1615</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.0552</v>
+        <v>-0.0907</v>
       </c>
       <c r="J38" t="n">
         <v>-1</v>
@@ -2185,7 +2185,7 @@
         <v>39</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0552</v>
+        <v>-1.0907</v>
       </c>
       <c r="N38" t="n">
         <v>142</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.1874</v>
+        <v>-1.2035</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3754</v>
+        <v>-0.3805</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1647</v>
+        <v>-1.154</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.1874</v>
+        <v>-1.2035</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.1874</v>
+        <v>-1.2035</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.1874</v>
+        <v>-1.2035</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.1874</v>
+        <v>-1.2035</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.1874</v>
+        <v>-1.2035</v>
       </c>
       <c r="N39" t="n">
         <v>90</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.181</v>
+        <v>-1.981</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.6896</v>
+        <v>-0.6263</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.617</v>
+        <v>-1.5082</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.181</v>
+        <v>-1.981</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.5587</v>
+        <v>-0.4234</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.6223</v>
+        <v>-1.5576</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.5587</v>
+        <v>-0.4234</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3017</v>
+        <v>-0.2377</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.6223</v>
+        <v>-1.5576</v>
       </c>
       <c r="K40" t="n">
         <v>192</v>
@@ -2277,7 +2277,7 @@
         <v>160</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.924</v>
+        <v>-1.7953</v>
       </c>
       <c r="N40" t="n">
         <v>352</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.1615</v>
+        <v>-2.9734</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.9996</v>
+        <v>-0.9401</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.0634</v>
+        <v>-1.9603</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.1615</v>
+        <v>-2.9734</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.9528</v>
+        <v>-1.8113</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.2087</v>
+        <v>-1.1621</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.9528</v>
+        <v>-1.8113</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.0545</v>
+        <v>-1.017</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.2087</v>
+        <v>-1.1621</v>
       </c>
       <c r="K41" t="n">
         <v>192</v>
@@ -2323,7 +2323,7 @@
         <v>160</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.2632</v>
+        <v>-2.1791</v>
       </c>
       <c r="N41" t="n">
         <v>352</v>
@@ -2429,10 +2429,10 @@
         <v>0.86</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1402</v>
+        <v>-0.1213</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.6638</v>
+        <v>-2.3047</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.8</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2074</v>
+        <v>-0.1916</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.9406</v>
+        <v>-3.6404</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.7</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3085</v>
+        <v>-0.2971</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.8615</v>
+        <v>-5.6449</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.49</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.493</v>
+        <v>-0.4904</v>
       </c>
       <c r="J5" t="n">
-        <v>-9.367000000000001</v>
+        <v>-9.317600000000001</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.29</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6685</v>
+        <v>-0.6927</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.7015</v>
+        <v>-13.1613</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.9</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6893</v>
+        <v>1.7207</v>
       </c>
       <c r="J7" t="n">
-        <v>32.0967</v>
+        <v>32.6933</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.75</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4946</v>
+        <v>1.5292</v>
       </c>
       <c r="J8" t="n">
-        <v>28.3974</v>
+        <v>29.0548</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.34</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7907999999999999</v>
+        <v>0.7789</v>
       </c>
       <c r="J9" t="n">
-        <v>15.0252</v>
+        <v>14.7991</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.33</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7713</v>
+        <v>0.7581</v>
       </c>
       <c r="J10" t="n">
-        <v>14.6547</v>
+        <v>14.4039</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.24</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5881</v>
+        <v>0.5633</v>
       </c>
       <c r="J11" t="n">
-        <v>11.1739</v>
+        <v>10.7027</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.17</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3949</v>
+        <v>0.3393</v>
       </c>
       <c r="J12" t="n">
-        <v>11.847</v>
+        <v>10.179</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.99</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0219</v>
+        <v>-0.0163</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.657</v>
+        <v>-0.489</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.93</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1075</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.225</v>
+        <v>-2.727</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.92</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1194</v>
+        <v>-0.102</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.582</v>
+        <v>-3.06</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.72</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3242</v>
+        <v>-0.3074</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.726000000000001</v>
+        <v>-9.222</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.42</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0131</v>
+        <v>1.0064</v>
       </c>
       <c r="J17" t="n">
-        <v>30.393</v>
+        <v>30.192</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.14</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4199</v>
+        <v>0.3812</v>
       </c>
       <c r="J18" t="n">
-        <v>12.597</v>
+        <v>11.436</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.04</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1523</v>
+        <v>0.1269</v>
       </c>
       <c r="J19" t="n">
-        <v>4.569</v>
+        <v>3.807</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.01</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0412</v>
+        <v>0.0304</v>
       </c>
       <c r="J20" t="n">
-        <v>1.236</v>
+        <v>0.912</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.97</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1563</v>
+        <v>-0.1249</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.689</v>
+        <v>-3.747</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>0.86</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1169</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.338</v>
+        <v>-1.818</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.8</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1871</v>
+        <v>-0.1668</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.742</v>
+        <v>-3.336</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.48</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4914</v>
+        <v>-0.4894</v>
       </c>
       <c r="J24" t="n">
-        <v>-9.827999999999999</v>
+        <v>-9.788</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.41</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5533</v>
+        <v>-0.5576</v>
       </c>
       <c r="J25" t="n">
-        <v>-11.066</v>
+        <v>-11.152</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.25</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6961000000000001</v>
+        <v>-0.7248</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.922</v>
+        <v>-14.496</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>2.13</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8453</v>
+        <v>1.9822</v>
       </c>
       <c r="J27" t="n">
-        <v>36.906</v>
+        <v>39.644</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.83</v>
       </c>
       <c r="I28" t="n">
-        <v>1.5953</v>
+        <v>1.6242</v>
       </c>
       <c r="J28" t="n">
-        <v>31.906</v>
+        <v>32.484</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.42</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9342</v>
+        <v>0.9352</v>
       </c>
       <c r="J29" t="n">
-        <v>18.684</v>
+        <v>18.704</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.29</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6838</v>
+        <v>0.6651</v>
       </c>
       <c r="J30" t="n">
-        <v>13.676</v>
+        <v>13.302</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.18</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4484</v>
+        <v>0.4168</v>
       </c>
       <c r="J31" t="n">
-        <v>8.968</v>
+        <v>8.336</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.7</v>
       </c>
       <c r="I32" t="n">
-        <v>1.1718</v>
+        <v>1.1675</v>
       </c>
       <c r="J32" t="n">
-        <v>23.436</v>
+        <v>23.35</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.65</v>
       </c>
       <c r="I33" t="n">
-        <v>1.1097</v>
+        <v>1.1031</v>
       </c>
       <c r="J33" t="n">
-        <v>22.194</v>
+        <v>22.062</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.59</v>
       </c>
       <c r="I34" t="n">
-        <v>1.0343</v>
+        <v>1.0258</v>
       </c>
       <c r="J34" t="n">
-        <v>20.686</v>
+        <v>20.516</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.34</v>
       </c>
       <c r="I35" t="n">
-        <v>0.7054</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>14.108</v>
+        <v>13.982</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.96</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2444</v>
+        <v>-0.2158</v>
       </c>
       <c r="J36" t="n">
-        <v>-4.888</v>
+        <v>-4.316</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.19</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4929</v>
+        <v>0.4723</v>
       </c>
       <c r="J37" t="n">
-        <v>9.858000000000001</v>
+        <v>9.446</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.79</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2386</v>
+        <v>-0.223</v>
       </c>
       <c r="J38" t="n">
-        <v>-4.772</v>
+        <v>-4.46</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.7</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3212</v>
+        <v>-0.3061</v>
       </c>
       <c r="J39" t="n">
-        <v>-6.424</v>
+        <v>-6.122</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.59</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.42</v>
+        <v>-0.4102</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.4</v>
+        <v>-8.204000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.44</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5512</v>
+        <v>-0.5568</v>
       </c>
       <c r="J41" t="n">
-        <v>-11.024</v>
+        <v>-11.136</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>2.04</v>
       </c>
       <c r="I42" t="n">
-        <v>1.5354</v>
+        <v>1.5567</v>
       </c>
       <c r="J42" t="n">
-        <v>29.1726</v>
+        <v>29.5773</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.84</v>
       </c>
       <c r="I43" t="n">
-        <v>1.3085</v>
+        <v>1.3155</v>
       </c>
       <c r="J43" t="n">
-        <v>24.8615</v>
+        <v>24.9945</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.6</v>
       </c>
       <c r="I44" t="n">
-        <v>1.0275</v>
+        <v>1.0263</v>
       </c>
       <c r="J44" t="n">
-        <v>19.5225</v>
+        <v>19.4997</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.57</v>
       </c>
       <c r="I45" t="n">
-        <v>0.9903</v>
+        <v>0.9885</v>
       </c>
       <c r="J45" t="n">
-        <v>18.8157</v>
+        <v>18.7815</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1.37</v>
       </c>
       <c r="I46" t="n">
-        <v>0.7251</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>13.7769</v>
+        <v>13.7047</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>0.72</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.2284</v>
+        <v>-0.2019</v>
       </c>
       <c r="J47" t="n">
-        <v>-4.3396</v>
+        <v>-3.8361</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.47</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.4833</v>
+        <v>-0.4858</v>
       </c>
       <c r="J48" t="n">
-        <v>-9.182700000000001</v>
+        <v>-9.2302</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.46</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.4919</v>
+        <v>-0.4946</v>
       </c>
       <c r="J49" t="n">
-        <v>-9.3461</v>
+        <v>-9.397399999999999</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.35</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5871</v>
+        <v>-0.5958</v>
       </c>
       <c r="J50" t="n">
-        <v>-11.1549</v>
+        <v>-11.3202</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.24</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6895</v>
+        <v>-0.7146</v>
       </c>
       <c r="J51" t="n">
-        <v>-13.1005</v>
+        <v>-13.5774</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.41</v>
       </c>
       <c r="I52" t="n">
-        <v>0.672</v>
+        <v>0.6399</v>
       </c>
       <c r="J52" t="n">
-        <v>26.88</v>
+        <v>25.596</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.35</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6055</v>
+        <v>0.5769</v>
       </c>
       <c r="J53" t="n">
-        <v>24.22</v>
+        <v>23.076</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.96</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.0604</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.016</v>
+        <v>-2.416</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.74</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3138</v>
+        <v>-0.2969</v>
       </c>
       <c r="J55" t="n">
-        <v>-12.552</v>
+        <v>-11.876</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.73</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3232</v>
+        <v>-0.3069</v>
       </c>
       <c r="J56" t="n">
-        <v>-12.928</v>
+        <v>-12.276</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.53</v>
       </c>
       <c r="I57" t="n">
-        <v>1.0262</v>
+        <v>1.0169</v>
       </c>
       <c r="J57" t="n">
-        <v>41.048</v>
+        <v>40.676</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.24</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5956</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="J58" t="n">
-        <v>23.824</v>
+        <v>23.328</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.98</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1153</v>
+        <v>-0.0887</v>
       </c>
       <c r="J59" t="n">
-        <v>-4.612</v>
+        <v>-3.548</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.88</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4124</v>
+        <v>-0.3695</v>
       </c>
       <c r="J60" t="n">
-        <v>-16.496</v>
+        <v>-14.78</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.83</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5357</v>
+        <v>-0.4952</v>
       </c>
       <c r="J61" t="n">
-        <v>-21.428</v>
+        <v>-19.808</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.91</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8238</v>
+        <v>0.7706</v>
       </c>
       <c r="J62" t="n">
-        <v>17.2998</v>
+        <v>16.1826</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.69</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6804</v>
+        <v>0.638</v>
       </c>
       <c r="J63" t="n">
-        <v>14.2884</v>
+        <v>13.398</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.54</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5798</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="J64" t="n">
-        <v>12.1758</v>
+        <v>11.5059</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.42</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4943</v>
+        <v>0.4525</v>
       </c>
       <c r="J65" t="n">
-        <v>10.3803</v>
+        <v>9.5025</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.18</v>
       </c>
       <c r="I66" t="n">
-        <v>0.2477</v>
+        <v>0.2028</v>
       </c>
       <c r="J66" t="n">
-        <v>5.2017</v>
+        <v>4.2588</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>0.82</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.1877</v>
+        <v>-0.1712</v>
       </c>
       <c r="J67" t="n">
-        <v>-3.9417</v>
+        <v>-3.5952</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.79</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.22</v>
+        <v>-0.2049</v>
       </c>
       <c r="J68" t="n">
-        <v>-4.62</v>
+        <v>-4.3029</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.75</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2612</v>
+        <v>-0.2478</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.4852</v>
+        <v>-5.2038</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.42</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5557</v>
+        <v>-0.5607</v>
       </c>
       <c r="J70" t="n">
-        <v>-11.6697</v>
+        <v>-11.7747</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.4</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5732</v>
+        <v>-0.5808</v>
       </c>
       <c r="J71" t="n">
-        <v>-12.0372</v>
+        <v>-12.1968</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.31</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5806</v>
+        <v>0.5557</v>
       </c>
       <c r="J72" t="n">
-        <v>17.418</v>
+        <v>16.671</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.07</v>
       </c>
       <c r="I73" t="n">
-        <v>0.202</v>
+        <v>0.1602</v>
       </c>
       <c r="J73" t="n">
-        <v>6.06</v>
+        <v>4.806</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.97</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.055</v>
+        <v>-0.044</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.65</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.71</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3333</v>
+        <v>-0.3171</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.999000000000001</v>
+        <v>-9.513</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.66</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.379</v>
+        <v>-0.3663</v>
       </c>
       <c r="J76" t="n">
-        <v>-11.37</v>
+        <v>-10.989</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.36</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7713</v>
+        <v>0.7553</v>
       </c>
       <c r="J77" t="n">
-        <v>23.139</v>
+        <v>22.659</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.24</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.577</v>
       </c>
       <c r="J78" t="n">
-        <v>17.646</v>
+        <v>17.31</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.05</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1804</v>
+        <v>0.153</v>
       </c>
       <c r="J79" t="n">
-        <v>5.412</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.03</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1153</v>
+        <v>0.094</v>
       </c>
       <c r="J80" t="n">
-        <v>3.459</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.0222</v>
+        <v>-0.0169</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.666</v>
+        <v>-0.507</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.42</v>
       </c>
       <c r="I82" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.6978</v>
       </c>
       <c r="J82" t="n">
-        <v>22.635</v>
+        <v>20.934</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.13</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2952</v>
+        <v>0.2471</v>
       </c>
       <c r="J83" t="n">
-        <v>8.856</v>
+        <v>7.413</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.11</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2587</v>
+        <v>0.2141</v>
       </c>
       <c r="J84" t="n">
-        <v>7.761</v>
+        <v>6.423</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.05</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1387</v>
+        <v>0.1089</v>
       </c>
       <c r="J85" t="n">
-        <v>4.161</v>
+        <v>3.267</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.74</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3181</v>
+        <v>-0.302</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.542999999999999</v>
+        <v>-9.06</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.59</v>
       </c>
       <c r="I87" t="n">
-        <v>1.2918</v>
+        <v>1.3222</v>
       </c>
       <c r="J87" t="n">
-        <v>38.754</v>
+        <v>39.666</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.09</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3161</v>
+        <v>0.2749</v>
       </c>
       <c r="J88" t="n">
-        <v>9.483000000000001</v>
+        <v>8.247</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.5634</v>
+        <v>-0.5231</v>
       </c>
       <c r="J89" t="n">
-        <v>-16.902</v>
+        <v>-15.693</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.78</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.6323</v>
+        <v>-0.5951</v>
       </c>
       <c r="J90" t="n">
-        <v>-18.969</v>
+        <v>-17.853</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.71</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.7602</v>
       </c>
       <c r="J91" t="n">
-        <v>-23.604</v>
+        <v>-22.806</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.24</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3588</v>
+        <v>0.2983</v>
       </c>
       <c r="J92" t="n">
-        <v>12.9168</v>
+        <v>10.7388</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.14</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2336</v>
+        <v>0.1859</v>
       </c>
       <c r="J93" t="n">
-        <v>8.409599999999999</v>
+        <v>6.6924</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.08</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1505</v>
+        <v>0.1151</v>
       </c>
       <c r="J94" t="n">
-        <v>5.418</v>
+        <v>4.1436</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.03</v>
       </c>
       <c r="I95" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.049</v>
       </c>
       <c r="J95" t="n">
-        <v>2.466</v>
+        <v>1.764</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.91</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1422</v>
+        <v>-0.1225</v>
       </c>
       <c r="J96" t="n">
-        <v>-5.1192</v>
+        <v>-4.41</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.23</v>
       </c>
       <c r="I97" t="n">
-        <v>0.38</v>
+        <v>0.3749</v>
       </c>
       <c r="J97" t="n">
-        <v>13.68</v>
+        <v>13.4964</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.22</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3669</v>
+        <v>0.3605</v>
       </c>
       <c r="J98" t="n">
-        <v>13.2084</v>
+        <v>12.978</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.19</v>
       </c>
       <c r="I99" t="n">
-        <v>0.327</v>
+        <v>0.317</v>
       </c>
       <c r="J99" t="n">
-        <v>11.772</v>
+        <v>11.412</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.78</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2717</v>
+        <v>-0.2525</v>
       </c>
       <c r="J100" t="n">
-        <v>-9.7812</v>
+        <v>-9.09</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4716</v>
+        <v>-0.4694</v>
       </c>
       <c r="J101" t="n">
-        <v>-16.9776</v>
+        <v>-16.8984</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.32</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6405</v>
+        <v>0.5838</v>
       </c>
       <c r="J102" t="n">
-        <v>17.934</v>
+        <v>16.3464</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.93</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.1086</v>
+        <v>-0.0916</v>
       </c>
       <c r="J103" t="n">
-        <v>-3.0408</v>
+        <v>-2.5648</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.92</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1206</v>
+        <v>-0.1028</v>
       </c>
       <c r="J104" t="n">
-        <v>-3.3768</v>
+        <v>-2.8784</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.89</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1549</v>
+        <v>-0.1354</v>
       </c>
       <c r="J105" t="n">
-        <v>-4.3372</v>
+        <v>-3.7912</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.75</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2974</v>
+        <v>-0.2792</v>
       </c>
       <c r="J106" t="n">
-        <v>-8.327199999999999</v>
+        <v>-7.8176</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.37</v>
       </c>
       <c r="I107" t="n">
-        <v>0.924</v>
+        <v>0.9088000000000001</v>
       </c>
       <c r="J107" t="n">
-        <v>25.872</v>
+        <v>25.4464</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.26</v>
       </c>
       <c r="I108" t="n">
-        <v>0.6962</v>
+        <v>0.6626</v>
       </c>
       <c r="J108" t="n">
-        <v>19.4936</v>
+        <v>18.5528</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.23</v>
       </c>
       <c r="I109" t="n">
-        <v>0.6311</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="J109" t="n">
-        <v>17.6708</v>
+        <v>16.6404</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.79</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.6274</v>
+        <v>-0.591</v>
       </c>
       <c r="J110" t="n">
-        <v>-17.5672</v>
+        <v>-16.548</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.77</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6726</v>
+        <v>-0.639</v>
       </c>
       <c r="J111" t="n">
-        <v>-18.8328</v>
+        <v>-17.892</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.43</v>
       </c>
       <c r="I112" t="n">
-        <v>1.001</v>
+        <v>0.9981</v>
       </c>
       <c r="J112" t="n">
-        <v>26.026</v>
+        <v>25.9506</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.35</v>
       </c>
       <c r="I113" t="n">
-        <v>0.8528</v>
+        <v>0.832</v>
       </c>
       <c r="J113" t="n">
-        <v>22.1728</v>
+        <v>21.632</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.15</v>
       </c>
       <c r="I114" t="n">
-        <v>0.4336</v>
+        <v>0.399</v>
       </c>
       <c r="J114" t="n">
-        <v>11.2736</v>
+        <v>10.374</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.09</v>
       </c>
       <c r="I115" t="n">
-        <v>0.2838</v>
+        <v>0.2519</v>
       </c>
       <c r="J115" t="n">
-        <v>7.3788</v>
+        <v>6.5494</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.98</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.1349</v>
+        <v>-0.1077</v>
       </c>
       <c r="J116" t="n">
-        <v>-3.5074</v>
+        <v>-2.8002</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.13</v>
       </c>
       <c r="I117" t="n">
-        <v>0.322</v>
+        <v>0.27</v>
       </c>
       <c r="J117" t="n">
-        <v>8.372</v>
+        <v>7.02</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.12</v>
       </c>
       <c r="I118" t="n">
-        <v>0.303</v>
+        <v>0.2522</v>
       </c>
       <c r="J118" t="n">
-        <v>7.878</v>
+        <v>6.5572</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.87</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1752</v>
+        <v>-0.1553</v>
       </c>
       <c r="J119" t="n">
-        <v>-4.5552</v>
+        <v>-4.0378</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.85</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1964</v>
+        <v>-0.1761</v>
       </c>
       <c r="J120" t="n">
-        <v>-5.1064</v>
+        <v>-4.5786</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.75</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2957</v>
+        <v>-0.2774</v>
       </c>
       <c r="J121" t="n">
-        <v>-7.6882</v>
+        <v>-7.2124</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.39</v>
       </c>
       <c r="I122" t="n">
-        <v>0.9346</v>
+        <v>0.921</v>
       </c>
       <c r="J122" t="n">
-        <v>25.2342</v>
+        <v>24.867</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.2</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.5118</v>
       </c>
       <c r="J123" t="n">
-        <v>14.7663</v>
+        <v>13.8186</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.16</v>
       </c>
       <c r="I124" t="n">
-        <v>0.4591</v>
+        <v>0.4236</v>
       </c>
       <c r="J124" t="n">
-        <v>12.3957</v>
+        <v>11.4372</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.09</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2868</v>
+        <v>0.2543</v>
       </c>
       <c r="J125" t="n">
-        <v>7.7436</v>
+        <v>6.8661</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>1.07</v>
       </c>
       <c r="I126" t="n">
-        <v>0.2317</v>
+        <v>0.2016</v>
       </c>
       <c r="J126" t="n">
-        <v>6.2559</v>
+        <v>5.4432</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.58</v>
       </c>
       <c r="I127" t="n">
-        <v>1.0259</v>
+        <v>1.0081</v>
       </c>
       <c r="J127" t="n">
-        <v>27.6993</v>
+        <v>27.2187</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.09520000000000001</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="J128" t="n">
-        <v>-2.5704</v>
+        <v>-2.1519</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.79</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2571</v>
+        <v>-0.2373</v>
       </c>
       <c r="J129" t="n">
-        <v>-6.9417</v>
+        <v>-6.4071</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.76</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2862</v>
+        <v>-0.2674</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.7274</v>
+        <v>-7.2198</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.65</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.388</v>
+        <v>-0.3761</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.476</v>
+        <v>-10.1547</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.39</v>
       </c>
       <c r="I132" t="n">
-        <v>0.7499</v>
+        <v>0.6979</v>
       </c>
       <c r="J132" t="n">
-        <v>19.4974</v>
+        <v>18.1454</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.24</v>
       </c>
       <c r="I133" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.4533</v>
       </c>
       <c r="J133" t="n">
-        <v>13.3016</v>
+        <v>11.7858</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.88</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1658</v>
+        <v>-0.1459</v>
       </c>
       <c r="J134" t="n">
-        <v>-4.3108</v>
+        <v>-3.7934</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.68</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3624</v>
+        <v>-0.3484</v>
       </c>
       <c r="J135" t="n">
-        <v>-9.4224</v>
+        <v>-9.058400000000001</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.61</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4251</v>
+        <v>-0.417</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.0526</v>
+        <v>-10.842</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.48</v>
       </c>
       <c r="I137" t="n">
-        <v>1.0809</v>
+        <v>1.0904</v>
       </c>
       <c r="J137" t="n">
-        <v>28.1034</v>
+        <v>28.3504</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.35</v>
       </c>
       <c r="I138" t="n">
-        <v>0.8574000000000001</v>
+        <v>0.8364</v>
       </c>
       <c r="J138" t="n">
-        <v>22.2924</v>
+        <v>21.7464</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.16</v>
       </c>
       <c r="I139" t="n">
-        <v>0.4594</v>
+        <v>0.4237</v>
       </c>
       <c r="J139" t="n">
-        <v>11.9444</v>
+        <v>11.0162</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.1</v>
       </c>
       <c r="I140" t="n">
-        <v>0.3134</v>
+        <v>0.2801</v>
       </c>
       <c r="J140" t="n">
-        <v>8.148400000000001</v>
+        <v>7.2826</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5989</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="J141" t="n">
-        <v>-15.5714</v>
+        <v>-14.638</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.44</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.483</v>
       </c>
       <c r="J142" t="n">
-        <v>12.1418</v>
+        <v>10.626</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.37</v>
       </c>
       <c r="I143" t="n">
-        <v>0.4797</v>
+        <v>0.4144</v>
       </c>
       <c r="J143" t="n">
-        <v>10.5534</v>
+        <v>9.1168</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.33</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4376</v>
+        <v>0.3751</v>
       </c>
       <c r="J144" t="n">
-        <v>9.6272</v>
+        <v>8.2522</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.21</v>
       </c>
       <c r="I145" t="n">
-        <v>0.3049</v>
+        <v>0.2539</v>
       </c>
       <c r="J145" t="n">
-        <v>6.7078</v>
+        <v>5.5858</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.1</v>
       </c>
       <c r="I146" t="n">
-        <v>0.1621</v>
+        <v>0.1274</v>
       </c>
       <c r="J146" t="n">
-        <v>3.5662</v>
+        <v>2.8028</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.44</v>
       </c>
       <c r="I147" t="n">
-        <v>0.6999</v>
+        <v>0.7645</v>
       </c>
       <c r="J147" t="n">
-        <v>15.3978</v>
+        <v>16.819</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.02</v>
       </c>
       <c r="I148" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.0762</v>
       </c>
       <c r="J148" t="n">
-        <v>1.9338</v>
+        <v>1.6764</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.74</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2924</v>
+        <v>-0.2748</v>
       </c>
       <c r="J149" t="n">
-        <v>-6.4328</v>
+        <v>-6.0456</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.46</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.5417999999999999</v>
+        <v>-0.547</v>
       </c>
       <c r="J150" t="n">
-        <v>-11.9196</v>
+        <v>-12.034</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.43</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5673</v>
+        <v>-0.5765</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.4806</v>
+        <v>-12.683</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.72</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.2743</v>
+        <v>-0.2612</v>
       </c>
       <c r="J152" t="n">
-        <v>-5.7603</v>
+        <v>-5.4852</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.68</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.3145</v>
+        <v>-0.3042</v>
       </c>
       <c r="J153" t="n">
-        <v>-6.6045</v>
+        <v>-6.3882</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.5</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.4746</v>
+        <v>-0.4712</v>
       </c>
       <c r="J154" t="n">
-        <v>-9.9666</v>
+        <v>-9.895200000000001</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.47</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.5009</v>
+        <v>-0.4995</v>
       </c>
       <c r="J155" t="n">
-        <v>-10.5189</v>
+        <v>-10.4895</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.45</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5185</v>
+        <v>-0.5189</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.8885</v>
+        <v>-10.8969</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.59</v>
       </c>
       <c r="I157" t="n">
-        <v>1.1803</v>
+        <v>1.1977</v>
       </c>
       <c r="J157" t="n">
-        <v>24.7863</v>
+        <v>25.1517</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.57</v>
       </c>
       <c r="I158" t="n">
-        <v>1.155</v>
+        <v>1.172</v>
       </c>
       <c r="J158" t="n">
-        <v>24.255</v>
+        <v>24.612</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.55</v>
       </c>
       <c r="I159" t="n">
-        <v>1.1296</v>
+        <v>1.1463</v>
       </c>
       <c r="J159" t="n">
-        <v>23.7216</v>
+        <v>24.0723</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.46</v>
       </c>
       <c r="I160" t="n">
-        <v>1.0098</v>
+        <v>1.0173</v>
       </c>
       <c r="J160" t="n">
-        <v>21.2058</v>
+        <v>21.3633</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.12</v>
       </c>
       <c r="I161" t="n">
-        <v>0.321</v>
+        <v>0.288</v>
       </c>
       <c r="J161" t="n">
-        <v>6.741</v>
+        <v>6.048</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.41</v>
       </c>
       <c r="I162" t="n">
-        <v>0.7927</v>
+        <v>0.7457</v>
       </c>
       <c r="J162" t="n">
-        <v>21.4029</v>
+        <v>20.1339</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.21</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4702</v>
+        <v>0.4133</v>
       </c>
       <c r="J163" t="n">
-        <v>12.6954</v>
+        <v>11.1591</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.91</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1297</v>
+        <v>-0.1121</v>
       </c>
       <c r="J164" t="n">
-        <v>-3.5019</v>
+        <v>-3.0267</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.61</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.4222</v>
+        <v>-0.4135</v>
       </c>
       <c r="J165" t="n">
-        <v>-11.3994</v>
+        <v>-11.1645</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.5</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5174</v>
+        <v>-0.5205</v>
       </c>
       <c r="J166" t="n">
-        <v>-13.9698</v>
+        <v>-14.0535</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.37</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8915999999999999</v>
+        <v>0.8739</v>
       </c>
       <c r="J167" t="n">
-        <v>24.0732</v>
+        <v>23.5953</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.3</v>
       </c>
       <c r="I168" t="n">
-        <v>0.7526</v>
+        <v>0.7255</v>
       </c>
       <c r="J168" t="n">
-        <v>20.3202</v>
+        <v>19.5885</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.19</v>
       </c>
       <c r="I169" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.4894</v>
       </c>
       <c r="J169" t="n">
-        <v>14.1399</v>
+        <v>13.2138</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.1</v>
       </c>
       <c r="I170" t="n">
-        <v>0.3099</v>
+        <v>0.2772</v>
       </c>
       <c r="J170" t="n">
-        <v>8.3673</v>
+        <v>7.4844</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.05</v>
       </c>
       <c r="I171" t="n">
-        <v>0.1691</v>
+        <v>0.143</v>
       </c>
       <c r="J171" t="n">
-        <v>4.5657</v>
+        <v>3.861</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.11</v>
       </c>
       <c r="I172" t="n">
-        <v>0.2719</v>
+        <v>0.2236</v>
       </c>
       <c r="J172" t="n">
-        <v>6.5256</v>
+        <v>5.3664</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.06</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1701</v>
+        <v>0.133</v>
       </c>
       <c r="J173" t="n">
-        <v>4.0824</v>
+        <v>3.192</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.05</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1479</v>
+        <v>0.1138</v>
       </c>
       <c r="J174" t="n">
-        <v>3.5496</v>
+        <v>2.7312</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.99</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.0252</v>
+        <v>-0.0181</v>
       </c>
       <c r="J175" t="n">
-        <v>-0.6048</v>
+        <v>-0.4344</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.79</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.2623</v>
+        <v>-0.2427</v>
       </c>
       <c r="J176" t="n">
-        <v>-6.2952</v>
+        <v>-5.8248</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.5</v>
       </c>
       <c r="I177" t="n">
-        <v>1.1047</v>
+        <v>1.1161</v>
       </c>
       <c r="J177" t="n">
-        <v>26.5128</v>
+        <v>26.7864</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.45</v>
       </c>
       <c r="I178" t="n">
-        <v>1.0331</v>
+        <v>1.0359</v>
       </c>
       <c r="J178" t="n">
-        <v>24.7944</v>
+        <v>24.8616</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.37</v>
       </c>
       <c r="I179" t="n">
-        <v>0.8925</v>
+        <v>0.8748</v>
       </c>
       <c r="J179" t="n">
-        <v>21.42</v>
+        <v>20.9952</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.85</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.5069</v>
+        <v>-0.4676</v>
       </c>
       <c r="J180" t="n">
-        <v>-12.1656</v>
+        <v>-11.2224</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.82</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5786</v>
+        <v>-0.5422</v>
       </c>
       <c r="J181" t="n">
-        <v>-13.8864</v>
+        <v>-13.0128</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.89</v>
       </c>
       <c r="I182" t="n">
-        <v>1.5448</v>
+        <v>1.5795</v>
       </c>
       <c r="J182" t="n">
-        <v>33.9856</v>
+        <v>34.749</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.76</v>
       </c>
       <c r="I183" t="n">
-        <v>1.3888</v>
+        <v>1.4137</v>
       </c>
       <c r="J183" t="n">
-        <v>30.5536</v>
+        <v>31.1014</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.45</v>
       </c>
       <c r="I184" t="n">
-        <v>0.9939</v>
+        <v>0.9999</v>
       </c>
       <c r="J184" t="n">
-        <v>21.8658</v>
+        <v>21.9978</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.16</v>
       </c>
       <c r="I185" t="n">
-        <v>0.4159</v>
+        <v>0.3842</v>
       </c>
       <c r="J185" t="n">
-        <v>9.149800000000001</v>
+        <v>8.452400000000001</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.1</v>
       </c>
       <c r="I186" t="n">
-        <v>0.2677</v>
+        <v>0.2344</v>
       </c>
       <c r="J186" t="n">
-        <v>5.8894</v>
+        <v>5.1568</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.11</v>
       </c>
       <c r="I187" t="n">
-        <v>0.3682</v>
+        <v>0.3318</v>
       </c>
       <c r="J187" t="n">
-        <v>8.1004</v>
+        <v>7.2996</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.83</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1938</v>
+        <v>-0.1784</v>
       </c>
       <c r="J188" t="n">
-        <v>-4.2636</v>
+        <v>-3.9248</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.57</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.4344</v>
+        <v>-0.426</v>
       </c>
       <c r="J189" t="n">
-        <v>-9.556800000000001</v>
+        <v>-9.372</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.55</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.4521</v>
+        <v>-0.4453</v>
       </c>
       <c r="J190" t="n">
-        <v>-9.946199999999999</v>
+        <v>-9.7966</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.52</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4785</v>
+        <v>-0.4744</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.527</v>
+        <v>-10.4368</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.79</v>
       </c>
       <c r="I192" t="n">
-        <v>1.4475</v>
+        <v>1.4755</v>
       </c>
       <c r="J192" t="n">
-        <v>30.3975</v>
+        <v>30.9855</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.56</v>
       </c>
       <c r="I193" t="n">
-        <v>1.1561</v>
+        <v>1.1706</v>
       </c>
       <c r="J193" t="n">
-        <v>24.2781</v>
+        <v>24.5826</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.22</v>
       </c>
       <c r="I194" t="n">
-        <v>0.5682</v>
+        <v>0.5406</v>
       </c>
       <c r="J194" t="n">
-        <v>11.9322</v>
+        <v>11.3526</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.21</v>
       </c>
       <c r="I195" t="n">
-        <v>0.5465</v>
+        <v>0.5182</v>
       </c>
       <c r="J195" t="n">
-        <v>11.4765</v>
+        <v>10.8822</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.99</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.1189</v>
+        <v>-0.1003</v>
       </c>
       <c r="J196" t="n">
-        <v>-2.4969</v>
+        <v>-2.1063</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.15</v>
       </c>
       <c r="I197" t="n">
-        <v>0.4464</v>
+        <v>0.4088</v>
       </c>
       <c r="J197" t="n">
-        <v>9.3744</v>
+        <v>8.5848</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.86</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.1622</v>
+        <v>-0.1466</v>
       </c>
       <c r="J198" t="n">
-        <v>-3.4062</v>
+        <v>-3.0786</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.59</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.4175</v>
+        <v>-0.4076</v>
       </c>
       <c r="J199" t="n">
-        <v>-8.7675</v>
+        <v>-8.5596</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.57</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4352</v>
+        <v>-0.4268</v>
       </c>
       <c r="J200" t="n">
-        <v>-9.139200000000001</v>
+        <v>-8.9628</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.44</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5489000000000001</v>
+        <v>-0.554</v>
       </c>
       <c r="J201" t="n">
-        <v>-11.5269</v>
+        <v>-11.634</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.63</v>
       </c>
       <c r="I202" t="n">
-        <v>1.2734</v>
+        <v>1.2919</v>
       </c>
       <c r="J202" t="n">
-        <v>36.9286</v>
+        <v>37.4651</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.43</v>
       </c>
       <c r="I203" t="n">
-        <v>0.9957</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="J203" t="n">
-        <v>28.8753</v>
+        <v>28.7796</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.13</v>
       </c>
       <c r="I204" t="n">
-        <v>0.3821</v>
+        <v>0.3486</v>
       </c>
       <c r="J204" t="n">
-        <v>11.0809</v>
+        <v>10.1094</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.07</v>
       </c>
       <c r="I205" t="n">
-        <v>0.2246</v>
+        <v>0.1953</v>
       </c>
       <c r="J205" t="n">
-        <v>6.5134</v>
+        <v>5.6637</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.86</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4868</v>
+        <v>-0.4475</v>
       </c>
       <c r="J206" t="n">
-        <v>-14.1172</v>
+        <v>-12.9775</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.31</v>
       </c>
       <c r="I207" t="n">
-        <v>0.6293</v>
+        <v>0.5729</v>
       </c>
       <c r="J207" t="n">
-        <v>18.2497</v>
+        <v>16.6141</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.18</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4121</v>
+        <v>0.3559</v>
       </c>
       <c r="J208" t="n">
-        <v>11.9509</v>
+        <v>10.3211</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.91</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1312</v>
+        <v>-0.113</v>
       </c>
       <c r="J209" t="n">
-        <v>-3.8048</v>
+        <v>-3.277</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3521</v>
+        <v>-0.3373</v>
       </c>
       <c r="J210" t="n">
-        <v>-10.2109</v>
+        <v>-9.781700000000001</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.65</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3884</v>
+        <v>-0.3766</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.2636</v>
+        <v>-10.9214</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.25</v>
       </c>
       <c r="I212" t="n">
-        <v>0.6682</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="J212" t="n">
-        <v>19.3778</v>
+        <v>18.3744</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.23</v>
       </c>
       <c r="I213" t="n">
-        <v>0.625</v>
+        <v>0.5886</v>
       </c>
       <c r="J213" t="n">
-        <v>18.125</v>
+        <v>17.0694</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.22</v>
       </c>
       <c r="I214" t="n">
-        <v>0.6031</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="J214" t="n">
-        <v>17.4899</v>
+        <v>16.414</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.97</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1552</v>
+        <v>-0.1238</v>
       </c>
       <c r="J215" t="n">
-        <v>-4.5008</v>
+        <v>-3.5902</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.88</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4159</v>
+        <v>-0.3732</v>
       </c>
       <c r="J216" t="n">
-        <v>-12.0611</v>
+        <v>-10.8228</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.33</v>
       </c>
       <c r="I217" t="n">
-        <v>0.6603</v>
+        <v>0.6049</v>
       </c>
       <c r="J217" t="n">
-        <v>19.1487</v>
+        <v>17.5421</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.12</v>
       </c>
       <c r="I218" t="n">
-        <v>0.3016</v>
+        <v>0.2508</v>
       </c>
       <c r="J218" t="n">
-        <v>8.7464</v>
+        <v>7.2732</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.01</v>
       </c>
       <c r="I219" t="n">
-        <v>0.0499</v>
+        <v>0.0334</v>
       </c>
       <c r="J219" t="n">
-        <v>1.4471</v>
+        <v>0.9686</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.86</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1864</v>
+        <v>-0.1662</v>
       </c>
       <c r="J220" t="n">
-        <v>-5.4056</v>
+        <v>-4.8198</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.43</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5779</v>
+        <v>-0.5907</v>
       </c>
       <c r="J221" t="n">
-        <v>-16.7591</v>
+        <v>-17.1303</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.73</v>
       </c>
       <c r="I222" t="n">
-        <v>1.3906</v>
+        <v>1.4156</v>
       </c>
       <c r="J222" t="n">
-        <v>38.9368</v>
+        <v>39.6368</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.35</v>
       </c>
       <c r="I223" t="n">
-        <v>0.8387</v>
+        <v>0.8198</v>
       </c>
       <c r="J223" t="n">
-        <v>23.4836</v>
+        <v>22.9544</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.34</v>
       </c>
       <c r="I224" t="n">
-        <v>0.8193</v>
+        <v>0.7993</v>
       </c>
       <c r="J224" t="n">
-        <v>22.9404</v>
+        <v>22.3804</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.03</v>
       </c>
       <c r="I225" t="n">
-        <v>0.0916</v>
+        <v>0.0709</v>
       </c>
       <c r="J225" t="n">
-        <v>2.5648</v>
+        <v>1.9852</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.92</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3381</v>
+        <v>-0.2995</v>
       </c>
       <c r="J226" t="n">
-        <v>-9.466799999999999</v>
+        <v>-8.385999999999999</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.07</v>
       </c>
       <c r="I227" t="n">
-        <v>0.2112</v>
+        <v>0.1688</v>
       </c>
       <c r="J227" t="n">
-        <v>5.9136</v>
+        <v>4.7264</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.97</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.0514</v>
+        <v>-0.0414</v>
       </c>
       <c r="J228" t="n">
-        <v>-1.4392</v>
+        <v>-1.1592</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.89</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1504</v>
+        <v>-0.1322</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.2112</v>
+        <v>-3.7016</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2334</v>
+        <v>-0.2136</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.5352</v>
+        <v>-5.9808</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.78</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2629</v>
+        <v>-0.2436</v>
       </c>
       <c r="J231" t="n">
-        <v>-7.3612</v>
+        <v>-6.8208</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>2.16</v>
       </c>
       <c r="I232" t="n">
-        <v>1.8725</v>
+        <v>1.9407</v>
       </c>
       <c r="J232" t="n">
-        <v>39.3225</v>
+        <v>40.7547</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.65</v>
       </c>
       <c r="I233" t="n">
-        <v>1.2617</v>
+        <v>1.2802</v>
       </c>
       <c r="J233" t="n">
-        <v>26.4957</v>
+        <v>26.8842</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.16</v>
       </c>
       <c r="I234" t="n">
-        <v>0.4241</v>
+        <v>0.3929</v>
       </c>
       <c r="J234" t="n">
-        <v>8.9061</v>
+        <v>8.2509</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.06</v>
       </c>
       <c r="I235" t="n">
-        <v>0.1649</v>
+        <v>0.1355</v>
       </c>
       <c r="J235" t="n">
-        <v>3.4629</v>
+        <v>2.8455</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>1.05</v>
       </c>
       <c r="I236" t="n">
-        <v>0.1347</v>
+        <v>0.1068</v>
       </c>
       <c r="J236" t="n">
-        <v>2.8287</v>
+        <v>2.2428</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>0.82</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.1892</v>
+        <v>-0.1729</v>
       </c>
       <c r="J237" t="n">
-        <v>-3.9732</v>
+        <v>-3.6309</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.79</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.2213</v>
+        <v>-0.2064</v>
       </c>
       <c r="J238" t="n">
-        <v>-4.6473</v>
+        <v>-4.3344</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.55</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.4422</v>
+        <v>-0.4351</v>
       </c>
       <c r="J239" t="n">
-        <v>-9.286199999999999</v>
+        <v>-9.1371</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.53</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.4598</v>
+        <v>-0.454</v>
       </c>
       <c r="J240" t="n">
-        <v>-9.655799999999999</v>
+        <v>-9.534000000000001</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.52</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4686</v>
+        <v>-0.4636</v>
       </c>
       <c r="J241" t="n">
-        <v>-9.8406</v>
+        <v>-9.7356</v>
       </c>
     </row>
   </sheetData>
